--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>12 September 2026</t>
+    <t>13 September 2026</t>
   </si>
   <si>
     <t>To</t>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>13 September 2026</t>
+    <t>14 September 2026</t>
   </si>
   <si>
     <t>To</t>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9232,7 +9232,7 @@
         <v>20</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I20" s="0" t="s">
         <v>21</v>
@@ -9377,7 +9377,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>21</v>
@@ -9667,7 +9667,7 @@
         <v>20</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I35" s="0" t="s">
         <v>21</v>
@@ -9696,7 +9696,7 @@
         <v>20</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="0" t="s">
         <v>21</v>
@@ -10943,7 +10943,7 @@
         <v>20</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I79" s="0" t="s">
         <v>21</v>
@@ -11349,7 +11349,7 @@
         <v>20</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I93" s="0" t="s">
         <v>21</v>
@@ -11668,7 +11668,7 @@
         <v>20</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I104" s="0" t="s">
         <v>21</v>
@@ -11900,7 +11900,7 @@
         <v>20</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I112" s="0" t="s">
         <v>21</v>
@@ -11929,7 +11929,7 @@
         <v>20</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I113" s="0" t="s">
         <v>21</v>
@@ -12103,7 +12103,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12654,7 +12654,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -12886,7 +12886,7 @@
         <v>20</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>21</v>
@@ -13321,7 +13321,7 @@
         <v>20</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I161" s="0" t="s">
         <v>21</v>
@@ -13437,7 +13437,7 @@
         <v>20</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I165" s="0" t="s">
         <v>21</v>
@@ -13814,7 +13814,7 @@
         <v>20</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>21</v>
@@ -14394,7 +14394,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -16598,7 +16598,7 @@
         <v>20</v>
       </c>
       <c r="H274" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I274" s="0" t="s">
         <v>21</v>
@@ -17091,7 +17091,7 @@
         <v>20</v>
       </c>
       <c r="H291" s="3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="I291" s="0" t="s">
         <v>21</v>
@@ -17642,7 +17642,7 @@
         <v>20</v>
       </c>
       <c r="H310" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I310" s="0" t="s">
         <v>21</v>
@@ -18164,7 +18164,7 @@
         <v>20</v>
       </c>
       <c r="H328" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I328" s="0" t="s">
         <v>21</v>
@@ -19962,7 +19962,7 @@
         <v>20</v>
       </c>
       <c r="H390" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I390" s="0" t="s">
         <v>21</v>
@@ -20136,7 +20136,7 @@
         <v>20</v>
       </c>
       <c r="H396" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I396" s="0" t="s">
         <v>21</v>
@@ -20281,7 +20281,7 @@
         <v>20</v>
       </c>
       <c r="H401" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I401" s="0" t="s">
         <v>21</v>
@@ -21876,7 +21876,7 @@
         <v>391</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22050,7 +22050,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -25153,7 +25153,7 @@
         <v>20</v>
       </c>
       <c r="H569" s="3" t="n">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="I569" s="0" t="s">
         <v>21</v>
@@ -25182,7 +25182,7 @@
         <v>20</v>
       </c>
       <c r="H570" s="3" t="n">
-        <v>-726</v>
+        <v>-727</v>
       </c>
       <c r="I570" s="0" t="s">
         <v>21</v>
@@ -25260,7 +25260,7 @@
         <v>10</v>
       </c>
       <c r="E573" s="3" t="n">
-        <v>5.83</v>
+        <v>5.38</v>
       </c>
       <c r="F573" s="2" t="s">
         <v>19</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>-3</v>
+        <v>10</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -29068,7 +29068,7 @@
         <v>391</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -30286,7 +30286,7 @@
         <v>844</v>
       </c>
       <c r="H746" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I746" s="0" t="s">
         <v>21</v>
@@ -31243,7 +31243,7 @@
         <v>391</v>
       </c>
       <c r="H779" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I779" s="0" t="s">
         <v>21</v>
@@ -31533,7 +31533,7 @@
         <v>391</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I789" s="0" t="s">
         <v>21</v>
@@ -35622,7 +35622,7 @@
         <v>20</v>
       </c>
       <c r="H930" s="3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I930" s="0" t="s">
         <v>21</v>
@@ -35680,7 +35680,7 @@
         <v>20</v>
       </c>
       <c r="H932" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I932" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>8926.4</v>
+        <v>8883.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -11639,7 +11639,7 @@
         <v>20</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>21</v>
@@ -13350,7 +13350,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -13814,7 +13814,7 @@
         <v>20</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>21</v>
@@ -14278,7 +14278,7 @@
         <v>391</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I194" s="0" t="s">
         <v>21</v>
@@ -14307,7 +14307,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14336,7 +14336,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14365,7 +14365,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14394,7 +14394,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -15641,7 +15641,7 @@
         <v>20</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I241" s="0" t="s">
         <v>21</v>
@@ -17091,7 +17091,7 @@
         <v>20</v>
       </c>
       <c r="H291" s="3" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I291" s="0" t="s">
         <v>21</v>
@@ -18309,7 +18309,7 @@
         <v>391</v>
       </c>
       <c r="H333" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I333" s="0" t="s">
         <v>21</v>
@@ -18338,7 +18338,7 @@
         <v>391</v>
       </c>
       <c r="H334" s="3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I334" s="0" t="s">
         <v>21</v>
@@ -18367,7 +18367,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18396,7 +18396,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18425,7 +18425,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18454,7 +18454,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -19179,7 +19179,7 @@
         <v>391</v>
       </c>
       <c r="H363" s="3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I363" s="0" t="s">
         <v>21</v>
@@ -19208,7 +19208,7 @@
         <v>391</v>
       </c>
       <c r="H364" s="3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I364" s="0" t="s">
         <v>21</v>
@@ -19237,7 +19237,7 @@
         <v>391</v>
       </c>
       <c r="H365" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I365" s="0" t="s">
         <v>21</v>
@@ -19295,7 +19295,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19440,7 +19440,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19469,7 +19469,7 @@
         <v>391</v>
       </c>
       <c r="H373" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I373" s="0" t="s">
         <v>21</v>
@@ -19498,7 +19498,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -20571,7 +20571,7 @@
         <v>20</v>
       </c>
       <c r="H411" s="3" t="n">
-        <v>-294</v>
+        <v>-296</v>
       </c>
       <c r="I411" s="0" t="s">
         <v>21</v>
@@ -20716,7 +20716,7 @@
         <v>844</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -21093,7 +21093,7 @@
         <v>391</v>
       </c>
       <c r="H429" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I429" s="0" t="s">
         <v>21</v>
@@ -21151,7 +21151,7 @@
         <v>391</v>
       </c>
       <c r="H431" s="3" t="n">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="I431" s="0" t="s">
         <v>21</v>
@@ -21760,7 +21760,7 @@
         <v>391</v>
       </c>
       <c r="H452" s="3" t="n">
-        <v>-6197.6</v>
+        <v>-6213.6</v>
       </c>
       <c r="I452" s="0" t="s">
         <v>21</v>
@@ -21789,7 +21789,7 @@
         <v>20</v>
       </c>
       <c r="H453" s="3" t="n">
-        <v>-457</v>
+        <v>-459</v>
       </c>
       <c r="I453" s="0" t="s">
         <v>21</v>
@@ -21934,7 +21934,7 @@
         <v>391</v>
       </c>
       <c r="H458" s="3" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I458" s="0" t="s">
         <v>21</v>
@@ -21992,7 +21992,7 @@
         <v>391</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22050,7 +22050,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -22108,7 +22108,7 @@
         <v>391</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>21</v>
@@ -22456,7 +22456,7 @@
         <v>391</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22485,7 +22485,7 @@
         <v>391</v>
       </c>
       <c r="H477" s="3" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I477" s="0" t="s">
         <v>21</v>
@@ -22862,7 +22862,7 @@
         <v>391</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="I490" s="0" t="s">
         <v>21</v>
@@ -23210,7 +23210,7 @@
         <v>391</v>
       </c>
       <c r="H502" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I502" s="0" t="s">
         <v>21</v>
@@ -23239,7 +23239,7 @@
         <v>391</v>
       </c>
       <c r="H503" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I503" s="0" t="s">
         <v>21</v>
@@ -23297,7 +23297,7 @@
         <v>391</v>
       </c>
       <c r="H505" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I505" s="0" t="s">
         <v>21</v>
@@ -23355,7 +23355,7 @@
         <v>391</v>
       </c>
       <c r="H507" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I507" s="0" t="s">
         <v>21</v>
@@ -23558,7 +23558,7 @@
         <v>391</v>
       </c>
       <c r="H514" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I514" s="0" t="s">
         <v>21</v>
@@ -23674,7 +23674,7 @@
         <v>391</v>
       </c>
       <c r="H518" s="3" t="n">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="I518" s="0" t="s">
         <v>21</v>
@@ -23703,7 +23703,7 @@
         <v>391</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I519" s="0" t="s">
         <v>21</v>
@@ -24544,7 +24544,7 @@
         <v>391</v>
       </c>
       <c r="H548" s="3" t="n">
-        <v>700</v>
+        <v>675</v>
       </c>
       <c r="I548" s="0" t="s">
         <v>21</v>
@@ -24660,7 +24660,7 @@
         <v>391</v>
       </c>
       <c r="H552" s="3" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I552" s="0" t="s">
         <v>21</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25965,7 +25965,7 @@
         <v>391</v>
       </c>
       <c r="H597" s="3" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="I597" s="0" t="s">
         <v>21</v>
@@ -26226,7 +26226,7 @@
         <v>391</v>
       </c>
       <c r="H606" s="3" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I606" s="0" t="s">
         <v>21</v>
@@ -26458,7 +26458,7 @@
         <v>391</v>
       </c>
       <c r="H614" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I614" s="0" t="s">
         <v>21</v>
@@ -27038,7 +27038,7 @@
         <v>391</v>
       </c>
       <c r="H634" s="3" t="n">
-        <v>-67</v>
+        <v>-69</v>
       </c>
       <c r="I634" s="0" t="s">
         <v>21</v>
@@ -27067,7 +27067,7 @@
         <v>391</v>
       </c>
       <c r="H635" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I635" s="0" t="s">
         <v>21</v>
@@ -27705,7 +27705,7 @@
         <v>391</v>
       </c>
       <c r="H657" s="3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I657" s="0" t="s">
         <v>21</v>
@@ -28372,7 +28372,7 @@
         <v>391</v>
       </c>
       <c r="H680" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I680" s="0" t="s">
         <v>21</v>
@@ -28720,7 +28720,7 @@
         <v>844</v>
       </c>
       <c r="H692" s="3" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I692" s="0" t="s">
         <v>21</v>
@@ -28749,7 +28749,7 @@
         <v>844</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I693" s="0" t="s">
         <v>21</v>
@@ -28807,7 +28807,7 @@
         <v>844</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -29068,7 +29068,7 @@
         <v>391</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -29880,7 +29880,7 @@
         <v>391</v>
       </c>
       <c r="H732" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I732" s="0" t="s">
         <v>21</v>
@@ -30286,7 +30286,7 @@
         <v>844</v>
       </c>
       <c r="H746" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I746" s="0" t="s">
         <v>21</v>
@@ -31098,7 +31098,7 @@
         <v>391</v>
       </c>
       <c r="H774" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I774" s="0" t="s">
         <v>21</v>
@@ -31214,7 +31214,7 @@
         <v>391</v>
       </c>
       <c r="H778" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I778" s="0" t="s">
         <v>21</v>
@@ -31562,7 +31562,7 @@
         <v>391</v>
       </c>
       <c r="H790" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I790" s="0" t="s">
         <v>21</v>
@@ -32461,7 +32461,7 @@
         <v>391</v>
       </c>
       <c r="H821" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I821" s="0" t="s">
         <v>21</v>
@@ -33012,7 +33012,7 @@
         <v>20</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-796</v>
+        <v>-800</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -34114,7 +34114,7 @@
         <v>391</v>
       </c>
       <c r="H878" s="3" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I878" s="0" t="s">
         <v>21</v>
@@ -35535,7 +35535,7 @@
         <v>391</v>
       </c>
       <c r="H927" s="3" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I927" s="0" t="s">
         <v>21</v>
@@ -35825,7 +35825,7 @@
         <v>391</v>
       </c>
       <c r="H937" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I937" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>8883.4</v>
+        <v>8634.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>14 September 2026</t>
+    <t>15 September 2026</t>
   </si>
   <si>
     <t>To</t>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -8971,7 +8971,7 @@
         <v>20</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="0" t="s">
         <v>21</v>
@@ -9232,7 +9232,7 @@
         <v>20</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I20" s="0" t="s">
         <v>21</v>
@@ -9319,7 +9319,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -9348,7 +9348,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -9667,7 +9667,7 @@
         <v>20</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" s="0" t="s">
         <v>21</v>
@@ -10073,7 +10073,7 @@
         <v>20</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I49" s="0" t="s">
         <v>21</v>
@@ -10798,7 +10798,7 @@
         <v>20</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" s="0" t="s">
         <v>21</v>
@@ -10856,7 +10856,7 @@
         <v>20</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I76" s="0" t="s">
         <v>21</v>
@@ -12045,7 +12045,7 @@
         <v>20</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I117" s="0" t="s">
         <v>21</v>
@@ -12103,7 +12103,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12306,7 +12306,7 @@
         <v>20</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I126" s="0" t="s">
         <v>21</v>
@@ -13089,7 +13089,7 @@
         <v>20</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I153" s="0" t="s">
         <v>21</v>
@@ -13350,7 +13350,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -13756,7 +13756,7 @@
         <v>20</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I176" s="0" t="s">
         <v>21</v>
@@ -15380,7 +15380,7 @@
         <v>20</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I232" s="0" t="s">
         <v>21</v>
@@ -15641,7 +15641,7 @@
         <v>20</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I241" s="0" t="s">
         <v>21</v>
@@ -18396,7 +18396,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18860,7 +18860,7 @@
         <v>391</v>
       </c>
       <c r="H352" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I352" s="0" t="s">
         <v>21</v>
@@ -19817,7 +19817,7 @@
         <v>20</v>
       </c>
       <c r="H385" s="3" t="n">
-        <v>-201</v>
+        <v>-203</v>
       </c>
       <c r="I385" s="0" t="s">
         <v>21</v>
@@ -19933,7 +19933,7 @@
         <v>20</v>
       </c>
       <c r="H389" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I389" s="0" t="s">
         <v>21</v>
@@ -19991,7 +19991,7 @@
         <v>20</v>
       </c>
       <c r="H391" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I391" s="0" t="s">
         <v>21</v>
@@ -20107,7 +20107,7 @@
         <v>20</v>
       </c>
       <c r="H395" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I395" s="0" t="s">
         <v>21</v>
@@ -20658,7 +20658,7 @@
         <v>391</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I414" s="0" t="s">
         <v>21</v>
@@ -20716,7 +20716,7 @@
         <v>844</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -21789,7 +21789,7 @@
         <v>20</v>
       </c>
       <c r="H453" s="3" t="n">
-        <v>-459</v>
+        <v>-461</v>
       </c>
       <c r="I453" s="0" t="s">
         <v>21</v>
@@ -21992,7 +21992,7 @@
         <v>391</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22195,7 +22195,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22688,7 +22688,7 @@
         <v>391</v>
       </c>
       <c r="H484" s="3" t="n">
-        <v>-372</v>
+        <v>-377</v>
       </c>
       <c r="I484" s="0" t="s">
         <v>21</v>
@@ -23239,7 +23239,7 @@
         <v>391</v>
       </c>
       <c r="H503" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I503" s="0" t="s">
         <v>21</v>
@@ -23297,7 +23297,7 @@
         <v>391</v>
       </c>
       <c r="H505" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I505" s="0" t="s">
         <v>21</v>
@@ -24979,7 +24979,7 @@
         <v>20</v>
       </c>
       <c r="H563" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I563" s="0" t="s">
         <v>21</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -27067,7 +27067,7 @@
         <v>391</v>
       </c>
       <c r="H635" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I635" s="0" t="s">
         <v>21</v>
@@ -28749,7 +28749,7 @@
         <v>844</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I693" s="0" t="s">
         <v>21</v>
@@ -28807,7 +28807,7 @@
         <v>844</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -29880,7 +29880,7 @@
         <v>391</v>
       </c>
       <c r="H732" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I732" s="0" t="s">
         <v>21</v>
@@ -32768,7 +32768,7 @@
         <v>1682</v>
       </c>
       <c r="D832" s="3" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="E832" s="3" t="n">
         <v>1000</v>
@@ -33012,7 +33012,7 @@
         <v>20</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-800</v>
+        <v>-803</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -34346,7 +34346,7 @@
         <v>391</v>
       </c>
       <c r="H886" s="3" t="n">
-        <v>-124</v>
+        <v>-129</v>
       </c>
       <c r="I886" s="0" t="s">
         <v>21</v>
@@ -35535,7 +35535,7 @@
         <v>391</v>
       </c>
       <c r="H927" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I927" s="0" t="s">
         <v>21</v>
@@ -35622,7 +35622,7 @@
         <v>20</v>
       </c>
       <c r="H930" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I930" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>8634.4</v>
+        <v>8556.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -13901,7 +13901,7 @@
         <v>20</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I181" s="0" t="s">
         <v>21</v>
@@ -14307,7 +14307,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14336,7 +14336,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -15902,7 +15902,7 @@
         <v>20</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I250" s="0" t="s">
         <v>21</v>
@@ -18338,7 +18338,7 @@
         <v>391</v>
       </c>
       <c r="H334" s="3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I334" s="0" t="s">
         <v>21</v>
@@ -18454,7 +18454,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18918,7 +18918,7 @@
         <v>391</v>
       </c>
       <c r="H354" s="3" t="n">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="I354" s="0" t="s">
         <v>21</v>
@@ -20136,7 +20136,7 @@
         <v>20</v>
       </c>
       <c r="H396" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I396" s="0" t="s">
         <v>21</v>
@@ -20716,7 +20716,7 @@
         <v>844</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -21093,7 +21093,7 @@
         <v>391</v>
       </c>
       <c r="H429" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I429" s="0" t="s">
         <v>21</v>
@@ -21151,7 +21151,7 @@
         <v>391</v>
       </c>
       <c r="H431" s="3" t="n">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="I431" s="0" t="s">
         <v>21</v>
@@ -21760,7 +21760,7 @@
         <v>391</v>
       </c>
       <c r="H452" s="3" t="n">
-        <v>-6213.6</v>
+        <v>-6224.6</v>
       </c>
       <c r="I452" s="0" t="s">
         <v>21</v>
@@ -21963,7 +21963,7 @@
         <v>391</v>
       </c>
       <c r="H459" s="3" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I459" s="0" t="s">
         <v>21</v>
@@ -21992,7 +21992,7 @@
         <v>391</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>133</v>
+        <v>433</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22166,7 +22166,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22195,7 +22195,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22485,7 +22485,7 @@
         <v>391</v>
       </c>
       <c r="H477" s="3" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I477" s="0" t="s">
         <v>21</v>
@@ -22688,7 +22688,7 @@
         <v>391</v>
       </c>
       <c r="H484" s="3" t="n">
-        <v>-377</v>
+        <v>-387</v>
       </c>
       <c r="I484" s="0" t="s">
         <v>21</v>
@@ -22920,7 +22920,7 @@
         <v>391</v>
       </c>
       <c r="H492" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I492" s="0" t="s">
         <v>21</v>
@@ -23355,7 +23355,7 @@
         <v>391</v>
       </c>
       <c r="H507" s="3" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I507" s="0" t="s">
         <v>21</v>
@@ -23558,7 +23558,7 @@
         <v>391</v>
       </c>
       <c r="H514" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I514" s="0" t="s">
         <v>21</v>
@@ -23674,7 +23674,7 @@
         <v>391</v>
       </c>
       <c r="H518" s="3" t="n">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="I518" s="0" t="s">
         <v>21</v>
@@ -23703,7 +23703,7 @@
         <v>391</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I519" s="0" t="s">
         <v>21</v>
@@ -25124,7 +25124,7 @@
         <v>20</v>
       </c>
       <c r="H568" s="3" t="n">
-        <v>-308</v>
+        <v>-309</v>
       </c>
       <c r="I568" s="0" t="s">
         <v>21</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25327,7 +25327,7 @@
         <v>391</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -26458,7 +26458,7 @@
         <v>391</v>
       </c>
       <c r="H614" s="3" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="I614" s="0" t="s">
         <v>21</v>
@@ -28140,7 +28140,7 @@
         <v>391</v>
       </c>
       <c r="H672" s="3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I672" s="0" t="s">
         <v>21</v>
@@ -28198,7 +28198,7 @@
         <v>391</v>
       </c>
       <c r="H674" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I674" s="0" t="s">
         <v>21</v>
@@ -28227,7 +28227,7 @@
         <v>391</v>
       </c>
       <c r="H675" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I675" s="0" t="s">
         <v>21</v>
@@ -28256,7 +28256,7 @@
         <v>391</v>
       </c>
       <c r="H676" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I676" s="0" t="s">
         <v>21</v>
@@ -28285,7 +28285,7 @@
         <v>391</v>
       </c>
       <c r="H677" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I677" s="0" t="s">
         <v>21</v>
@@ -28314,7 +28314,7 @@
         <v>391</v>
       </c>
       <c r="H678" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I678" s="0" t="s">
         <v>21</v>
@@ -28372,7 +28372,7 @@
         <v>391</v>
       </c>
       <c r="H680" s="3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I680" s="0" t="s">
         <v>21</v>
@@ -28604,7 +28604,7 @@
         <v>391</v>
       </c>
       <c r="H688" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I688" s="0" t="s">
         <v>21</v>
@@ -28720,7 +28720,7 @@
         <v>844</v>
       </c>
       <c r="H692" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I692" s="0" t="s">
         <v>21</v>
@@ -28749,7 +28749,7 @@
         <v>844</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I693" s="0" t="s">
         <v>21</v>
@@ -28807,7 +28807,7 @@
         <v>844</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -28952,7 +28952,7 @@
         <v>391</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29909,7 +29909,7 @@
         <v>391</v>
       </c>
       <c r="H733" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I733" s="0" t="s">
         <v>21</v>
@@ -29938,7 +29938,7 @@
         <v>391</v>
       </c>
       <c r="H734" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I734" s="0" t="s">
         <v>21</v>
@@ -30286,7 +30286,7 @@
         <v>844</v>
       </c>
       <c r="H746" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I746" s="0" t="s">
         <v>21</v>
@@ -31533,7 +31533,7 @@
         <v>391</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I789" s="0" t="s">
         <v>21</v>
@@ -32229,7 +32229,7 @@
         <v>391</v>
       </c>
       <c r="H813" s="3" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="I813" s="0" t="s">
         <v>21</v>
@@ -32780,7 +32780,7 @@
         <v>391</v>
       </c>
       <c r="H832" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I832" s="0" t="s">
         <v>21</v>
@@ -34027,7 +34027,7 @@
         <v>391</v>
       </c>
       <c r="H875" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I875" s="0" t="s">
         <v>21</v>
@@ -34056,7 +34056,7 @@
         <v>391</v>
       </c>
       <c r="H876" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I876" s="0" t="s">
         <v>21</v>
@@ -34433,7 +34433,7 @@
         <v>391</v>
       </c>
       <c r="H889" s="3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I889" s="0" t="s">
         <v>21</v>
@@ -35535,7 +35535,7 @@
         <v>391</v>
       </c>
       <c r="H927" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I927" s="0" t="s">
         <v>21</v>
@@ -35825,7 +35825,7 @@
         <v>391</v>
       </c>
       <c r="H937" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I937" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>8556.4</v>
+        <v>9532.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>15 September 2026</t>
+    <t>16 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12770,7 +12770,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9532.4</v>
+        <v>9531.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -10334,7 +10334,7 @@
         <v>20</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I58" s="0" t="s">
         <v>21</v>
@@ -10856,7 +10856,7 @@
         <v>20</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I76" s="0" t="s">
         <v>21</v>
@@ -10943,7 +10943,7 @@
         <v>20</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I79" s="0" t="s">
         <v>21</v>
@@ -12103,7 +12103,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12132,7 +12132,7 @@
         <v>20</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I120" s="0" t="s">
         <v>21</v>
@@ -12277,7 +12277,7 @@
         <v>20</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I125" s="0" t="s">
         <v>21</v>
@@ -12712,7 +12712,7 @@
         <v>20</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I140" s="0" t="s">
         <v>21</v>
@@ -12770,7 +12770,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -12799,7 +12799,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13060,7 +13060,7 @@
         <v>20</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I152" s="0" t="s">
         <v>21</v>
@@ -13234,7 +13234,7 @@
         <v>20</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I158" s="0" t="s">
         <v>21</v>
@@ -13350,7 +13350,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -13756,7 +13756,7 @@
         <v>20</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I176" s="0" t="s">
         <v>21</v>
@@ -13814,7 +13814,7 @@
         <v>20</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>21</v>
@@ -13901,7 +13901,7 @@
         <v>20</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I181" s="0" t="s">
         <v>21</v>
@@ -14220,7 +14220,7 @@
         <v>20</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I192" s="0" t="s">
         <v>21</v>
@@ -14336,7 +14336,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14394,7 +14394,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -17091,7 +17091,7 @@
         <v>20</v>
       </c>
       <c r="H291" s="3" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I291" s="0" t="s">
         <v>21</v>
@@ -19933,7 +19933,7 @@
         <v>20</v>
       </c>
       <c r="H389" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I389" s="0" t="s">
         <v>21</v>
@@ -19962,7 +19962,7 @@
         <v>20</v>
       </c>
       <c r="H390" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I390" s="0" t="s">
         <v>21</v>
@@ -19991,7 +19991,7 @@
         <v>20</v>
       </c>
       <c r="H391" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I391" s="0" t="s">
         <v>21</v>
@@ -20252,7 +20252,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -21789,7 +21789,7 @@
         <v>20</v>
       </c>
       <c r="H453" s="3" t="n">
-        <v>-461</v>
+        <v>-463</v>
       </c>
       <c r="I453" s="0" t="s">
         <v>21</v>
@@ -22108,7 +22108,7 @@
         <v>391</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>21</v>
@@ -24834,7 +24834,7 @@
         <v>20</v>
       </c>
       <c r="H558" s="3" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="I558" s="0" t="s">
         <v>21</v>
@@ -25182,7 +25182,7 @@
         <v>20</v>
       </c>
       <c r="H570" s="3" t="n">
-        <v>-727</v>
+        <v>-729</v>
       </c>
       <c r="I570" s="0" t="s">
         <v>21</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -30286,7 +30286,7 @@
         <v>844</v>
       </c>
       <c r="H746" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I746" s="0" t="s">
         <v>21</v>
@@ -31127,7 +31127,7 @@
         <v>391</v>
       </c>
       <c r="H775" s="3" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I775" s="0" t="s">
         <v>21</v>
@@ -31214,7 +31214,7 @@
         <v>391</v>
       </c>
       <c r="H778" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I778" s="0" t="s">
         <v>21</v>
@@ -33012,7 +33012,7 @@
         <v>20</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-803</v>
+        <v>-806</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9531.4</v>
+        <v>9481.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9029,7 +9029,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I13" s="0" t="s">
         <v>21</v>
@@ -12886,7 +12886,7 @@
         <v>20</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>21</v>
@@ -13176,7 +13176,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -14336,7 +14336,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14365,7 +14365,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -18338,7 +18338,7 @@
         <v>391</v>
       </c>
       <c r="H334" s="3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I334" s="0" t="s">
         <v>21</v>
@@ -18367,7 +18367,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18396,7 +18396,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18425,7 +18425,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18454,7 +18454,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18483,7 +18483,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -19179,7 +19179,7 @@
         <v>391</v>
       </c>
       <c r="H363" s="3" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="I363" s="0" t="s">
         <v>21</v>
@@ -19208,7 +19208,7 @@
         <v>391</v>
       </c>
       <c r="H364" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I364" s="0" t="s">
         <v>21</v>
@@ -19237,7 +19237,7 @@
         <v>391</v>
       </c>
       <c r="H365" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I365" s="0" t="s">
         <v>21</v>
@@ -19411,7 +19411,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19440,7 +19440,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19498,7 +19498,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -20716,7 +20716,7 @@
         <v>844</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -21354,7 +21354,7 @@
         <v>391</v>
       </c>
       <c r="H438" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I438" s="0" t="s">
         <v>21</v>
@@ -21760,7 +21760,7 @@
         <v>391</v>
       </c>
       <c r="H452" s="3" t="n">
-        <v>-6224.6</v>
+        <v>-6249.2</v>
       </c>
       <c r="I452" s="0" t="s">
         <v>21</v>
@@ -21934,7 +21934,7 @@
         <v>391</v>
       </c>
       <c r="H458" s="3" t="n">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="I458" s="0" t="s">
         <v>21</v>
@@ -22050,7 +22050,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -22079,7 +22079,7 @@
         <v>391</v>
       </c>
       <c r="H463" s="3" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I463" s="0" t="s">
         <v>21</v>
@@ -22108,7 +22108,7 @@
         <v>391</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>21</v>
@@ -22166,7 +22166,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22398,7 +22398,7 @@
         <v>391</v>
       </c>
       <c r="H474" s="3" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I474" s="0" t="s">
         <v>21</v>
@@ -22485,7 +22485,7 @@
         <v>391</v>
       </c>
       <c r="H477" s="3" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I477" s="0" t="s">
         <v>21</v>
@@ -22804,7 +22804,7 @@
         <v>391</v>
       </c>
       <c r="H488" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I488" s="0" t="s">
         <v>21</v>
@@ -23297,7 +23297,7 @@
         <v>391</v>
       </c>
       <c r="H505" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I505" s="0" t="s">
         <v>21</v>
@@ -23558,7 +23558,7 @@
         <v>391</v>
       </c>
       <c r="H514" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I514" s="0" t="s">
         <v>21</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -26168,7 +26168,7 @@
         <v>391</v>
       </c>
       <c r="H604" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I604" s="0" t="s">
         <v>21</v>
@@ -27038,7 +27038,7 @@
         <v>391</v>
       </c>
       <c r="H634" s="3" t="n">
-        <v>-69</v>
+        <v>-70</v>
       </c>
       <c r="I634" s="0" t="s">
         <v>21</v>
@@ -27067,7 +27067,7 @@
         <v>391</v>
       </c>
       <c r="H635" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I635" s="0" t="s">
         <v>21</v>
@@ -27705,7 +27705,7 @@
         <v>391</v>
       </c>
       <c r="H657" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I657" s="0" t="s">
         <v>21</v>
@@ -27763,7 +27763,7 @@
         <v>391</v>
       </c>
       <c r="H659" s="3" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="I659" s="0" t="s">
         <v>21</v>
@@ -28140,7 +28140,7 @@
         <v>391</v>
       </c>
       <c r="H672" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I672" s="0" t="s">
         <v>21</v>
@@ -28720,7 +28720,7 @@
         <v>844</v>
       </c>
       <c r="H692" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I692" s="0" t="s">
         <v>21</v>
@@ -28749,7 +28749,7 @@
         <v>844</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I693" s="0" t="s">
         <v>21</v>
@@ -29068,7 +29068,7 @@
         <v>391</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -29880,7 +29880,7 @@
         <v>391</v>
       </c>
       <c r="H732" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I732" s="0" t="s">
         <v>21</v>
@@ -29938,7 +29938,7 @@
         <v>391</v>
       </c>
       <c r="H734" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I734" s="0" t="s">
         <v>21</v>
@@ -30576,7 +30576,7 @@
         <v>391</v>
       </c>
       <c r="H756" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I756" s="0" t="s">
         <v>21</v>
@@ -30634,7 +30634,7 @@
         <v>391</v>
       </c>
       <c r="H758" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I758" s="0" t="s">
         <v>21</v>
@@ -31098,7 +31098,7 @@
         <v>391</v>
       </c>
       <c r="H774" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I774" s="0" t="s">
         <v>21</v>
@@ -31127,7 +31127,7 @@
         <v>391</v>
       </c>
       <c r="H775" s="3" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I775" s="0" t="s">
         <v>21</v>
@@ -31330,7 +31330,7 @@
         <v>391</v>
       </c>
       <c r="H782" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I782" s="0" t="s">
         <v>21</v>
@@ -31533,7 +31533,7 @@
         <v>391</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I789" s="0" t="s">
         <v>21</v>
@@ -31910,7 +31910,7 @@
         <v>391</v>
       </c>
       <c r="H802" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I802" s="0" t="s">
         <v>830</v>
@@ -32258,7 +32258,7 @@
         <v>391</v>
       </c>
       <c r="H814" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I814" s="0" t="s">
         <v>21</v>
@@ -32374,7 +32374,7 @@
         <v>391</v>
       </c>
       <c r="H818" s="3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I818" s="0" t="s">
         <v>21</v>
@@ -32461,7 +32461,7 @@
         <v>391</v>
       </c>
       <c r="H821" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I821" s="0" t="s">
         <v>21</v>
@@ -32809,7 +32809,7 @@
         <v>391</v>
       </c>
       <c r="H833" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I833" s="0" t="s">
         <v>21</v>
@@ -34433,7 +34433,7 @@
         <v>391</v>
       </c>
       <c r="H889" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I889" s="0" t="s">
         <v>21</v>
@@ -35535,7 +35535,7 @@
         <v>391</v>
       </c>
       <c r="H927" s="3" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I927" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9481.4</v>
+        <v>9288.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>16 September 2026</t>
+    <t>17 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12770,7 +12770,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -15844,7 +15844,7 @@
         <v>20</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I248" s="0" t="s">
         <v>21</v>
@@ -16308,7 +16308,7 @@
         <v>20</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I264" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9288.8</v>
+        <v>9285.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -8942,7 +8942,7 @@
         <v>20</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I10" s="0" t="s">
         <v>21</v>
@@ -10073,7 +10073,7 @@
         <v>20</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I49" s="0" t="s">
         <v>21</v>
@@ -10334,7 +10334,7 @@
         <v>20</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I58" s="0" t="s">
         <v>21</v>
@@ -10450,7 +10450,7 @@
         <v>20</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I62" s="0" t="s">
         <v>21</v>
@@ -10943,7 +10943,7 @@
         <v>20</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" s="0" t="s">
         <v>21</v>
@@ -11668,7 +11668,7 @@
         <v>20</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I104" s="0" t="s">
         <v>21</v>
@@ -11697,7 +11697,7 @@
         <v>20</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I105" s="0" t="s">
         <v>21</v>
@@ -11900,7 +11900,7 @@
         <v>20</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I112" s="0" t="s">
         <v>21</v>
@@ -11987,7 +11987,7 @@
         <v>20</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>21</v>
@@ -12045,7 +12045,7 @@
         <v>20</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I117" s="0" t="s">
         <v>21</v>
@@ -12306,7 +12306,7 @@
         <v>20</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I126" s="0" t="s">
         <v>21</v>
@@ -12654,7 +12654,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -13234,7 +13234,7 @@
         <v>20</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I158" s="0" t="s">
         <v>21</v>
@@ -13350,7 +13350,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -13437,7 +13437,7 @@
         <v>20</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I165" s="0" t="s">
         <v>21</v>
@@ -13466,7 +13466,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -13756,7 +13756,7 @@
         <v>20</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I176" s="0" t="s">
         <v>21</v>
@@ -13814,7 +13814,7 @@
         <v>20</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>21</v>
@@ -14104,7 +14104,7 @@
         <v>20</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="I188" s="0" t="s">
         <v>21</v>
@@ -14220,7 +14220,7 @@
         <v>20</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I192" s="0" t="s">
         <v>21</v>
@@ -14655,7 +14655,7 @@
         <v>20</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I207" s="0" t="s">
         <v>21</v>
@@ -15728,7 +15728,7 @@
         <v>20</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I244" s="0" t="s">
         <v>21</v>
@@ -15844,7 +15844,7 @@
         <v>20</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I248" s="0" t="s">
         <v>21</v>
@@ -15873,7 +15873,7 @@
         <v>20</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I249" s="0" t="s">
         <v>21</v>
@@ -16598,7 +16598,7 @@
         <v>20</v>
       </c>
       <c r="H274" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I274" s="0" t="s">
         <v>21</v>
@@ -16627,7 +16627,7 @@
         <v>20</v>
       </c>
       <c r="H275" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I275" s="0" t="s">
         <v>21</v>
@@ -17091,7 +17091,7 @@
         <v>20</v>
       </c>
       <c r="H291" s="3" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I291" s="0" t="s">
         <v>21</v>
@@ -17120,7 +17120,7 @@
         <v>20</v>
       </c>
       <c r="H292" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I292" s="0" t="s">
         <v>21</v>
@@ -17642,7 +17642,7 @@
         <v>20</v>
       </c>
       <c r="H310" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I310" s="0" t="s">
         <v>21</v>
@@ -18396,7 +18396,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18425,7 +18425,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18454,7 +18454,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -19991,7 +19991,7 @@
         <v>20</v>
       </c>
       <c r="H391" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I391" s="0" t="s">
         <v>21</v>
@@ -20252,7 +20252,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -21180,7 +21180,7 @@
         <v>391</v>
       </c>
       <c r="H432" s="3" t="n">
-        <v>-5</v>
+        <v>45</v>
       </c>
       <c r="I432" s="0" t="s">
         <v>21</v>
@@ -21789,7 +21789,7 @@
         <v>20</v>
       </c>
       <c r="H453" s="3" t="n">
-        <v>-463</v>
+        <v>-465</v>
       </c>
       <c r="I453" s="0" t="s">
         <v>21</v>
@@ -22543,7 +22543,7 @@
         <v>391</v>
       </c>
       <c r="H479" s="3" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="I479" s="0" t="s">
         <v>21</v>
@@ -25182,7 +25182,7 @@
         <v>20</v>
       </c>
       <c r="H570" s="3" t="n">
-        <v>-729</v>
+        <v>-731</v>
       </c>
       <c r="I570" s="0" t="s">
         <v>21</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -31533,7 +31533,7 @@
         <v>391</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I789" s="0" t="s">
         <v>21</v>
@@ -33012,7 +33012,7 @@
         <v>20</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-806</v>
+        <v>-810</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -33940,7 +33940,7 @@
         <v>391</v>
       </c>
       <c r="H872" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I872" s="0" t="s">
         <v>21</v>
@@ -34636,7 +34636,7 @@
         <v>391</v>
       </c>
       <c r="H896" s="3" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="I896" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9285.8</v>
+        <v>9542.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9029,7 +9029,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I13" s="0" t="s">
         <v>21</v>
@@ -9290,7 +9290,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I22" s="0" t="s">
         <v>21</v>
@@ -11668,7 +11668,7 @@
         <v>20</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I104" s="0" t="s">
         <v>21</v>
@@ -11697,7 +11697,7 @@
         <v>20</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I105" s="0" t="s">
         <v>21</v>
@@ -11755,7 +11755,7 @@
         <v>20</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I107" s="0" t="s">
         <v>21</v>
@@ -14307,7 +14307,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14336,7 +14336,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14394,7 +14394,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -18309,7 +18309,7 @@
         <v>391</v>
       </c>
       <c r="H333" s="3" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I333" s="0" t="s">
         <v>21</v>
@@ -18396,7 +18396,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18425,7 +18425,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18454,7 +18454,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18483,7 +18483,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -19179,7 +19179,7 @@
         <v>391</v>
       </c>
       <c r="H363" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I363" s="0" t="s">
         <v>21</v>
@@ -19208,7 +19208,7 @@
         <v>391</v>
       </c>
       <c r="H364" s="3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I364" s="0" t="s">
         <v>21</v>
@@ -19237,7 +19237,7 @@
         <v>391</v>
       </c>
       <c r="H365" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I365" s="0" t="s">
         <v>21</v>
@@ -19440,7 +19440,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -20252,7 +20252,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -20658,7 +20658,7 @@
         <v>391</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I414" s="0" t="s">
         <v>21</v>
@@ -20716,7 +20716,7 @@
         <v>844</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -21093,7 +21093,7 @@
         <v>391</v>
       </c>
       <c r="H429" s="3" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I429" s="0" t="s">
         <v>21</v>
@@ -21760,7 +21760,7 @@
         <v>391</v>
       </c>
       <c r="H452" s="3" t="n">
-        <v>-6249.2</v>
+        <v>-6259.2</v>
       </c>
       <c r="I452" s="0" t="s">
         <v>21</v>
@@ -21963,7 +21963,7 @@
         <v>391</v>
       </c>
       <c r="H459" s="3" t="n">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="I459" s="0" t="s">
         <v>21</v>
@@ -22166,7 +22166,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22398,7 +22398,7 @@
         <v>391</v>
       </c>
       <c r="H474" s="3" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I474" s="0" t="s">
         <v>21</v>
@@ -22485,7 +22485,7 @@
         <v>391</v>
       </c>
       <c r="H477" s="3" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I477" s="0" t="s">
         <v>21</v>
@@ -22717,7 +22717,7 @@
         <v>391</v>
       </c>
       <c r="H485" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I485" s="0" t="s">
         <v>21</v>
@@ -25791,7 +25791,7 @@
         <v>391</v>
       </c>
       <c r="H591" s="3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I591" s="0" t="s">
         <v>21</v>
@@ -25820,7 +25820,7 @@
         <v>391</v>
       </c>
       <c r="H592" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I592" s="0" t="s">
         <v>21</v>
@@ -26226,7 +26226,7 @@
         <v>391</v>
       </c>
       <c r="H606" s="3" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I606" s="0" t="s">
         <v>21</v>
@@ -28604,7 +28604,7 @@
         <v>391</v>
       </c>
       <c r="H688" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I688" s="0" t="s">
         <v>21</v>
@@ -28749,7 +28749,7 @@
         <v>844</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I693" s="0" t="s">
         <v>21</v>
@@ -29068,7 +29068,7 @@
         <v>391</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -29880,7 +29880,7 @@
         <v>391</v>
       </c>
       <c r="H732" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I732" s="0" t="s">
         <v>21</v>
@@ -29909,7 +29909,7 @@
         <v>391</v>
       </c>
       <c r="H733" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I733" s="0" t="s">
         <v>21</v>
@@ -29938,7 +29938,7 @@
         <v>391</v>
       </c>
       <c r="H734" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I734" s="0" t="s">
         <v>21</v>
@@ -30286,7 +30286,7 @@
         <v>844</v>
       </c>
       <c r="H746" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I746" s="0" t="s">
         <v>21</v>
@@ -30576,7 +30576,7 @@
         <v>391</v>
       </c>
       <c r="H756" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I756" s="0" t="s">
         <v>21</v>
@@ -31098,7 +31098,7 @@
         <v>391</v>
       </c>
       <c r="H774" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I774" s="0" t="s">
         <v>21</v>
@@ -31649,7 +31649,7 @@
         <v>391</v>
       </c>
       <c r="H793" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I793" s="0" t="s">
         <v>21</v>
@@ -34433,7 +34433,7 @@
         <v>391</v>
       </c>
       <c r="H889" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I889" s="0" t="s">
         <v>21</v>
@@ -35535,7 +35535,7 @@
         <v>391</v>
       </c>
       <c r="H927" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I927" s="0" t="s">
         <v>21</v>
@@ -35767,7 +35767,7 @@
         <v>391</v>
       </c>
       <c r="H935" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I935" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9542.8</v>
+        <v>9436.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>17 September 2026</t>
+    <t>18 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12770,7 +12770,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9436.8</v>
+        <v>9435.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9290,7 +9290,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I22" s="0" t="s">
         <v>21</v>
@@ -11204,7 +11204,7 @@
         <v>20</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I88" s="0" t="s">
         <v>21</v>
@@ -11987,7 +11987,7 @@
         <v>20</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>21</v>
@@ -12045,7 +12045,7 @@
         <v>20</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I117" s="0" t="s">
         <v>21</v>
@@ -12132,7 +12132,7 @@
         <v>20</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I120" s="0" t="s">
         <v>21</v>
@@ -12277,7 +12277,7 @@
         <v>20</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I125" s="0" t="s">
         <v>21</v>
@@ -12654,7 +12654,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -12770,7 +12770,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -12799,7 +12799,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13234,7 +13234,7 @@
         <v>20</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I158" s="0" t="s">
         <v>21</v>
@@ -13350,7 +13350,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -13466,7 +13466,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -15090,7 +15090,7 @@
         <v>20</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I222" s="0" t="s">
         <v>21</v>
@@ -15844,7 +15844,7 @@
         <v>20</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I248" s="0" t="s">
         <v>21</v>
@@ -17120,7 +17120,7 @@
         <v>20</v>
       </c>
       <c r="H292" s="3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I292" s="0" t="s">
         <v>21</v>
@@ -17642,7 +17642,7 @@
         <v>20</v>
       </c>
       <c r="H310" s="3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I310" s="0" t="s">
         <v>21</v>
@@ -18135,7 +18135,7 @@
         <v>20</v>
       </c>
       <c r="H327" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I327" s="0" t="s">
         <v>21</v>
@@ -18396,7 +18396,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -20107,7 +20107,7 @@
         <v>20</v>
       </c>
       <c r="H395" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I395" s="0" t="s">
         <v>21</v>
@@ -20194,7 +20194,7 @@
         <v>20</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I398" s="0" t="s">
         <v>21</v>
@@ -20310,7 +20310,7 @@
         <v>20</v>
       </c>
       <c r="H402" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I402" s="0" t="s">
         <v>21</v>
@@ -20716,7 +20716,7 @@
         <v>844</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -22050,7 +22050,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -25124,7 +25124,7 @@
         <v>20</v>
       </c>
       <c r="H568" s="3" t="n">
-        <v>-309</v>
+        <v>-310</v>
       </c>
       <c r="I568" s="0" t="s">
         <v>21</v>
@@ -25182,7 +25182,7 @@
         <v>20</v>
       </c>
       <c r="H570" s="3" t="n">
-        <v>-731</v>
+        <v>-732</v>
       </c>
       <c r="I570" s="0" t="s">
         <v>21</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -27067,7 +27067,7 @@
         <v>391</v>
       </c>
       <c r="H635" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I635" s="0" t="s">
         <v>21</v>
@@ -28720,7 +28720,7 @@
         <v>844</v>
       </c>
       <c r="H692" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I692" s="0" t="s">
         <v>21</v>
@@ -30286,7 +30286,7 @@
         <v>844</v>
       </c>
       <c r="H746" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I746" s="0" t="s">
         <v>21</v>
@@ -35622,7 +35622,7 @@
         <v>20</v>
       </c>
       <c r="H930" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I930" s="0" t="s">
         <v>21</v>
@@ -35680,7 +35680,7 @@
         <v>20</v>
       </c>
       <c r="H932" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I932" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9435.8</v>
+        <v>9376.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9029,7 +9029,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I13" s="0" t="s">
         <v>21</v>
@@ -9232,7 +9232,7 @@
         <v>20</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I20" s="0" t="s">
         <v>21</v>
@@ -10682,7 +10682,7 @@
         <v>20</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I70" s="0" t="s">
         <v>21</v>
@@ -10769,7 +10769,7 @@
         <v>20</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I73" s="0" t="s">
         <v>21</v>
@@ -10856,7 +10856,7 @@
         <v>20</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I76" s="0" t="s">
         <v>21</v>
@@ -12654,7 +12654,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -12799,7 +12799,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -18309,7 +18309,7 @@
         <v>391</v>
       </c>
       <c r="H333" s="3" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I333" s="0" t="s">
         <v>21</v>
@@ -18367,7 +18367,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18396,7 +18396,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18425,7 +18425,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18454,7 +18454,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -19179,7 +19179,7 @@
         <v>391</v>
       </c>
       <c r="H363" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I363" s="0" t="s">
         <v>21</v>
@@ -19208,7 +19208,7 @@
         <v>391</v>
       </c>
       <c r="H364" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I364" s="0" t="s">
         <v>21</v>
@@ -19237,7 +19237,7 @@
         <v>391</v>
       </c>
       <c r="H365" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I365" s="0" t="s">
         <v>21</v>
@@ -19411,7 +19411,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19440,7 +19440,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -20281,7 +20281,7 @@
         <v>20</v>
       </c>
       <c r="H401" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I401" s="0" t="s">
         <v>21</v>
@@ -20716,7 +20716,7 @@
         <v>844</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -21093,7 +21093,7 @@
         <v>391</v>
       </c>
       <c r="H429" s="3" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I429" s="0" t="s">
         <v>21</v>
@@ -21151,7 +21151,7 @@
         <v>391</v>
       </c>
       <c r="H431" s="3" t="n">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="I431" s="0" t="s">
         <v>21</v>
@@ -21760,7 +21760,7 @@
         <v>391</v>
       </c>
       <c r="H452" s="3" t="n">
-        <v>-6259.2</v>
+        <v>-6272.2</v>
       </c>
       <c r="I452" s="0" t="s">
         <v>21</v>
@@ -21789,7 +21789,7 @@
         <v>20</v>
       </c>
       <c r="H453" s="3" t="n">
-        <v>-465</v>
+        <v>-468</v>
       </c>
       <c r="I453" s="0" t="s">
         <v>21</v>
@@ -21905,7 +21905,7 @@
         <v>391</v>
       </c>
       <c r="H457" s="3" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I457" s="0" t="s">
         <v>21</v>
@@ -21934,7 +21934,7 @@
         <v>391</v>
       </c>
       <c r="H458" s="3" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="I458" s="0" t="s">
         <v>21</v>
@@ -21992,7 +21992,7 @@
         <v>391</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22079,7 +22079,7 @@
         <v>391</v>
       </c>
       <c r="H463" s="3" t="n">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="I463" s="0" t="s">
         <v>21</v>
@@ -22166,7 +22166,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22195,7 +22195,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22601,7 +22601,7 @@
         <v>391</v>
       </c>
       <c r="H481" s="3" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I481" s="0" t="s">
         <v>21</v>
@@ -23297,7 +23297,7 @@
         <v>391</v>
       </c>
       <c r="H505" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I505" s="0" t="s">
         <v>21</v>
@@ -23558,7 +23558,7 @@
         <v>391</v>
       </c>
       <c r="H514" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I514" s="0" t="s">
         <v>21</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25733,7 +25733,7 @@
         <v>391</v>
       </c>
       <c r="H589" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I589" s="0" t="s">
         <v>21</v>
@@ -26458,7 +26458,7 @@
         <v>391</v>
       </c>
       <c r="H614" s="3" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="I614" s="0" t="s">
         <v>21</v>
@@ -27067,7 +27067,7 @@
         <v>391</v>
       </c>
       <c r="H635" s="3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I635" s="0" t="s">
         <v>21</v>
@@ -28662,7 +28662,7 @@
         <v>391</v>
       </c>
       <c r="H690" s="3" t="n">
-        <v>-38</v>
+        <v>-43</v>
       </c>
       <c r="I690" s="0" t="s">
         <v>21</v>
@@ -28720,7 +28720,7 @@
         <v>844</v>
       </c>
       <c r="H692" s="3" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I692" s="0" t="s">
         <v>21</v>
@@ -29068,7 +29068,7 @@
         <v>391</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -29909,7 +29909,7 @@
         <v>391</v>
       </c>
       <c r="H733" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I733" s="0" t="s">
         <v>21</v>
@@ -30286,7 +30286,7 @@
         <v>844</v>
       </c>
       <c r="H746" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I746" s="0" t="s">
         <v>21</v>
@@ -31504,7 +31504,7 @@
         <v>391</v>
       </c>
       <c r="H788" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I788" s="0" t="s">
         <v>21</v>
@@ -31591,7 +31591,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -33012,7 +33012,7 @@
         <v>20</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-810</v>
+        <v>-813</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -35535,7 +35535,7 @@
         <v>391</v>
       </c>
       <c r="H927" s="3" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I927" s="0" t="s">
         <v>21</v>
@@ -35825,7 +35825,7 @@
         <v>391</v>
       </c>
       <c r="H937" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I937" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9376.8</v>
+        <v>9224.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>18 September 2026</t>
+    <t>19 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12770,7 +12770,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -16250,7 +16250,7 @@
         <v>20</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I262" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9224.8</v>
+        <v>9222.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9261,7 +9261,7 @@
         <v>20</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I21" s="0" t="s">
         <v>21</v>
@@ -9290,7 +9290,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I22" s="0" t="s">
         <v>21</v>
@@ -10682,7 +10682,7 @@
         <v>20</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" s="0" t="s">
         <v>21</v>
@@ -10856,7 +10856,7 @@
         <v>20</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I76" s="0" t="s">
         <v>21</v>
@@ -11204,7 +11204,7 @@
         <v>20</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I88" s="0" t="s">
         <v>21</v>
@@ -11349,7 +11349,7 @@
         <v>20</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I93" s="0" t="s">
         <v>21</v>
@@ -11900,7 +11900,7 @@
         <v>20</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I112" s="0" t="s">
         <v>21</v>
@@ -12103,7 +12103,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12654,7 +12654,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -12770,7 +12770,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -12799,7 +12799,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -12886,7 +12886,7 @@
         <v>20</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>21</v>
@@ -13814,7 +13814,7 @@
         <v>20</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>21</v>
@@ -14278,7 +14278,7 @@
         <v>391</v>
       </c>
       <c r="H194" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I194" s="0" t="s">
         <v>21</v>
@@ -14394,7 +14394,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -16221,7 +16221,7 @@
         <v>20</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I261" s="0" t="s">
         <v>21</v>
@@ -17120,7 +17120,7 @@
         <v>20</v>
       </c>
       <c r="H292" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I292" s="0" t="s">
         <v>21</v>
@@ -19208,7 +19208,7 @@
         <v>391</v>
       </c>
       <c r="H364" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I364" s="0" t="s">
         <v>21</v>
@@ -19962,7 +19962,7 @@
         <v>20</v>
       </c>
       <c r="H390" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I390" s="0" t="s">
         <v>21</v>
@@ -20165,7 +20165,7 @@
         <v>20</v>
       </c>
       <c r="H397" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I397" s="0" t="s">
         <v>21</v>
@@ -20281,7 +20281,7 @@
         <v>20</v>
       </c>
       <c r="H401" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I401" s="0" t="s">
         <v>21</v>
@@ -20716,7 +20716,7 @@
         <v>844</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -21789,7 +21789,7 @@
         <v>20</v>
       </c>
       <c r="H453" s="3" t="n">
-        <v>-468</v>
+        <v>-470</v>
       </c>
       <c r="I453" s="0" t="s">
         <v>21</v>
@@ -24979,7 +24979,7 @@
         <v>20</v>
       </c>
       <c r="H563" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I563" s="0" t="s">
         <v>21</v>
@@ -25153,7 +25153,7 @@
         <v>20</v>
       </c>
       <c r="H569" s="3" t="n">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="I569" s="0" t="s">
         <v>21</v>
@@ -25182,7 +25182,7 @@
         <v>20</v>
       </c>
       <c r="H570" s="3" t="n">
-        <v>-732</v>
+        <v>-735</v>
       </c>
       <c r="I570" s="0" t="s">
         <v>21</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -33012,7 +33012,7 @@
         <v>20</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-813</v>
+        <v>-817</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -34636,7 +34636,7 @@
         <v>391</v>
       </c>
       <c r="H896" s="3" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="I896" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9222.8</v>
+        <v>9187.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9232,7 +9232,7 @@
         <v>20</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I20" s="0" t="s">
         <v>21</v>
@@ -9609,7 +9609,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>21</v>
@@ -17091,7 +17091,7 @@
         <v>20</v>
       </c>
       <c r="H291" s="3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I291" s="0" t="s">
         <v>21</v>
@@ -18425,7 +18425,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18454,7 +18454,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18483,7 +18483,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -19179,7 +19179,7 @@
         <v>391</v>
       </c>
       <c r="H363" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I363" s="0" t="s">
         <v>21</v>
@@ -19208,7 +19208,7 @@
         <v>391</v>
       </c>
       <c r="H364" s="3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I364" s="0" t="s">
         <v>21</v>
@@ -19237,7 +19237,7 @@
         <v>391</v>
       </c>
       <c r="H365" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I365" s="0" t="s">
         <v>21</v>
@@ -19440,7 +19440,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19469,7 +19469,7 @@
         <v>391</v>
       </c>
       <c r="H373" s="3" t="n">
-        <v>-2</v>
+        <v>70</v>
       </c>
       <c r="I373" s="0" t="s">
         <v>21</v>
@@ -20658,7 +20658,7 @@
         <v>391</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I414" s="0" t="s">
         <v>21</v>
@@ -20716,7 +20716,7 @@
         <v>844</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -21093,7 +21093,7 @@
         <v>391</v>
       </c>
       <c r="H429" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I429" s="0" t="s">
         <v>21</v>
@@ -21151,7 +21151,7 @@
         <v>391</v>
       </c>
       <c r="H431" s="3" t="n">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="I431" s="0" t="s">
         <v>21</v>
@@ -21354,7 +21354,7 @@
         <v>391</v>
       </c>
       <c r="H438" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I438" s="0" t="s">
         <v>21</v>
@@ -21760,7 +21760,7 @@
         <v>391</v>
       </c>
       <c r="H452" s="3" t="n">
-        <v>-6272.2</v>
+        <v>-6279.2</v>
       </c>
       <c r="I452" s="0" t="s">
         <v>21</v>
@@ -22050,7 +22050,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -22079,7 +22079,7 @@
         <v>391</v>
       </c>
       <c r="H463" s="3" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="I463" s="0" t="s">
         <v>21</v>
@@ -22108,7 +22108,7 @@
         <v>391</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>21</v>
@@ -22166,7 +22166,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22311,7 +22311,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>1</v>
+        <v>301</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22340,7 +22340,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>54</v>
+        <v>354</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22514,7 +22514,7 @@
         <v>391</v>
       </c>
       <c r="H478" s="3" t="n">
-        <v>-97</v>
+        <v>-99</v>
       </c>
       <c r="I478" s="0" t="s">
         <v>21</v>
@@ -22862,7 +22862,7 @@
         <v>391</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="I490" s="0" t="s">
         <v>21</v>
@@ -22920,7 +22920,7 @@
         <v>391</v>
       </c>
       <c r="H492" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I492" s="0" t="s">
         <v>21</v>
@@ -23210,7 +23210,7 @@
         <v>391</v>
       </c>
       <c r="H502" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I502" s="0" t="s">
         <v>21</v>
@@ -23239,7 +23239,7 @@
         <v>391</v>
       </c>
       <c r="H503" s="3" t="n">
-        <v>-2</v>
+        <v>16</v>
       </c>
       <c r="I503" s="0" t="s">
         <v>21</v>
@@ -23268,7 +23268,7 @@
         <v>391</v>
       </c>
       <c r="H504" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I504" s="0" t="s">
         <v>21</v>
@@ -23297,7 +23297,7 @@
         <v>391</v>
       </c>
       <c r="H505" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I505" s="0" t="s">
         <v>21</v>
@@ -23326,7 +23326,7 @@
         <v>391</v>
       </c>
       <c r="H506" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I506" s="0" t="s">
         <v>21</v>
@@ -23645,7 +23645,7 @@
         <v>391</v>
       </c>
       <c r="H517" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I517" s="0" t="s">
         <v>21</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25733,7 +25733,7 @@
         <v>391</v>
       </c>
       <c r="H589" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I589" s="0" t="s">
         <v>21</v>
@@ -25791,7 +25791,7 @@
         <v>391</v>
       </c>
       <c r="H591" s="3" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="I591" s="0" t="s">
         <v>21</v>
@@ -25820,7 +25820,7 @@
         <v>391</v>
       </c>
       <c r="H592" s="3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="I592" s="0" t="s">
         <v>21</v>
@@ -28227,7 +28227,7 @@
         <v>391</v>
       </c>
       <c r="H675" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I675" s="0" t="s">
         <v>21</v>
@@ -28749,7 +28749,7 @@
         <v>844</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I693" s="0" t="s">
         <v>21</v>
@@ -28807,7 +28807,7 @@
         <v>844</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -29068,7 +29068,7 @@
         <v>391</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -30286,7 +30286,7 @@
         <v>844</v>
       </c>
       <c r="H746" s="3" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="I746" s="0" t="s">
         <v>21</v>
@@ -31156,7 +31156,7 @@
         <v>391</v>
       </c>
       <c r="H776" s="3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I776" s="0" t="s">
         <v>21</v>
@@ -31214,7 +31214,7 @@
         <v>391</v>
       </c>
       <c r="H778" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I778" s="0" t="s">
         <v>21</v>
@@ -31417,7 +31417,7 @@
         <v>391</v>
       </c>
       <c r="H785" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I785" s="0" t="s">
         <v>21</v>
@@ -31533,7 +31533,7 @@
         <v>391</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I789" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9187.8</v>
+        <v>9806.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>19 September 2026</t>
+    <t>20 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12770,7 +12770,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -15844,7 +15844,7 @@
         <v>20</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I248" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9806.8</v>
+        <v>9804.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -12770,7 +12770,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9804.8</v>
+        <v>9803.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>20 September 2026</t>
+    <t>21 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12770,7 +12770,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9803.8</v>
+        <v>9802.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9319,7 +9319,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -11697,7 +11697,7 @@
         <v>20</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I105" s="0" t="s">
         <v>21</v>
@@ -11900,7 +11900,7 @@
         <v>20</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I112" s="0" t="s">
         <v>21</v>
@@ -11987,7 +11987,7 @@
         <v>20</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>21</v>
@@ -12103,7 +12103,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12712,7 +12712,7 @@
         <v>20</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I140" s="0" t="s">
         <v>21</v>
@@ -12857,7 +12857,7 @@
         <v>20</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I145" s="0" t="s">
         <v>21</v>
@@ -12886,7 +12886,7 @@
         <v>20</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>21</v>
@@ -13089,7 +13089,7 @@
         <v>20</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I153" s="0" t="s">
         <v>21</v>
@@ -13350,7 +13350,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -13437,7 +13437,7 @@
         <v>20</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I165" s="0" t="s">
         <v>21</v>
@@ -14307,7 +14307,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14655,7 +14655,7 @@
         <v>20</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I207" s="0" t="s">
         <v>21</v>
@@ -19179,7 +19179,7 @@
         <v>391</v>
       </c>
       <c r="H363" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I363" s="0" t="s">
         <v>21</v>
@@ -19208,7 +19208,7 @@
         <v>391</v>
       </c>
       <c r="H364" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I364" s="0" t="s">
         <v>21</v>
@@ -19411,7 +19411,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19469,7 +19469,7 @@
         <v>391</v>
       </c>
       <c r="H373" s="3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I373" s="0" t="s">
         <v>21</v>
@@ -20716,7 +20716,7 @@
         <v>844</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -21789,7 +21789,7 @@
         <v>20</v>
       </c>
       <c r="H453" s="3" t="n">
-        <v>-470</v>
+        <v>-472</v>
       </c>
       <c r="I453" s="0" t="s">
         <v>21</v>
@@ -21905,7 +21905,7 @@
         <v>391</v>
       </c>
       <c r="H457" s="3" t="n">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="I457" s="0" t="s">
         <v>21</v>
@@ -21992,7 +21992,7 @@
         <v>391</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -23558,7 +23558,7 @@
         <v>391</v>
       </c>
       <c r="H514" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I514" s="0" t="s">
         <v>21</v>
@@ -24544,7 +24544,7 @@
         <v>391</v>
       </c>
       <c r="H548" s="3" t="n">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="I548" s="0" t="s">
         <v>21</v>
@@ -24602,7 +24602,7 @@
         <v>391</v>
       </c>
       <c r="H550" s="3" t="n">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="I550" s="0" t="s">
         <v>21</v>
@@ -24660,7 +24660,7 @@
         <v>391</v>
       </c>
       <c r="H552" s="3" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="I552" s="0" t="s">
         <v>21</v>
@@ -24979,7 +24979,7 @@
         <v>20</v>
       </c>
       <c r="H563" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I563" s="0" t="s">
         <v>21</v>
@@ -25124,7 +25124,7 @@
         <v>20</v>
       </c>
       <c r="H568" s="3" t="n">
-        <v>-310</v>
+        <v>-312</v>
       </c>
       <c r="I568" s="0" t="s">
         <v>21</v>
@@ -25182,7 +25182,7 @@
         <v>20</v>
       </c>
       <c r="H570" s="3" t="n">
-        <v>-735</v>
+        <v>-736</v>
       </c>
       <c r="I570" s="0" t="s">
         <v>21</v>
@@ -25260,7 +25260,7 @@
         <v>10</v>
       </c>
       <c r="E573" s="3" t="n">
-        <v>5.38</v>
+        <v>5.83</v>
       </c>
       <c r="F573" s="2" t="s">
         <v>19</v>
@@ -25269,7 +25269,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -26168,7 +26168,7 @@
         <v>391</v>
       </c>
       <c r="H604" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I604" s="0" t="s">
         <v>21</v>
@@ -26458,7 +26458,7 @@
         <v>391</v>
       </c>
       <c r="H614" s="3" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I614" s="0" t="s">
         <v>21</v>
@@ -27038,7 +27038,7 @@
         <v>391</v>
       </c>
       <c r="H634" s="3" t="n">
-        <v>-70</v>
+        <v>-71</v>
       </c>
       <c r="I634" s="0" t="s">
         <v>21</v>
@@ -28314,7 +28314,7 @@
         <v>391</v>
       </c>
       <c r="H678" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I678" s="0" t="s">
         <v>21</v>
@@ -28343,7 +28343,7 @@
         <v>391</v>
       </c>
       <c r="H679" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I679" s="0" t="s">
         <v>21</v>
@@ -28662,7 +28662,7 @@
         <v>391</v>
       </c>
       <c r="H690" s="3" t="n">
-        <v>-43</v>
+        <v>-3</v>
       </c>
       <c r="I690" s="0" t="s">
         <v>21</v>
@@ -28807,7 +28807,7 @@
         <v>844</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -29068,7 +29068,7 @@
         <v>391</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -29126,7 +29126,7 @@
         <v>391</v>
       </c>
       <c r="H706" s="3" t="n">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="I706" s="0" t="s">
         <v>21</v>
@@ -29706,7 +29706,7 @@
         <v>391</v>
       </c>
       <c r="H726" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I726" s="0" t="s">
         <v>21</v>
@@ -29880,7 +29880,7 @@
         <v>391</v>
       </c>
       <c r="H732" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I732" s="0" t="s">
         <v>21</v>
@@ -29909,7 +29909,7 @@
         <v>391</v>
       </c>
       <c r="H733" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I733" s="0" t="s">
         <v>21</v>
@@ -29938,7 +29938,7 @@
         <v>391</v>
       </c>
       <c r="H734" s="3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I734" s="0" t="s">
         <v>21</v>
@@ -30286,7 +30286,7 @@
         <v>844</v>
       </c>
       <c r="H746" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I746" s="0" t="s">
         <v>21</v>
@@ -31533,7 +31533,7 @@
         <v>391</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I789" s="0" t="s">
         <v>21</v>
@@ -32461,7 +32461,7 @@
         <v>391</v>
       </c>
       <c r="H821" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I821" s="0" t="s">
         <v>21</v>
@@ -33012,7 +33012,7 @@
         <v>20</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-817</v>
+        <v>-821</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -35622,7 +35622,7 @@
         <v>20</v>
       </c>
       <c r="H930" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I930" s="0" t="s">
         <v>21</v>
@@ -35680,7 +35680,7 @@
         <v>20</v>
       </c>
       <c r="H932" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I932" s="0" t="s">
         <v>21</v>
@@ -35709,7 +35709,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -36703,7 +36703,7 @@
     </row>
     <row r="968" spans="8:8" customHeight="1">
       <c r="H968" s="3" t="n">
-        <v>9802.8</v>
+        <v>9803.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>21 September 2026</t>
+    <t>22 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12788,7 +12788,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -22184,7 +22184,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -25055,7 +25055,7 @@
         <v>20</v>
       </c>
       <c r="H565" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I565" s="0" t="s">
         <v>21</v>
@@ -29782,7 +29782,7 @@
         <v>391</v>
       </c>
       <c r="H728" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I728" s="0" t="s">
         <v>21</v>
@@ -31609,7 +31609,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -36779,7 +36779,7 @@
     </row>
     <row r="970" spans="8:8" customHeight="1">
       <c r="H970" s="3" t="n">
-        <v>9571.6</v>
+        <v>9558.6</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9308,7 +9308,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" s="0" t="s">
         <v>21</v>
@@ -10874,7 +10874,7 @@
         <v>20</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" s="0" t="s">
         <v>21</v>
@@ -10961,7 +10961,7 @@
         <v>20</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" s="0" t="s">
         <v>21</v>
@@ -11773,7 +11773,7 @@
         <v>20</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I107" s="0" t="s">
         <v>21</v>
@@ -11947,7 +11947,7 @@
         <v>20</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I113" s="0" t="s">
         <v>21</v>
@@ -12121,7 +12121,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12817,7 +12817,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13252,7 +13252,7 @@
         <v>20</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I158" s="0" t="s">
         <v>21</v>
@@ -13832,7 +13832,7 @@
         <v>20</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>21</v>
@@ -14325,7 +14325,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14354,7 +14354,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>-3</v>
+        <v>47</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14383,7 +14383,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14412,7 +14412,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -17167,7 +17167,7 @@
         <v>20</v>
       </c>
       <c r="H293" s="3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I293" s="0" t="s">
         <v>21</v>
@@ -18559,7 +18559,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -19980,7 +19980,7 @@
         <v>20</v>
       </c>
       <c r="H390" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I390" s="0" t="s">
         <v>21</v>
@@ -20096,7 +20096,7 @@
         <v>20</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I394" s="0" t="s">
         <v>21</v>
@@ -20328,7 +20328,7 @@
         <v>20</v>
       </c>
       <c r="H402" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I402" s="0" t="s">
         <v>21</v>
@@ -20792,7 +20792,7 @@
         <v>848</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="I418" s="0" t="s">
         <v>21</v>
@@ -21430,7 +21430,7 @@
         <v>391</v>
       </c>
       <c r="H440" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I440" s="0" t="s">
         <v>21</v>
@@ -21720,7 +21720,7 @@
         <v>391</v>
       </c>
       <c r="H450" s="3" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I450" s="0" t="s">
         <v>21</v>
@@ -21865,7 +21865,7 @@
         <v>20</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-472</v>
+        <v>-474</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22532,7 +22532,7 @@
         <v>391</v>
       </c>
       <c r="H478" s="3" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I478" s="0" t="s">
         <v>21</v>
@@ -25055,7 +25055,7 @@
         <v>20</v>
       </c>
       <c r="H565" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I565" s="0" t="s">
         <v>21</v>
@@ -25258,7 +25258,7 @@
         <v>20</v>
       </c>
       <c r="H572" s="3" t="n">
-        <v>-736</v>
+        <v>-737</v>
       </c>
       <c r="I572" s="0" t="s">
         <v>21</v>
@@ -25345,7 +25345,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -28825,7 +28825,7 @@
         <v>848</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -30014,7 +30014,7 @@
         <v>391</v>
       </c>
       <c r="H736" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I736" s="0" t="s">
         <v>21</v>
@@ -30362,7 +30362,7 @@
         <v>848</v>
       </c>
       <c r="H748" s="3" t="n">
-        <v>-3</v>
+        <v>94</v>
       </c>
       <c r="I748" s="0" t="s">
         <v>21</v>
@@ -30710,7 +30710,7 @@
         <v>391</v>
       </c>
       <c r="H760" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I760" s="0" t="s">
         <v>21</v>
@@ -30913,7 +30913,7 @@
         <v>391</v>
       </c>
       <c r="H767" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I767" s="0" t="s">
         <v>834</v>
@@ -31000,7 +31000,7 @@
         <v>391</v>
       </c>
       <c r="H770" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I770" s="0" t="s">
         <v>834</v>
@@ -31754,7 +31754,7 @@
         <v>391</v>
       </c>
       <c r="H796" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I796" s="0" t="s">
         <v>21</v>
@@ -31783,7 +31783,7 @@
         <v>391</v>
       </c>
       <c r="H797" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I797" s="0" t="s">
         <v>21</v>
@@ -32421,7 +32421,7 @@
         <v>391</v>
       </c>
       <c r="H819" s="3" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I819" s="0" t="s">
         <v>21</v>
@@ -32450,7 +32450,7 @@
         <v>391</v>
       </c>
       <c r="H820" s="3" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I820" s="0" t="s">
         <v>21</v>
@@ -33088,7 +33088,7 @@
         <v>20</v>
       </c>
       <c r="H842" s="3" t="n">
-        <v>-821</v>
+        <v>-824</v>
       </c>
       <c r="I842" s="0" t="s">
         <v>21</v>
@@ -33813,7 +33813,7 @@
         <v>391</v>
       </c>
       <c r="H867" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I867" s="0" t="s">
         <v>21</v>
@@ -35495,7 +35495,7 @@
         <v>391</v>
       </c>
       <c r="H925" s="3" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I925" s="0" t="s">
         <v>21</v>
@@ -35524,7 +35524,7 @@
         <v>391</v>
       </c>
       <c r="H926" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I926" s="0" t="s">
         <v>21</v>
@@ -35756,7 +35756,7 @@
         <v>20</v>
       </c>
       <c r="H934" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I934" s="0" t="s">
         <v>21</v>
@@ -36779,7 +36779,7 @@
     </row>
     <row r="970" spans="8:8" customHeight="1">
       <c r="H970" s="3" t="n">
-        <v>9558.6</v>
+        <v>9854.6</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -13252,7 +13252,7 @@
         <v>20</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158" s="0" t="s">
         <v>21</v>
@@ -14354,7 +14354,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -15717,7 +15717,7 @@
         <v>20</v>
       </c>
       <c r="H243" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I243" s="0" t="s">
         <v>21</v>
@@ -17196,7 +17196,7 @@
         <v>20</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I294" s="0" t="s">
         <v>21</v>
@@ -18385,7 +18385,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18414,7 +18414,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18443,7 +18443,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18472,7 +18472,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18530,7 +18530,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -19255,7 +19255,7 @@
         <v>391</v>
       </c>
       <c r="H365" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I365" s="0" t="s">
         <v>21</v>
@@ -20183,7 +20183,7 @@
         <v>20</v>
       </c>
       <c r="H397" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I397" s="0" t="s">
         <v>21</v>
@@ -20792,7 +20792,7 @@
         <v>848</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="I418" s="0" t="s">
         <v>21</v>
@@ -21836,7 +21836,7 @@
         <v>391</v>
       </c>
       <c r="H454" s="3" t="n">
-        <v>-6303.4</v>
+        <v>-6309.4</v>
       </c>
       <c r="I454" s="0" t="s">
         <v>21</v>
@@ -22010,7 +22010,7 @@
         <v>391</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22068,7 +22068,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -22126,7 +22126,7 @@
         <v>391</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>21</v>
@@ -22184,7 +22184,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22242,7 +22242,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -23402,7 +23402,7 @@
         <v>391</v>
       </c>
       <c r="H508" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I508" s="0" t="s">
         <v>21</v>
@@ -23431,7 +23431,7 @@
         <v>391</v>
       </c>
       <c r="H509" s="3" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I509" s="0" t="s">
         <v>21</v>
@@ -23634,7 +23634,7 @@
         <v>391</v>
       </c>
       <c r="H516" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I516" s="0" t="s">
         <v>21</v>
@@ -25345,7 +25345,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -28825,7 +28825,7 @@
         <v>848</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -30362,7 +30362,7 @@
         <v>848</v>
       </c>
       <c r="H748" s="3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I748" s="0" t="s">
         <v>21</v>
@@ -31493,7 +31493,7 @@
         <v>391</v>
       </c>
       <c r="H787" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I787" s="0" t="s">
         <v>21</v>
@@ -31522,7 +31522,7 @@
         <v>391</v>
       </c>
       <c r="H788" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I788" s="0" t="s">
         <v>21</v>
@@ -35611,7 +35611,7 @@
         <v>391</v>
       </c>
       <c r="H929" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I929" s="0" t="s">
         <v>21</v>
@@ -36779,7 +36779,7 @@
     </row>
     <row r="970" spans="8:8" customHeight="1">
       <c r="H970" s="3" t="n">
-        <v>9854.6</v>
+        <v>9746.6</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>22 September 2026</t>
+    <t>23 September 2026</t>
   </si>
   <si>
     <t>To</t>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9337,7 +9337,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -9366,7 +9366,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -12121,7 +12121,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -13107,7 +13107,7 @@
         <v>20</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I153" s="0" t="s">
         <v>21</v>
@@ -13484,7 +13484,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -14383,7 +14383,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14412,7 +14412,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -17167,7 +17167,7 @@
         <v>20</v>
       </c>
       <c r="H293" s="3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I293" s="0" t="s">
         <v>21</v>
@@ -18414,7 +18414,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18443,7 +18443,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18472,7 +18472,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18530,7 +18530,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -19371,7 +19371,7 @@
         <v>391</v>
       </c>
       <c r="H369" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I369" s="0" t="s">
         <v>21</v>
@@ -19516,7 +19516,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -19545,7 +19545,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19574,7 +19574,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -20038,7 +20038,7 @@
         <v>20</v>
       </c>
       <c r="H392" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I392" s="0" t="s">
         <v>21</v>
@@ -20067,7 +20067,7 @@
         <v>20</v>
       </c>
       <c r="H393" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I393" s="0" t="s">
         <v>21</v>
@@ -20792,7 +20792,7 @@
         <v>848</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I418" s="0" t="s">
         <v>21</v>
@@ -21865,7 +21865,7 @@
         <v>20</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-474</v>
+        <v>-476</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22126,7 +22126,7 @@
         <v>391</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>21</v>
@@ -25055,7 +25055,7 @@
         <v>20</v>
       </c>
       <c r="H565" s="3" t="n">
-        <v>-2</v>
+        <v>8</v>
       </c>
       <c r="I565" s="0" t="s">
         <v>21</v>
@@ -25345,7 +25345,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -27143,7 +27143,7 @@
         <v>391</v>
       </c>
       <c r="H637" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I637" s="0" t="s">
         <v>21</v>
@@ -28448,7 +28448,7 @@
         <v>391</v>
       </c>
       <c r="H682" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I682" s="0" t="s">
         <v>21</v>
@@ -28883,7 +28883,7 @@
         <v>848</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -30362,7 +30362,7 @@
         <v>848</v>
       </c>
       <c r="H748" s="3" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I748" s="0" t="s">
         <v>21</v>
@@ -31783,7 +31783,7 @@
         <v>391</v>
       </c>
       <c r="H797" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I797" s="0" t="s">
         <v>21</v>
@@ -32450,7 +32450,7 @@
         <v>391</v>
       </c>
       <c r="H820" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I820" s="0" t="s">
         <v>21</v>
@@ -33088,7 +33088,7 @@
         <v>20</v>
       </c>
       <c r="H842" s="3" t="n">
-        <v>-824</v>
+        <v>-828</v>
       </c>
       <c r="I842" s="0" t="s">
         <v>21</v>
@@ -35437,7 +35437,7 @@
         <v>391</v>
       </c>
       <c r="H923" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I923" s="0" t="s">
         <v>21</v>
@@ -35466,7 +35466,7 @@
         <v>391</v>
       </c>
       <c r="H924" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I924" s="0" t="s">
         <v>21</v>
@@ -35611,7 +35611,7 @@
         <v>391</v>
       </c>
       <c r="H929" s="3" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I929" s="0" t="s">
         <v>21</v>
@@ -35698,7 +35698,7 @@
         <v>20</v>
       </c>
       <c r="H932" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I932" s="0" t="s">
         <v>21</v>
@@ -36779,7 +36779,7 @@
     </row>
     <row r="970" spans="8:8" customHeight="1">
       <c r="H970" s="3" t="n">
-        <v>9746.6</v>
+        <v>9747.6</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -12353,7 +12353,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -12875,7 +12875,7 @@
         <v>20</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I145" s="0" t="s">
         <v>21</v>
@@ -14325,7 +14325,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14383,7 +14383,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -18385,7 +18385,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18414,7 +18414,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18472,7 +18472,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18530,7 +18530,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18559,7 +18559,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -19313,7 +19313,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19516,7 +19516,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -20270,7 +20270,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -20328,7 +20328,7 @@
         <v>20</v>
       </c>
       <c r="H402" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I402" s="0" t="s">
         <v>21</v>
@@ -20357,7 +20357,7 @@
         <v>20</v>
       </c>
       <c r="H403" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I403" s="0" t="s">
         <v>21</v>
@@ -20734,7 +20734,7 @@
         <v>391</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -20792,7 +20792,7 @@
         <v>848</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="I418" s="0" t="s">
         <v>21</v>
@@ -21169,7 +21169,7 @@
         <v>391</v>
       </c>
       <c r="H431" s="3" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="I431" s="0" t="s">
         <v>21</v>
@@ -21227,7 +21227,7 @@
         <v>391</v>
       </c>
       <c r="H433" s="3" t="n">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="I433" s="0" t="s">
         <v>21</v>
@@ -21430,7 +21430,7 @@
         <v>391</v>
       </c>
       <c r="H440" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I440" s="0" t="s">
         <v>21</v>
@@ -21836,7 +21836,7 @@
         <v>391</v>
       </c>
       <c r="H454" s="3" t="n">
-        <v>-6309.4</v>
+        <v>-6320</v>
       </c>
       <c r="I454" s="0" t="s">
         <v>21</v>
@@ -21865,7 +21865,7 @@
         <v>20</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-476</v>
+        <v>-478</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -21952,7 +21952,7 @@
         <v>391</v>
       </c>
       <c r="H458" s="3" t="n">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="I458" s="0" t="s">
         <v>21</v>
@@ -22184,7 +22184,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22242,7 +22242,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22271,7 +22271,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22561,7 +22561,7 @@
         <v>391</v>
       </c>
       <c r="H479" s="3" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I479" s="0" t="s">
         <v>21</v>
@@ -23373,7 +23373,7 @@
         <v>391</v>
       </c>
       <c r="H507" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I507" s="0" t="s">
         <v>21</v>
@@ -23431,7 +23431,7 @@
         <v>391</v>
       </c>
       <c r="H509" s="3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I509" s="0" t="s">
         <v>21</v>
@@ -23634,7 +23634,7 @@
         <v>391</v>
       </c>
       <c r="H516" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I516" s="0" t="s">
         <v>21</v>
@@ -24620,7 +24620,7 @@
         <v>391</v>
       </c>
       <c r="H550" s="3" t="n">
-        <v>670</v>
+        <v>645</v>
       </c>
       <c r="I550" s="0" t="s">
         <v>21</v>
@@ -24736,7 +24736,7 @@
         <v>391</v>
       </c>
       <c r="H554" s="3" t="n">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="I554" s="0" t="s">
         <v>21</v>
@@ -25345,7 +25345,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25896,7 +25896,7 @@
         <v>391</v>
       </c>
       <c r="H594" s="3" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I594" s="0" t="s">
         <v>21</v>
@@ -26244,7 +26244,7 @@
         <v>391</v>
       </c>
       <c r="H606" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I606" s="0" t="s">
         <v>21</v>
@@ -27143,7 +27143,7 @@
         <v>391</v>
       </c>
       <c r="H637" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I637" s="0" t="s">
         <v>21</v>
@@ -28796,7 +28796,7 @@
         <v>848</v>
       </c>
       <c r="H694" s="3" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I694" s="0" t="s">
         <v>21</v>
@@ -30362,7 +30362,7 @@
         <v>848</v>
       </c>
       <c r="H748" s="3" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I748" s="0" t="s">
         <v>21</v>
@@ -31522,7 +31522,7 @@
         <v>391</v>
       </c>
       <c r="H788" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I788" s="0" t="s">
         <v>21</v>
@@ -31609,7 +31609,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -33088,7 +33088,7 @@
         <v>20</v>
       </c>
       <c r="H842" s="3" t="n">
-        <v>-828</v>
+        <v>-831</v>
       </c>
       <c r="I842" s="0" t="s">
         <v>21</v>
@@ -34190,7 +34190,7 @@
         <v>391</v>
       </c>
       <c r="H880" s="3" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I880" s="0" t="s">
         <v>21</v>
@@ -34422,7 +34422,7 @@
         <v>391</v>
       </c>
       <c r="H888" s="3" t="n">
-        <v>-129</v>
+        <v>-179</v>
       </c>
       <c r="I888" s="0" t="s">
         <v>21</v>
@@ -34509,7 +34509,7 @@
         <v>391</v>
       </c>
       <c r="H891" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I891" s="0" t="s">
         <v>21</v>
@@ -35611,7 +35611,7 @@
         <v>391</v>
       </c>
       <c r="H929" s="3" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I929" s="0" t="s">
         <v>21</v>
@@ -36779,7 +36779,7 @@
     </row>
     <row r="970" spans="8:8" customHeight="1">
       <c r="H970" s="3" t="n">
-        <v>9747.6</v>
+        <v>9489</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>23 September 2026</t>
+    <t>24 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12788,7 +12788,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -36779,7 +36779,7 @@
     </row>
     <row r="970" spans="8:8" customHeight="1">
       <c r="H970" s="3" t="n">
-        <v>9489</v>
+        <v>9488</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -11715,7 +11715,7 @@
         <v>20</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I105" s="0" t="s">
         <v>21</v>
@@ -11947,7 +11947,7 @@
         <v>20</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I113" s="0" t="s">
         <v>21</v>
@@ -12063,7 +12063,7 @@
         <v>20</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I117" s="0" t="s">
         <v>21</v>
@@ -12121,7 +12121,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12817,7 +12817,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -12991,7 +12991,7 @@
         <v>20</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I149" s="0" t="s">
         <v>21</v>
@@ -13484,7 +13484,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -14354,7 +14354,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14383,7 +14383,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14412,7 +14412,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -17196,7 +17196,7 @@
         <v>20</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I294" s="0" t="s">
         <v>21</v>
@@ -18472,7 +18472,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -20096,7 +20096,7 @@
         <v>20</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I394" s="0" t="s">
         <v>21</v>
@@ -20183,7 +20183,7 @@
         <v>20</v>
       </c>
       <c r="H397" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I397" s="0" t="s">
         <v>21</v>
@@ -20270,7 +20270,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -20734,7 +20734,7 @@
         <v>391</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -20792,7 +20792,7 @@
         <v>848</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I418" s="0" t="s">
         <v>21</v>
@@ -22126,7 +22126,7 @@
         <v>391</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>21</v>
@@ -22184,7 +22184,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -24910,7 +24910,7 @@
         <v>20</v>
       </c>
       <c r="H560" s="3" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="I560" s="0" t="s">
         <v>21</v>
@@ -25200,7 +25200,7 @@
         <v>20</v>
       </c>
       <c r="H570" s="3" t="n">
-        <v>-312</v>
+        <v>-313</v>
       </c>
       <c r="I570" s="0" t="s">
         <v>21</v>
@@ -25258,7 +25258,7 @@
         <v>20</v>
       </c>
       <c r="H572" s="3" t="n">
-        <v>-737</v>
+        <v>-740</v>
       </c>
       <c r="I572" s="0" t="s">
         <v>21</v>
@@ -25345,7 +25345,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -27143,7 +27143,7 @@
         <v>391</v>
       </c>
       <c r="H637" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I637" s="0" t="s">
         <v>21</v>
@@ -28825,7 +28825,7 @@
         <v>848</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -28883,7 +28883,7 @@
         <v>848</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -30710,7 +30710,7 @@
         <v>391</v>
       </c>
       <c r="H760" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I760" s="0" t="s">
         <v>21</v>
@@ -31493,7 +31493,7 @@
         <v>391</v>
       </c>
       <c r="H787" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I787" s="0" t="s">
         <v>21</v>
@@ -35611,7 +35611,7 @@
         <v>391</v>
       </c>
       <c r="H929" s="3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I929" s="0" t="s">
         <v>21</v>
@@ -35698,7 +35698,7 @@
         <v>20</v>
       </c>
       <c r="H932" s="3" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="I932" s="0" t="s">
         <v>21</v>
@@ -36779,7 +36779,7 @@
     </row>
     <row r="970" spans="8:8" customHeight="1">
       <c r="H970" s="3" t="n">
-        <v>9488</v>
+        <v>9431</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>24 September 2026</t>
+    <t>25 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -11773,7 +11773,7 @@
         <v>20</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I107" s="0" t="s">
         <v>21</v>
@@ -12788,7 +12788,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -14354,7 +14354,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14412,7 +14412,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -18385,7 +18385,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18414,7 +18414,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18472,7 +18472,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18501,7 +18501,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18530,7 +18530,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18936,7 +18936,7 @@
         <v>391</v>
       </c>
       <c r="H354" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I354" s="0" t="s">
         <v>21</v>
@@ -19255,7 +19255,7 @@
         <v>391</v>
       </c>
       <c r="H365" s="3" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I365" s="0" t="s">
         <v>21</v>
@@ -19284,7 +19284,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19371,7 +19371,7 @@
         <v>391</v>
       </c>
       <c r="H369" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I369" s="0" t="s">
         <v>21</v>
@@ -19400,7 +19400,7 @@
         <v>391</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19487,7 +19487,7 @@
         <v>391</v>
       </c>
       <c r="H373" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I373" s="0" t="s">
         <v>21</v>
@@ -19545,7 +19545,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19574,7 +19574,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -20792,7 +20792,7 @@
         <v>848</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="I418" s="0" t="s">
         <v>21</v>
@@ -21430,7 +21430,7 @@
         <v>391</v>
       </c>
       <c r="H440" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I440" s="0" t="s">
         <v>21</v>
@@ -21836,7 +21836,7 @@
         <v>391</v>
       </c>
       <c r="H454" s="3" t="n">
-        <v>-6320</v>
+        <v>-6331</v>
       </c>
       <c r="I454" s="0" t="s">
         <v>21</v>
@@ -21952,7 +21952,7 @@
         <v>391</v>
       </c>
       <c r="H458" s="3" t="n">
-        <v>656</v>
+        <v>626</v>
       </c>
       <c r="I458" s="0" t="s">
         <v>21</v>
@@ -22010,7 +22010,7 @@
         <v>391</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22097,7 +22097,7 @@
         <v>391</v>
       </c>
       <c r="H463" s="3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I463" s="0" t="s">
         <v>21</v>
@@ -22126,7 +22126,7 @@
         <v>391</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>21</v>
@@ -22213,7 +22213,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22242,7 +22242,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22271,7 +22271,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22474,7 +22474,7 @@
         <v>391</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22503,7 +22503,7 @@
         <v>391</v>
       </c>
       <c r="H477" s="3" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="I477" s="0" t="s">
         <v>21</v>
@@ -22532,7 +22532,7 @@
         <v>391</v>
       </c>
       <c r="H478" s="3" t="n">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="I478" s="0" t="s">
         <v>21</v>
@@ -22648,7 +22648,7 @@
         <v>391</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I482" s="0" t="s">
         <v>21</v>
@@ -22996,7 +22996,7 @@
         <v>391</v>
       </c>
       <c r="H494" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I494" s="0" t="s">
         <v>21</v>
@@ -23344,7 +23344,7 @@
         <v>391</v>
       </c>
       <c r="H506" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I506" s="0" t="s">
         <v>21</v>
@@ -23373,7 +23373,7 @@
         <v>391</v>
       </c>
       <c r="H507" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I507" s="0" t="s">
         <v>21</v>
@@ -23431,7 +23431,7 @@
         <v>391</v>
       </c>
       <c r="H509" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I509" s="0" t="s">
         <v>21</v>
@@ -23634,7 +23634,7 @@
         <v>391</v>
       </c>
       <c r="H516" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I516" s="0" t="s">
         <v>21</v>
@@ -25345,7 +25345,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25867,7 +25867,7 @@
         <v>391</v>
       </c>
       <c r="H593" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I593" s="0" t="s">
         <v>21</v>
@@ -25896,7 +25896,7 @@
         <v>391</v>
       </c>
       <c r="H594" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I594" s="0" t="s">
         <v>21</v>
@@ -28448,7 +28448,7 @@
         <v>391</v>
       </c>
       <c r="H682" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I682" s="0" t="s">
         <v>21</v>
@@ -28477,7 +28477,7 @@
         <v>391</v>
       </c>
       <c r="H683" s="3" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I683" s="0" t="s">
         <v>21</v>
@@ -28506,7 +28506,7 @@
         <v>391</v>
       </c>
       <c r="H684" s="3" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I684" s="0" t="s">
         <v>21</v>
@@ -28535,7 +28535,7 @@
         <v>391</v>
       </c>
       <c r="H685" s="3" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I685" s="0" t="s">
         <v>21</v>
@@ -28825,7 +28825,7 @@
         <v>848</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -28883,7 +28883,7 @@
         <v>848</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -29144,7 +29144,7 @@
         <v>391</v>
       </c>
       <c r="H706" s="3" t="n">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="I706" s="0" t="s">
         <v>21</v>
@@ -30014,7 +30014,7 @@
         <v>391</v>
       </c>
       <c r="H736" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I736" s="0" t="s">
         <v>21</v>
@@ -30362,7 +30362,7 @@
         <v>848</v>
       </c>
       <c r="H748" s="3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I748" s="0" t="s">
         <v>21</v>
@@ -32334,7 +32334,7 @@
         <v>391</v>
       </c>
       <c r="H816" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I816" s="0" t="s">
         <v>21</v>
@@ -34770,7 +34770,7 @@
         <v>391</v>
       </c>
       <c r="H900" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I900" s="0" t="s">
         <v>21</v>
@@ -35611,7 +35611,7 @@
         <v>391</v>
       </c>
       <c r="H929" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I929" s="0" t="s">
         <v>21</v>
@@ -35814,7 +35814,7 @@
         <v>391</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -36779,7 +36779,7 @@
     </row>
     <row r="970" spans="8:8" customHeight="1">
       <c r="H970" s="3" t="n">
-        <v>9431</v>
+        <v>9158</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14372,7 +14372,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -18548,7 +18548,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -19331,7 +19331,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19389,7 +19389,7 @@
         <v>391</v>
       </c>
       <c r="H369" s="3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I369" s="0" t="s">
         <v>21</v>
@@ -19418,7 +19418,7 @@
         <v>391</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19447,7 +19447,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19534,7 +19534,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -19563,7 +19563,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -20752,7 +20752,7 @@
         <v>391</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -20810,7 +20810,7 @@
         <v>848</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I418" s="0" t="s">
         <v>21</v>
@@ -21187,7 +21187,7 @@
         <v>391</v>
       </c>
       <c r="H431" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I431" s="0" t="s">
         <v>21</v>
@@ -21245,7 +21245,7 @@
         <v>391</v>
       </c>
       <c r="H433" s="3" t="n">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="I433" s="0" t="s">
         <v>21</v>
@@ -21854,7 +21854,7 @@
         <v>391</v>
       </c>
       <c r="H454" s="3" t="n">
-        <v>-6331</v>
+        <v>-6343</v>
       </c>
       <c r="I454" s="0" t="s">
         <v>21</v>
@@ -21970,7 +21970,7 @@
         <v>391</v>
       </c>
       <c r="H458" s="3" t="n">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="I458" s="0" t="s">
         <v>21</v>
@@ -22115,7 +22115,7 @@
         <v>391</v>
       </c>
       <c r="H463" s="3" t="n">
-        <v>-1</v>
+        <v>149</v>
       </c>
       <c r="I463" s="0" t="s">
         <v>834</v>
@@ -22144,7 +22144,7 @@
         <v>833</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>834</v>
@@ -22173,7 +22173,7 @@
         <v>391</v>
       </c>
       <c r="H465" s="3" t="n">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="I465" s="0" t="s">
         <v>21</v>
@@ -22202,7 +22202,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>50</v>
+        <v>226</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22260,7 +22260,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>-1</v>
+        <v>199</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22666,7 +22666,7 @@
         <v>391</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>-119</v>
+        <v>-19</v>
       </c>
       <c r="I482" s="0" t="s">
         <v>21</v>
@@ -22695,7 +22695,7 @@
         <v>391</v>
       </c>
       <c r="H483" s="3" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="I483" s="0" t="s">
         <v>21</v>
@@ -22724,7 +22724,7 @@
         <v>391</v>
       </c>
       <c r="H484" s="3" t="n">
-        <v>7</v>
+        <v>307</v>
       </c>
       <c r="I484" s="0" t="s">
         <v>21</v>
@@ -23014,7 +23014,7 @@
         <v>391</v>
       </c>
       <c r="H494" s="3" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="I494" s="0" t="s">
         <v>21</v>
@@ -23072,7 +23072,7 @@
         <v>391</v>
       </c>
       <c r="H496" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I496" s="0" t="s">
         <v>21</v>
@@ -23449,7 +23449,7 @@
         <v>391</v>
       </c>
       <c r="H509" s="3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I509" s="0" t="s">
         <v>21</v>
@@ -23855,7 +23855,7 @@
         <v>391</v>
       </c>
       <c r="H523" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I523" s="0" t="s">
         <v>21</v>
@@ -24696,7 +24696,7 @@
         <v>391</v>
       </c>
       <c r="H552" s="3" t="n">
-        <v>645</v>
+        <v>613</v>
       </c>
       <c r="I552" s="0" t="s">
         <v>21</v>
@@ -27190,7 +27190,7 @@
         <v>391</v>
       </c>
       <c r="H638" s="3" t="n">
-        <v>-74</v>
+        <v>-78</v>
       </c>
       <c r="I638" s="0" t="s">
         <v>21</v>
@@ -27219,7 +27219,7 @@
         <v>391</v>
       </c>
       <c r="H639" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I639" s="0" t="s">
         <v>21</v>
@@ -28553,7 +28553,7 @@
         <v>391</v>
       </c>
       <c r="H685" s="3" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I685" s="0" t="s">
         <v>21</v>
@@ -28756,7 +28756,7 @@
         <v>391</v>
       </c>
       <c r="H692" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I692" s="0" t="s">
         <v>21</v>
@@ -28814,7 +28814,7 @@
         <v>391</v>
       </c>
       <c r="H694" s="3" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="I694" s="0" t="s">
         <v>21</v>
@@ -28872,7 +28872,7 @@
         <v>848</v>
       </c>
       <c r="H696" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I696" s="0" t="s">
         <v>21</v>
@@ -29220,7 +29220,7 @@
         <v>391</v>
       </c>
       <c r="H708" s="3" t="n">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="I708" s="0" t="s">
         <v>21</v>
@@ -29278,7 +29278,7 @@
         <v>391</v>
       </c>
       <c r="H710" s="3" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="I710" s="0" t="s">
         <v>21</v>
@@ -30061,7 +30061,7 @@
         <v>391</v>
       </c>
       <c r="H737" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I737" s="0" t="s">
         <v>21</v>
@@ -30090,7 +30090,7 @@
         <v>391</v>
       </c>
       <c r="H738" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I738" s="0" t="s">
         <v>21</v>
@@ -30438,7 +30438,7 @@
         <v>848</v>
       </c>
       <c r="H750" s="3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I750" s="0" t="s">
         <v>21</v>
@@ -31105,7 +31105,7 @@
         <v>391</v>
       </c>
       <c r="H773" s="3" t="n">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="I773" s="0" t="s">
         <v>21</v>
@@ -31192,7 +31192,7 @@
         <v>391</v>
       </c>
       <c r="H776" s="3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I776" s="0" t="s">
         <v>21</v>
@@ -31308,7 +31308,7 @@
         <v>391</v>
       </c>
       <c r="H780" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I780" s="0" t="s">
         <v>21</v>
@@ -31569,7 +31569,7 @@
         <v>391</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I789" s="0" t="s">
         <v>21</v>
@@ -31685,7 +31685,7 @@
         <v>391</v>
       </c>
       <c r="H793" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I793" s="0" t="s">
         <v>21</v>
@@ -32410,7 +32410,7 @@
         <v>391</v>
       </c>
       <c r="H818" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I818" s="0" t="s">
         <v>21</v>
@@ -34034,7 +34034,7 @@
         <v>391</v>
       </c>
       <c r="H874" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I874" s="0" t="s">
         <v>21</v>
@@ -34092,7 +34092,7 @@
         <v>391</v>
       </c>
       <c r="H876" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I876" s="0" t="s">
         <v>21</v>
@@ -34121,7 +34121,7 @@
         <v>391</v>
       </c>
       <c r="H877" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I877" s="0" t="s">
         <v>21</v>
@@ -34266,7 +34266,7 @@
         <v>391</v>
       </c>
       <c r="H882" s="3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I882" s="0" t="s">
         <v>21</v>
@@ -34730,7 +34730,7 @@
         <v>391</v>
       </c>
       <c r="H898" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I898" s="0" t="s">
         <v>21</v>
@@ -35687,7 +35687,7 @@
         <v>391</v>
       </c>
       <c r="H931" s="3" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I931" s="0" t="s">
         <v>21</v>
@@ -35890,7 +35890,7 @@
         <v>391</v>
       </c>
       <c r="H938" s="3" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I938" s="0" t="s">
         <v>21</v>
@@ -35977,7 +35977,7 @@
         <v>391</v>
       </c>
       <c r="H941" s="3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I941" s="0" t="s">
         <v>21</v>
@@ -36855,7 +36855,7 @@
     </row>
     <row r="972" spans="8:8" customHeight="1">
       <c r="H972" s="3" t="n">
-        <v>9088</v>
+        <v>10128</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>25 September 2026</t>
+    <t>26 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12806,7 +12806,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -14372,7 +14372,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14401,7 +14401,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -18461,7 +18461,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -20752,7 +20752,7 @@
         <v>391</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I416" s="0" t="s">
         <v>21</v>
@@ -20810,7 +20810,7 @@
         <v>848</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I418" s="0" t="s">
         <v>21</v>
@@ -22260,7 +22260,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -29220,7 +29220,7 @@
         <v>391</v>
       </c>
       <c r="H708" s="3" t="n">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="I708" s="0" t="s">
         <v>21</v>
@@ -36855,7 +36855,7 @@
     </row>
     <row r="972" spans="8:8" customHeight="1">
       <c r="H972" s="3" t="n">
-        <v>10128</v>
+        <v>10107</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -12371,7 +12371,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -15068,7 +15068,7 @@
         <v>20</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I220" s="0" t="s">
         <v>21</v>
@@ -16808,7 +16808,7 @@
         <v>20</v>
       </c>
       <c r="H280" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I280" s="0" t="s">
         <v>21</v>
@@ -20056,7 +20056,7 @@
         <v>20</v>
       </c>
       <c r="H392" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I392" s="0" t="s">
         <v>21</v>
@@ -20346,7 +20346,7 @@
         <v>20</v>
       </c>
       <c r="H402" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I402" s="0" t="s">
         <v>21</v>
@@ -25131,7 +25131,7 @@
         <v>20</v>
       </c>
       <c r="H567" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I567" s="0" t="s">
         <v>21</v>
@@ -25421,7 +25421,7 @@
         <v>20</v>
       </c>
       <c r="H577" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I577" s="0" t="s">
         <v>21</v>
@@ -28901,7 +28901,7 @@
         <v>848</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -35774,7 +35774,7 @@
         <v>20</v>
       </c>
       <c r="H934" s="3" t="n">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="I934" s="0" t="s">
         <v>21</v>
@@ -36855,7 +36855,7 @@
     </row>
     <row r="972" spans="8:8" customHeight="1">
       <c r="H972" s="3" t="n">
-        <v>10107</v>
+        <v>10127</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -12980,7 +12980,7 @@
         <v>20</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>21</v>
@@ -14430,7 +14430,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -14807,7 +14807,7 @@
         <v>20</v>
       </c>
       <c r="H211" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I211" s="0" t="s">
         <v>21</v>
@@ -15068,7 +15068,7 @@
         <v>20</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I220" s="0" t="s">
         <v>21</v>
@@ -15445,7 +15445,7 @@
         <v>20</v>
       </c>
       <c r="H233" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I233" s="0" t="s">
         <v>21</v>
@@ -18519,7 +18519,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18548,7 +18548,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -19534,7 +19534,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -19563,7 +19563,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -20230,7 +20230,7 @@
         <v>20</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I398" s="0" t="s">
         <v>21</v>
@@ -20810,7 +20810,7 @@
         <v>848</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I418" s="0" t="s">
         <v>21</v>
@@ -21448,7 +21448,7 @@
         <v>391</v>
       </c>
       <c r="H440" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I440" s="0" t="s">
         <v>21</v>
@@ -21854,7 +21854,7 @@
         <v>391</v>
       </c>
       <c r="H454" s="3" t="n">
-        <v>-6343</v>
+        <v>-6349</v>
       </c>
       <c r="I454" s="0" t="s">
         <v>21</v>
@@ -22202,7 +22202,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22318,7 +22318,7 @@
         <v>391</v>
       </c>
       <c r="H470" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I470" s="0" t="s">
         <v>21</v>
@@ -22347,7 +22347,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22840,7 +22840,7 @@
         <v>391</v>
       </c>
       <c r="H488" s="3" t="n">
-        <v>-387</v>
+        <v>-397</v>
       </c>
       <c r="I488" s="0" t="s">
         <v>21</v>
@@ -23014,7 +23014,7 @@
         <v>391</v>
       </c>
       <c r="H494" s="3" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="I494" s="0" t="s">
         <v>21</v>
@@ -23449,7 +23449,7 @@
         <v>391</v>
       </c>
       <c r="H509" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I509" s="0" t="s">
         <v>21</v>
@@ -23507,7 +23507,7 @@
         <v>391</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I511" s="0" t="s">
         <v>21</v>
@@ -23710,7 +23710,7 @@
         <v>391</v>
       </c>
       <c r="H518" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I518" s="0" t="s">
         <v>21</v>
@@ -24754,7 +24754,7 @@
         <v>391</v>
       </c>
       <c r="H554" s="3" t="n">
-        <v>713</v>
+        <v>663</v>
       </c>
       <c r="I554" s="0" t="s">
         <v>21</v>
@@ -25566,7 +25566,7 @@
         <v>391</v>
       </c>
       <c r="H582" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I582" s="0" t="s">
         <v>21</v>
@@ -25595,7 +25595,7 @@
         <v>391</v>
       </c>
       <c r="H583" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I583" s="0" t="s">
         <v>21</v>
@@ -25624,7 +25624,7 @@
         <v>391</v>
       </c>
       <c r="H584" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I584" s="0" t="s">
         <v>21</v>
@@ -28582,7 +28582,7 @@
         <v>391</v>
       </c>
       <c r="H686" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I686" s="0" t="s">
         <v>21</v>
@@ -28669,7 +28669,7 @@
         <v>833</v>
       </c>
       <c r="H689" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I689" s="0" t="s">
         <v>834</v>
@@ -28901,7 +28901,7 @@
         <v>848</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -28959,7 +28959,7 @@
         <v>848</v>
       </c>
       <c r="H699" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I699" s="0" t="s">
         <v>21</v>
@@ -30438,7 +30438,7 @@
         <v>848</v>
       </c>
       <c r="H750" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I750" s="0" t="s">
         <v>21</v>
@@ -30989,7 +30989,7 @@
         <v>391</v>
       </c>
       <c r="H769" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I769" s="0" t="s">
         <v>834</v>
@@ -31569,7 +31569,7 @@
         <v>391</v>
       </c>
       <c r="H789" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I789" s="0" t="s">
         <v>21</v>
@@ -35687,7 +35687,7 @@
         <v>391</v>
       </c>
       <c r="H931" s="3" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="I931" s="0" t="s">
         <v>21</v>
@@ -35774,7 +35774,7 @@
         <v>20</v>
       </c>
       <c r="H934" s="3" t="n">
-        <v>-16</v>
+        <v>-28</v>
       </c>
       <c r="I934" s="0" t="s">
         <v>21</v>
@@ -35977,7 +35977,7 @@
         <v>391</v>
       </c>
       <c r="H941" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I941" s="0" t="s">
         <v>21</v>
@@ -36855,7 +36855,7 @@
     </row>
     <row r="972" spans="8:8" customHeight="1">
       <c r="H972" s="3" t="n">
-        <v>10127</v>
+        <v>9998</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>26 September 2026</t>
+    <t>27 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12806,7 +12806,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -36855,7 +36855,7 @@
     </row>
     <row r="972" spans="8:8" customHeight="1">
       <c r="H972" s="3" t="n">
-        <v>9998</v>
+        <v>9997</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -12806,7 +12806,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -12980,7 +12980,7 @@
         <v>20</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>21</v>
@@ -13386,7 +13386,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -15938,7 +15938,7 @@
         <v>20</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I250" s="0" t="s">
         <v>21</v>
@@ -16692,7 +16692,7 @@
         <v>20</v>
       </c>
       <c r="H276" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I276" s="0" t="s">
         <v>21</v>
@@ -20056,7 +20056,7 @@
         <v>20</v>
       </c>
       <c r="H392" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I392" s="0" t="s">
         <v>21</v>
@@ -20288,7 +20288,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -36855,7 +36855,7 @@
     </row>
     <row r="972" spans="8:8" customHeight="1">
       <c r="H972" s="3" t="n">
-        <v>9997</v>
+        <v>9988</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>27 September 2026</t>
+    <t>28 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12806,7 +12806,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -16344,7 +16344,7 @@
         <v>20</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I264" s="0" t="s">
         <v>21</v>
@@ -36855,7 +36855,7 @@
     </row>
     <row r="972" spans="8:8" customHeight="1">
       <c r="H972" s="3" t="n">
-        <v>9988</v>
+        <v>9986</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -3172,631 +3172,631 @@
     <t>PEPSI 345 ML PET</t>
   </si>
   <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">3906556342267</t>
+    </r>
+  </si>
+  <si>
+    <t>PLOYA ดอกเห็ด 4มม</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">5800218202218</t>
+    </r>
+  </si>
+  <si>
+    <t>PLOYA ดอกเห็ด 6มม</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">7252083341306</t>
+    </r>
+  </si>
+  <si>
+    <t>PLOYA ดอกเห็ด 9มม</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010015</t>
+    </r>
+  </si>
+  <si>
+    <t>SET แทงใยไหม</t>
+  </si>
+  <si>
+    <t>เซท</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">PLU4135648313</t>
+    </r>
+  </si>
+  <si>
+    <t>TAKARA สายลม PVC ดำ/เรียบ (1/2)</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010205</t>
+    </r>
+  </si>
+  <si>
+    <t>TAKARA สายลมดำผิวเรียบ 3ชั้น(1/2)</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010204</t>
+    </r>
+  </si>
+  <si>
+    <t>TAKARA สายลมดำผิวเรียบ 3ชั้น(3/8)</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010203</t>
+    </r>
+  </si>
+  <si>
+    <t>TAKARA สายลมดำผิวเรียบ 3ชั้น(5/16)</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">PLU7651352486</t>
+    </r>
+  </si>
+  <si>
+    <t>TAKARA สายลมพียู สายโพลียูรีเทน 2.5x4</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">PLU7281158565</t>
+    </r>
+  </si>
+  <si>
+    <t>TAKARA สายลมพียู สายโพลียูรีเทน 4x6</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">PLU2275768365</t>
+    </r>
+  </si>
+  <si>
+    <t>TAKARA สายลมพียู สายโพลียูรีเทน 5x8</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">PLU8471760176</t>
+    </r>
+  </si>
+  <si>
+    <t>TAKARA สายลมพียู สายโพลียูรีเทน 6.5x10</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">PLU4203618056</t>
+    </r>
+  </si>
+  <si>
+    <t>TAKARA สายลมพียู สายโพลียูรีเทน 8x12</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010145</t>
+    </r>
+  </si>
+  <si>
+    <t>TJ-1</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010141</t>
+    </r>
+  </si>
+  <si>
+    <t>TJ-10HD</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010142</t>
+    </r>
+  </si>
+  <si>
+    <t>TJ-12</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">5125728400303</t>
+    </r>
+  </si>
+  <si>
+    <t>TJ-14HD</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010144</t>
+    </r>
+  </si>
+  <si>
+    <t>TJ-2</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">3517150546460</t>
+    </r>
+  </si>
+  <si>
+    <t>TJ-3</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">4989006195521</t>
+    </r>
+  </si>
+  <si>
+    <t>TJ-4</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010143</t>
+    </r>
+  </si>
+  <si>
+    <t>TJ-5</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">7144771489791</t>
+    </r>
+  </si>
+  <si>
+    <t>TJ-6</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">6822663488173</t>
+    </r>
+  </si>
+  <si>
+    <t>US 32 มม</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010001</t>
+    </r>
+  </si>
+  <si>
+    <t>US 42 มม</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010002</t>
+    </r>
+  </si>
+  <si>
+    <t>US 58 มม</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010003</t>
+    </r>
+  </si>
+  <si>
+    <t>US 80 มม</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851717020155</t>
+    </r>
+  </si>
+  <si>
+    <t>Y - ดัชชี่ รสถั่วและเม็ดบัว</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851717020124</t>
+    </r>
+  </si>
+  <si>
+    <t>Y - ดัชชี่ รสผลไม้รวม</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851717020148</t>
+    </r>
+  </si>
+  <si>
+    <t>Y - ดัชชี่ รสวุ้นมะพร้าว </t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851717020117</t>
+    </r>
+  </si>
+  <si>
+    <t>Y - ดัชชี่ รสสตรอเบอร์รี่ </t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851717020087</t>
+    </r>
+  </si>
+  <si>
+    <t>Y - ดัชชี่ ออริจินัล </t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851717030017</t>
+    </r>
+  </si>
+  <si>
+    <t>Y - ดัชมิลล์  สตรอเบอร์รี่  100 มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851717030178</t>
+    </r>
+  </si>
+  <si>
+    <t>Y - นมเปรี้ยว บลูเบอร์รี่</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851717030079</t>
+    </r>
+  </si>
+  <si>
+    <t>Y - นมเปรี้ยว ผลไม้รวม </t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851717030048</t>
+    </r>
+  </si>
+  <si>
+    <t>Y - นมเปรี้ยว รสส้ม </t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">11010014</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - กระดาษยาสูบ ชาว หมาลาย</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">5771760411471</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - กระดาษยาสูบ บาง</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">7843046241227</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - กระดาษยาสูบ แถมฟรี</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">11010015</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - กระดาษยาสูบ แมว</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">95509747</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - บุหรี่ L&amp;M เขียว 7.1</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">95509730</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - บุหรี่ L&amp;M แดง 7.1</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8850170000803</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - บุหรี่ SMS เขียว</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8850170000797</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - บุหรี่ SMS แดง</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8850170001800</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - บุหรี่ Wonder S เขียว</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8850170001794</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - บุหรี่ Wonder S แดง</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8857200307819</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - ยาเส้น รุ่งอรุณ</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8859441400243</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - ยาเส้น แมว เขียว 22g</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8859441400250</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - ยาเส้น แมว แดง22g</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8850486100372</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา ขาว 35ดีกรี ไผ่ทอง 330มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8854791000419</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา ขาว 40ดีกรี รวงข้าว 330มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8850793001553</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา ขาว เซี่ยงชุน 35ดีกรี 625มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8859361300241</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา ข้าวหอม 35ดีกรี 330มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8859361300258</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา ข้าวหอม 40ดีกรี 330มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8855155000304</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา นิยมไทยสุราข้าวหอมพิเศษ 40ดีกรี 330มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8858820900022</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา รีเจนซี่แบน 350มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8852388000620</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา หงส์ทอง 35ดีกรี 350มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8852388000613</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา หงส์ทอง 35ดีกรี 700มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8855155000748</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา เบลนด์ 285 ซิกเนเจอร์เบลนด์สปิริต 700มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8855155000700</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา เบลนด์ 285 เบลนด์สปิริต 700มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851707000174</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา แสงโสม เหรียญทอง 300มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851707000181</t>
+    </r>
+  </si>
+  <si>
+    <t>Z - สุรา แสงโสม เหรียญทอง 700มล.</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">https://lin.ee/73nvNpV</t>
+    </r>
+  </si>
+  <si>
+    <t>กระศาษเช็ดหน้า เซลล็อกพิวริฟาย</t>
+  </si>
+  <si>
+    <t>Uncategory</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">2737227119435</t>
+    </r>
+  </si>
+  <si>
+    <t>กล่องยายจิ๋ว</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">4178643741120</t>
+    </r>
+  </si>
+  <si>
+    <t>กะทะ เปอร์เซนต์</t>
+  </si>
+  <si>
+    <t>ร้านสุพจน์การยาง</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">2613507452401</t>
+    </r>
+  </si>
+  <si>
+    <t>กะทะ ใหม่</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010012</t>
+    </r>
+  </si>
+  <si>
+    <t>กาวดำ</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010013</t>
+    </r>
+  </si>
+  <si>
+    <t>กาวดำ กันซึม</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">99010014</t>
+    </r>
+  </si>
+  <si>
+    <t>กาวปะ MR</t>
+  </si>
+  <si>
     <t>อุปกรณ์ปะยาง MR</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">3906556342267</t>
-    </r>
-  </si>
-  <si>
-    <t>PLOYA ดอกเห็ด 4มม</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">5800218202218</t>
-    </r>
-  </si>
-  <si>
-    <t>PLOYA ดอกเห็ด 6มม</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">7252083341306</t>
-    </r>
-  </si>
-  <si>
-    <t>PLOYA ดอกเห็ด 9มม</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010015</t>
-    </r>
-  </si>
-  <si>
-    <t>SET แทงใยไหม</t>
-  </si>
-  <si>
-    <t>เซท</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">PLU4135648313</t>
-    </r>
-  </si>
-  <si>
-    <t>TAKARA สายลม PVC ดำ/เรียบ (1/2)</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010205</t>
-    </r>
-  </si>
-  <si>
-    <t>TAKARA สายลมดำผิวเรียบ 3ชั้น(1/2)</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010204</t>
-    </r>
-  </si>
-  <si>
-    <t>TAKARA สายลมดำผิวเรียบ 3ชั้น(3/8)</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010203</t>
-    </r>
-  </si>
-  <si>
-    <t>TAKARA สายลมดำผิวเรียบ 3ชั้น(5/16)</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">PLU7651352486</t>
-    </r>
-  </si>
-  <si>
-    <t>TAKARA สายลมพียู สายโพลียูรีเทน 2.5x4</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">PLU7281158565</t>
-    </r>
-  </si>
-  <si>
-    <t>TAKARA สายลมพียู สายโพลียูรีเทน 4x6</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">PLU2275768365</t>
-    </r>
-  </si>
-  <si>
-    <t>TAKARA สายลมพียู สายโพลียูรีเทน 5x8</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">PLU8471760176</t>
-    </r>
-  </si>
-  <si>
-    <t>TAKARA สายลมพียู สายโพลียูรีเทน 6.5x10</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">PLU4203618056</t>
-    </r>
-  </si>
-  <si>
-    <t>TAKARA สายลมพียู สายโพลียูรีเทน 8x12</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010145</t>
-    </r>
-  </si>
-  <si>
-    <t>TJ-1</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010141</t>
-    </r>
-  </si>
-  <si>
-    <t>TJ-10HD</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010142</t>
-    </r>
-  </si>
-  <si>
-    <t>TJ-12</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">5125728400303</t>
-    </r>
-  </si>
-  <si>
-    <t>TJ-14HD</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010144</t>
-    </r>
-  </si>
-  <si>
-    <t>TJ-2</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">3517150546460</t>
-    </r>
-  </si>
-  <si>
-    <t>TJ-3</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">4989006195521</t>
-    </r>
-  </si>
-  <si>
-    <t>TJ-4</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010143</t>
-    </r>
-  </si>
-  <si>
-    <t>TJ-5</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">7144771489791</t>
-    </r>
-  </si>
-  <si>
-    <t>TJ-6</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">6822663488173</t>
-    </r>
-  </si>
-  <si>
-    <t>US 32 มม</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010001</t>
-    </r>
-  </si>
-  <si>
-    <t>US 42 มม</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010002</t>
-    </r>
-  </si>
-  <si>
-    <t>US 58 มม</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010003</t>
-    </r>
-  </si>
-  <si>
-    <t>US 80 มม</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8851717020155</t>
-    </r>
-  </si>
-  <si>
-    <t>Y - ดัชชี่ รสถั่วและเม็ดบัว</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8851717020124</t>
-    </r>
-  </si>
-  <si>
-    <t>Y - ดัชชี่ รสผลไม้รวม</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8851717020148</t>
-    </r>
-  </si>
-  <si>
-    <t>Y - ดัชชี่ รสวุ้นมะพร้าว </t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8851717020117</t>
-    </r>
-  </si>
-  <si>
-    <t>Y - ดัชชี่ รสสตรอเบอร์รี่ </t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8851717020087</t>
-    </r>
-  </si>
-  <si>
-    <t>Y - ดัชชี่ ออริจินัล </t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8851717030017</t>
-    </r>
-  </si>
-  <si>
-    <t>Y - ดัชมิลล์  สตรอเบอร์รี่  100 มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8851717030178</t>
-    </r>
-  </si>
-  <si>
-    <t>Y - นมเปรี้ยว บลูเบอร์รี่</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8851717030079</t>
-    </r>
-  </si>
-  <si>
-    <t>Y - นมเปรี้ยว ผลไม้รวม </t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8851717030048</t>
-    </r>
-  </si>
-  <si>
-    <t>Y - นมเปรี้ยว รสส้ม </t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">11010014</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - กระดาษยาสูบ ชาว หมาลาย</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">5771760411471</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - กระดาษยาสูบ บาง</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">7843046241227</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - กระดาษยาสูบ แถมฟรี</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">11010015</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - กระดาษยาสูบ แมว</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">95509747</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - บุหรี่ L&amp;M เขียว 7.1</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">95509730</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - บุหรี่ L&amp;M แดง 7.1</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8850170000803</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - บุหรี่ SMS เขียว</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8850170000797</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - บุหรี่ SMS แดง</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8850170001800</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - บุหรี่ Wonder S เขียว</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8850170001794</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - บุหรี่ Wonder S แดง</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8857200307819</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - ยาเส้น รุ่งอรุณ</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8859441400243</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - ยาเส้น แมว เขียว 22g</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8859441400250</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - ยาเส้น แมว แดง22g</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8850486100372</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา ขาว 35ดีกรี ไผ่ทอง 330มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8854791000419</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา ขาว 40ดีกรี รวงข้าว 330มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8850793001553</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา ขาว เซี่ยงชุน 35ดีกรี 625มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8859361300241</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา ข้าวหอม 35ดีกรี 330มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8859361300258</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา ข้าวหอม 40ดีกรี 330มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8855155000304</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา นิยมไทยสุราข้าวหอมพิเศษ 40ดีกรี 330มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8858820900022</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา รีเจนซี่แบน 350มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8852388000620</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา หงส์ทอง 35ดีกรี 350มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8852388000613</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา หงส์ทอง 35ดีกรี 700มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8855155000748</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา เบลนด์ 285 ซิกเนเจอร์เบลนด์สปิริต 700มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8855155000700</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา เบลนด์ 285 เบลนด์สปิริต 700มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8851707000174</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา แสงโสม เหรียญทอง 300มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">8851707000181</t>
-    </r>
-  </si>
-  <si>
-    <t>Z - สุรา แสงโสม เหรียญทอง 700มล.</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">https://lin.ee/73nvNpV</t>
-    </r>
-  </si>
-  <si>
-    <t>กระศาษเช็ดหน้า เซลล็อกพิวริฟาย</t>
-  </si>
-  <si>
-    <t>Uncategory</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">2737227119435</t>
-    </r>
-  </si>
-  <si>
-    <t>กล่องยายจิ๋ว</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">4178643741120</t>
-    </r>
-  </si>
-  <si>
-    <t>กะทะ เปอร์เซนต์</t>
-  </si>
-  <si>
-    <t>ร้านสุพจน์การยาง</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">2613507452401</t>
-    </r>
-  </si>
-  <si>
-    <t>กะทะ ใหม่</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010012</t>
-    </r>
-  </si>
-  <si>
-    <t>กาวดำ</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010013</t>
-    </r>
-  </si>
-  <si>
-    <t>กาวดำ กันซึม</t>
-  </si>
-  <si>
-    <r>
-      <rPr/>
-      <t xml:space="preserve">99010014</t>
-    </r>
-  </si>
-  <si>
-    <t>กาวปะ MR</t>
   </si>
   <si>
     <r>
@@ -18439,7 +18439,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18555,7 +18555,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18900,7 +18900,7 @@
         <v>19</v>
       </c>
       <c r="G351" s="2" t="s">
-        <v>710</v>
+        <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
         <v>-1</v>
@@ -18914,10 +18914,10 @@
         <v>344</v>
       </c>
       <c r="B352" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C352" s="2" t="s">
         <v>711</v>
-      </c>
-      <c r="C352" s="2" t="s">
-        <v>712</v>
       </c>
       <c r="D352" s="3" t="n">
         <v>370</v>
@@ -18943,10 +18943,10 @@
         <v>345</v>
       </c>
       <c r="B353" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C353" s="2" t="s">
         <v>713</v>
-      </c>
-      <c r="C353" s="2" t="s">
-        <v>714</v>
       </c>
       <c r="D353" s="3" t="n">
         <v>420</v>
@@ -18972,10 +18972,10 @@
         <v>346</v>
       </c>
       <c r="B354" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="C354" s="2" t="s">
         <v>715</v>
-      </c>
-      <c r="C354" s="2" t="s">
-        <v>716</v>
       </c>
       <c r="D354" s="3" t="n">
         <v>500</v>
@@ -19001,10 +19001,10 @@
         <v>347</v>
       </c>
       <c r="B355" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="C355" s="2" t="s">
         <v>717</v>
-      </c>
-      <c r="C355" s="2" t="s">
-        <v>718</v>
       </c>
       <c r="D355" s="3" t="n">
         <v>200</v>
@@ -19013,7 +19013,7 @@
         <v>50</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G355" s="2" t="s">
         <v>391</v>
@@ -19030,10 +19030,10 @@
         <v>348</v>
       </c>
       <c r="B356" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="C356" s="2" t="s">
         <v>720</v>
-      </c>
-      <c r="C356" s="2" t="s">
-        <v>721</v>
       </c>
       <c r="D356" s="3" t="n">
         <v>60</v>
@@ -19059,10 +19059,10 @@
         <v>349</v>
       </c>
       <c r="B357" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="C357" s="2" t="s">
         <v>722</v>
-      </c>
-      <c r="C357" s="2" t="s">
-        <v>723</v>
       </c>
       <c r="D357" s="3" t="n">
         <v>80</v>
@@ -19088,10 +19088,10 @@
         <v>350</v>
       </c>
       <c r="B358" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="C358" s="2" t="s">
         <v>724</v>
-      </c>
-      <c r="C358" s="2" t="s">
-        <v>725</v>
       </c>
       <c r="D358" s="3" t="n">
         <v>60</v>
@@ -19117,10 +19117,10 @@
         <v>351</v>
       </c>
       <c r="B359" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="C359" s="2" t="s">
         <v>726</v>
-      </c>
-      <c r="C359" s="2" t="s">
-        <v>727</v>
       </c>
       <c r="D359" s="3" t="n">
         <v>50</v>
@@ -19146,10 +19146,10 @@
         <v>352</v>
       </c>
       <c r="B360" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C360" s="2" t="s">
         <v>728</v>
-      </c>
-      <c r="C360" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="D360" s="3" t="n">
         <v>10</v>
@@ -19175,10 +19175,10 @@
         <v>353</v>
       </c>
       <c r="B361" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="C361" s="2" t="s">
         <v>730</v>
-      </c>
-      <c r="C361" s="2" t="s">
-        <v>731</v>
       </c>
       <c r="D361" s="3" t="n">
         <v>15</v>
@@ -19204,10 +19204,10 @@
         <v>354</v>
       </c>
       <c r="B362" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C362" s="2" t="s">
         <v>732</v>
-      </c>
-      <c r="C362" s="2" t="s">
-        <v>733</v>
       </c>
       <c r="D362" s="3" t="n">
         <v>20</v>
@@ -19233,10 +19233,10 @@
         <v>355</v>
       </c>
       <c r="B363" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="C363" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="C363" s="2" t="s">
-        <v>735</v>
       </c>
       <c r="D363" s="3" t="n">
         <v>30</v>
@@ -19262,10 +19262,10 @@
         <v>356</v>
       </c>
       <c r="B364" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="C364" s="2" t="s">
         <v>736</v>
-      </c>
-      <c r="C364" s="2" t="s">
-        <v>737</v>
       </c>
       <c r="D364" s="3" t="n">
         <v>40</v>
@@ -19291,10 +19291,10 @@
         <v>357</v>
       </c>
       <c r="B365" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="C365" s="2" t="s">
         <v>738</v>
-      </c>
-      <c r="C365" s="2" t="s">
-        <v>739</v>
       </c>
       <c r="D365" s="3" t="n">
         <v>320</v>
@@ -19320,10 +19320,10 @@
         <v>358</v>
       </c>
       <c r="B366" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="C366" s="2" t="s">
         <v>740</v>
-      </c>
-      <c r="C366" s="2" t="s">
-        <v>741</v>
       </c>
       <c r="D366" s="3" t="n">
         <v>350</v>
@@ -19349,10 +19349,10 @@
         <v>359</v>
       </c>
       <c r="B367" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="C367" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="C367" s="2" t="s">
-        <v>743</v>
       </c>
       <c r="D367" s="3" t="n">
         <v>350</v>
@@ -19378,10 +19378,10 @@
         <v>360</v>
       </c>
       <c r="B368" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C368" s="2" t="s">
         <v>744</v>
-      </c>
-      <c r="C368" s="2" t="s">
-        <v>745</v>
       </c>
       <c r="D368" s="3" t="n">
         <v>350</v>
@@ -19407,10 +19407,10 @@
         <v>361</v>
       </c>
       <c r="B369" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="C369" s="2" t="s">
         <v>746</v>
-      </c>
-      <c r="C369" s="2" t="s">
-        <v>747</v>
       </c>
       <c r="D369" s="3" t="n">
         <v>200</v>
@@ -19436,10 +19436,10 @@
         <v>362</v>
       </c>
       <c r="B370" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C370" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="C370" s="2" t="s">
-        <v>749</v>
       </c>
       <c r="D370" s="3" t="n">
         <v>200</v>
@@ -19465,10 +19465,10 @@
         <v>363</v>
       </c>
       <c r="B371" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="C371" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="C371" s="2" t="s">
-        <v>751</v>
       </c>
       <c r="D371" s="3" t="n">
         <v>350</v>
@@ -19494,10 +19494,10 @@
         <v>364</v>
       </c>
       <c r="B372" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="C372" s="2" t="s">
         <v>752</v>
-      </c>
-      <c r="C372" s="2" t="s">
-        <v>753</v>
       </c>
       <c r="D372" s="3" t="n">
         <v>400</v>
@@ -19523,10 +19523,10 @@
         <v>365</v>
       </c>
       <c r="B373" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="C373" s="2" t="s">
         <v>754</v>
-      </c>
-      <c r="C373" s="2" t="s">
-        <v>755</v>
       </c>
       <c r="D373" s="3" t="n">
         <v>450</v>
@@ -19552,10 +19552,10 @@
         <v>366</v>
       </c>
       <c r="B374" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="C374" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="C374" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="D374" s="3" t="n">
         <v>320</v>
@@ -19581,10 +19581,10 @@
         <v>367</v>
       </c>
       <c r="B375" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="C375" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="C375" s="2" t="s">
-        <v>759</v>
       </c>
       <c r="D375" s="3" t="n">
         <v>320</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19610,10 +19610,10 @@
         <v>368</v>
       </c>
       <c r="B376" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="C376" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="C376" s="2" t="s">
-        <v>761</v>
       </c>
       <c r="D376" s="3" t="n">
         <v>320</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -19639,10 +19639,10 @@
         <v>369</v>
       </c>
       <c r="B377" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C377" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="C377" s="2" t="s">
-        <v>763</v>
       </c>
       <c r="D377" s="3" t="n">
         <v>320</v>
@@ -19668,10 +19668,10 @@
         <v>370</v>
       </c>
       <c r="B378" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="C378" s="2" t="s">
         <v>764</v>
-      </c>
-      <c r="C378" s="2" t="s">
-        <v>765</v>
       </c>
       <c r="D378" s="3" t="n">
         <v>15</v>
@@ -19697,10 +19697,10 @@
         <v>371</v>
       </c>
       <c r="B379" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="C379" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="C379" s="2" t="s">
-        <v>767</v>
       </c>
       <c r="D379" s="3" t="n">
         <v>15</v>
@@ -19726,10 +19726,10 @@
         <v>372</v>
       </c>
       <c r="B380" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="C380" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="C380" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="D380" s="3" t="n">
         <v>15</v>
@@ -19755,10 +19755,10 @@
         <v>373</v>
       </c>
       <c r="B381" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C381" s="2" t="s">
         <v>770</v>
-      </c>
-      <c r="C381" s="2" t="s">
-        <v>771</v>
       </c>
       <c r="D381" s="3" t="n">
         <v>15</v>
@@ -19784,10 +19784,10 @@
         <v>374</v>
       </c>
       <c r="B382" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C382" s="2" t="s">
         <v>772</v>
-      </c>
-      <c r="C382" s="2" t="s">
-        <v>773</v>
       </c>
       <c r="D382" s="3" t="n">
         <v>15</v>
@@ -19813,10 +19813,10 @@
         <v>375</v>
       </c>
       <c r="B383" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C383" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="C383" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="D383" s="3" t="n">
         <v>8</v>
@@ -19842,10 +19842,10 @@
         <v>376</v>
       </c>
       <c r="B384" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="C384" s="2" t="s">
         <v>776</v>
-      </c>
-      <c r="C384" s="2" t="s">
-        <v>777</v>
       </c>
       <c r="D384" s="3" t="n">
         <v>8</v>
@@ -19871,10 +19871,10 @@
         <v>377</v>
       </c>
       <c r="B385" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C385" s="2" t="s">
         <v>778</v>
-      </c>
-      <c r="C385" s="2" t="s">
-        <v>779</v>
       </c>
       <c r="D385" s="3" t="n">
         <v>8</v>
@@ -19900,10 +19900,10 @@
         <v>378</v>
       </c>
       <c r="B386" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C386" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="C386" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="D386" s="3" t="n">
         <v>8</v>
@@ -19929,10 +19929,10 @@
         <v>379</v>
       </c>
       <c r="B387" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C387" s="2" t="s">
         <v>782</v>
-      </c>
-      <c r="C387" s="2" t="s">
-        <v>783</v>
       </c>
       <c r="D387" s="3" t="n">
         <v>2</v>
@@ -19958,10 +19958,10 @@
         <v>380</v>
       </c>
       <c r="B388" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C388" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="C388" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="D388" s="3" t="n">
         <v>1</v>
@@ -19987,10 +19987,10 @@
         <v>381</v>
       </c>
       <c r="B389" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C389" s="2" t="s">
         <v>786</v>
-      </c>
-      <c r="C389" s="2" t="s">
-        <v>787</v>
       </c>
       <c r="D389" s="3" t="n">
         <v>0</v>
@@ -20016,10 +20016,10 @@
         <v>382</v>
       </c>
       <c r="B390" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C390" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="C390" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="D390" s="3" t="n">
         <v>1</v>
@@ -20045,10 +20045,10 @@
         <v>383</v>
       </c>
       <c r="B391" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C391" s="2" t="s">
         <v>790</v>
-      </c>
-      <c r="C391" s="2" t="s">
-        <v>791</v>
       </c>
       <c r="D391" s="3" t="n">
         <v>75</v>
@@ -20074,10 +20074,10 @@
         <v>384</v>
       </c>
       <c r="B392" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C392" s="2" t="s">
         <v>792</v>
-      </c>
-      <c r="C392" s="2" t="s">
-        <v>793</v>
       </c>
       <c r="D392" s="3" t="n">
         <v>75</v>
@@ -20103,10 +20103,10 @@
         <v>385</v>
       </c>
       <c r="B393" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C393" s="2" t="s">
         <v>794</v>
-      </c>
-      <c r="C393" s="2" t="s">
-        <v>795</v>
       </c>
       <c r="D393" s="3" t="n">
         <v>70</v>
@@ -20132,10 +20132,10 @@
         <v>386</v>
       </c>
       <c r="B394" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C394" s="2" t="s">
         <v>796</v>
-      </c>
-      <c r="C394" s="2" t="s">
-        <v>797</v>
       </c>
       <c r="D394" s="3" t="n">
         <v>70</v>
@@ -20161,10 +20161,10 @@
         <v>387</v>
       </c>
       <c r="B395" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C395" s="2" t="s">
         <v>798</v>
-      </c>
-      <c r="C395" s="2" t="s">
-        <v>799</v>
       </c>
       <c r="D395" s="3" t="n">
         <v>70</v>
@@ -20190,10 +20190,10 @@
         <v>388</v>
       </c>
       <c r="B396" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C396" s="2" t="s">
         <v>800</v>
-      </c>
-      <c r="C396" s="2" t="s">
-        <v>801</v>
       </c>
       <c r="D396" s="3" t="n">
         <v>70</v>
@@ -20219,10 +20219,10 @@
         <v>389</v>
       </c>
       <c r="B397" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C397" s="2" t="s">
         <v>802</v>
-      </c>
-      <c r="C397" s="2" t="s">
-        <v>803</v>
       </c>
       <c r="D397" s="3" t="n">
         <v>8</v>
@@ -20248,10 +20248,10 @@
         <v>390</v>
       </c>
       <c r="B398" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C398" s="2" t="s">
         <v>804</v>
-      </c>
-      <c r="C398" s="2" t="s">
-        <v>805</v>
       </c>
       <c r="D398" s="3" t="n">
         <v>15</v>
@@ -20277,10 +20277,10 @@
         <v>391</v>
       </c>
       <c r="B399" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C399" s="2" t="s">
         <v>806</v>
-      </c>
-      <c r="C399" s="2" t="s">
-        <v>807</v>
       </c>
       <c r="D399" s="3" t="n">
         <v>15</v>
@@ -20306,10 +20306,10 @@
         <v>392</v>
       </c>
       <c r="B400" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C400" s="2" t="s">
         <v>808</v>
-      </c>
-      <c r="C400" s="2" t="s">
-        <v>809</v>
       </c>
       <c r="D400" s="3" t="n">
         <v>65</v>
@@ -20335,10 +20335,10 @@
         <v>393</v>
       </c>
       <c r="B401" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="C401" s="2" t="s">
         <v>810</v>
-      </c>
-      <c r="C401" s="2" t="s">
-        <v>811</v>
       </c>
       <c r="D401" s="3" t="n">
         <v>70</v>
@@ -20364,10 +20364,10 @@
         <v>394</v>
       </c>
       <c r="B402" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C402" s="2" t="s">
         <v>812</v>
-      </c>
-      <c r="C402" s="2" t="s">
-        <v>813</v>
       </c>
       <c r="D402" s="3" t="n">
         <v>165</v>
@@ -20393,10 +20393,10 @@
         <v>395</v>
       </c>
       <c r="B403" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C403" s="2" t="s">
         <v>814</v>
-      </c>
-      <c r="C403" s="2" t="s">
-        <v>815</v>
       </c>
       <c r="D403" s="3" t="n">
         <v>65</v>
@@ -20422,10 +20422,10 @@
         <v>396</v>
       </c>
       <c r="B404" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C404" s="2" t="s">
         <v>816</v>
-      </c>
-      <c r="C404" s="2" t="s">
-        <v>817</v>
       </c>
       <c r="D404" s="3" t="n">
         <v>70</v>
@@ -20451,10 +20451,10 @@
         <v>397</v>
       </c>
       <c r="B405" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C405" s="2" t="s">
         <v>818</v>
-      </c>
-      <c r="C405" s="2" t="s">
-        <v>819</v>
       </c>
       <c r="D405" s="3" t="n">
         <v>65</v>
@@ -20480,10 +20480,10 @@
         <v>398</v>
       </c>
       <c r="B406" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C406" s="2" t="s">
         <v>820</v>
-      </c>
-      <c r="C406" s="2" t="s">
-        <v>821</v>
       </c>
       <c r="D406" s="3" t="n">
         <v>400</v>
@@ -20509,10 +20509,10 @@
         <v>399</v>
       </c>
       <c r="B407" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C407" s="2" t="s">
         <v>822</v>
-      </c>
-      <c r="C407" s="2" t="s">
-        <v>823</v>
       </c>
       <c r="D407" s="3" t="n">
         <v>160</v>
@@ -20538,10 +20538,10 @@
         <v>400</v>
       </c>
       <c r="B408" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C408" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="C408" s="2" t="s">
-        <v>825</v>
       </c>
       <c r="D408" s="3" t="n">
         <v>260</v>
@@ -20567,10 +20567,10 @@
         <v>401</v>
       </c>
       <c r="B409" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C409" s="2" t="s">
         <v>826</v>
-      </c>
-      <c r="C409" s="2" t="s">
-        <v>827</v>
       </c>
       <c r="D409" s="3" t="n">
         <v>325</v>
@@ -20596,10 +20596,10 @@
         <v>402</v>
       </c>
       <c r="B410" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C410" s="2" t="s">
         <v>828</v>
-      </c>
-      <c r="C410" s="2" t="s">
-        <v>829</v>
       </c>
       <c r="D410" s="3" t="n">
         <v>270</v>
@@ -20625,10 +20625,10 @@
         <v>403</v>
       </c>
       <c r="B411" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C411" s="2" t="s">
         <v>830</v>
-      </c>
-      <c r="C411" s="2" t="s">
-        <v>831</v>
       </c>
       <c r="D411" s="3" t="n">
         <v>165</v>
@@ -20654,10 +20654,10 @@
         <v>404</v>
       </c>
       <c r="B412" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C412" s="2" t="s">
         <v>832</v>
-      </c>
-      <c r="C412" s="2" t="s">
-        <v>833</v>
       </c>
       <c r="D412" s="3" t="n">
         <v>315</v>
@@ -20683,10 +20683,10 @@
         <v>405</v>
       </c>
       <c r="B413" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C413" s="2" t="s">
         <v>834</v>
-      </c>
-      <c r="C413" s="2" t="s">
-        <v>835</v>
       </c>
       <c r="D413" s="3" t="n">
         <v>20</v>
@@ -20698,13 +20698,13 @@
         <v>19</v>
       </c>
       <c r="G413" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H413" s="3" t="n">
         <v>-2</v>
       </c>
       <c r="I413" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="414" spans="1:9" customHeight="1">
@@ -20712,10 +20712,10 @@
         <v>406</v>
       </c>
       <c r="B414" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="C414" s="2" t="s">
         <v>838</v>
-      </c>
-      <c r="C414" s="2" t="s">
-        <v>839</v>
       </c>
       <c r="D414" s="3" t="n">
         <v>1</v>
@@ -20741,10 +20741,10 @@
         <v>407</v>
       </c>
       <c r="B415" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="C415" s="2" t="s">
         <v>840</v>
-      </c>
-      <c r="C415" s="2" t="s">
-        <v>841</v>
       </c>
       <c r="D415" s="3" t="n">
         <v>0</v>
@@ -20756,7 +20756,7 @@
         <v>19</v>
       </c>
       <c r="G415" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H415" s="3" t="n">
         <v>0</v>
@@ -20770,10 +20770,10 @@
         <v>408</v>
       </c>
       <c r="B416" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="C416" s="2" t="s">
         <v>843</v>
-      </c>
-      <c r="C416" s="2" t="s">
-        <v>844</v>
       </c>
       <c r="D416" s="3" t="n">
         <v>0</v>
@@ -20785,13 +20785,13 @@
         <v>19</v>
       </c>
       <c r="G416" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H416" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I416" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="417" spans="1:9" customHeight="1">
@@ -20799,10 +20799,10 @@
         <v>409</v>
       </c>
       <c r="B417" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="C417" s="2" t="s">
         <v>845</v>
-      </c>
-      <c r="C417" s="2" t="s">
-        <v>846</v>
       </c>
       <c r="D417" s="3" t="n">
         <v>220</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20828,10 +20828,10 @@
         <v>410</v>
       </c>
       <c r="B418" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="C418" s="2" t="s">
         <v>847</v>
-      </c>
-      <c r="C418" s="2" t="s">
-        <v>848</v>
       </c>
       <c r="D418" s="3" t="n">
         <v>150</v>
@@ -20857,10 +20857,10 @@
         <v>411</v>
       </c>
       <c r="B419" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C419" s="2" t="s">
         <v>849</v>
-      </c>
-      <c r="C419" s="2" t="s">
-        <v>850</v>
       </c>
       <c r="D419" s="3" t="n">
         <v>260</v>
@@ -20872,10 +20872,10 @@
         <v>689</v>
       </c>
       <c r="G419" s="2" t="s">
-        <v>710</v>
+        <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -20994,7 +20994,7 @@
         <v>0</v>
       </c>
       <c r="I423" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="424" spans="1:9" customHeight="1">
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6349</v>
+        <v>-6361.6</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -21974,13 +21974,13 @@
         <v>19</v>
       </c>
       <c r="G457" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H457" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I457" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="458" spans="1:9" customHeight="1">
@@ -22003,7 +22003,7 @@
         <v>19</v>
       </c>
       <c r="G458" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H458" s="3" t="n">
         <v>0</v>
@@ -22064,7 +22064,7 @@
         <v>391</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22183,7 +22183,7 @@
         <v>149</v>
       </c>
       <c r="I464" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="465" spans="1:9" customHeight="1">
@@ -22206,13 +22206,13 @@
         <v>19</v>
       </c>
       <c r="G465" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H465" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I465" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="466" spans="1:9" customHeight="1">
@@ -22238,7 +22238,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22412,7 +22412,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22673,7 +22673,7 @@
         <v>391</v>
       </c>
       <c r="H481" s="3" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I481" s="0" t="s">
         <v>21</v>
@@ -22966,7 +22966,7 @@
         <v>-6</v>
       </c>
       <c r="I491" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="492" spans="1:9" customHeight="1">
@@ -23131,7 +23131,7 @@
         <v>257</v>
       </c>
       <c r="F497" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G497" s="2" t="s">
         <v>391</v>
@@ -23395,7 +23395,7 @@
         <v>19</v>
       </c>
       <c r="G506" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H506" s="3" t="n">
         <v>0</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23543,7 +23543,7 @@
         <v>391</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I511" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -23775,7 +23775,7 @@
         <v>391</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I519" s="0" t="s">
         <v>21</v>
@@ -24068,7 +24068,7 @@
         <v>2</v>
       </c>
       <c r="I529" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="530" spans="1:9" customHeight="1">
@@ -24120,7 +24120,7 @@
         <v>19</v>
       </c>
       <c r="G531" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H531" s="3" t="n">
         <v>0</v>
@@ -24700,7 +24700,7 @@
         <v>19</v>
       </c>
       <c r="G551" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H551" s="3" t="n">
         <v>0</v>
@@ -25315,7 +25315,7 @@
         <v>0</v>
       </c>
       <c r="I572" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="573" spans="1:9" customHeight="1">
@@ -25512,7 +25512,7 @@
         <v>19</v>
       </c>
       <c r="G579" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H579" s="3" t="n">
         <v>0</v>
@@ -26063,7 +26063,7 @@
         <v>19</v>
       </c>
       <c r="G598" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H598" s="3" t="n">
         <v>0</v>
@@ -26092,7 +26092,7 @@
         <v>19</v>
       </c>
       <c r="G599" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H599" s="3" t="n">
         <v>0</v>
@@ -26385,7 +26385,7 @@
         <v>391</v>
       </c>
       <c r="H609" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I609" s="0" t="s">
         <v>21</v>
@@ -26469,7 +26469,7 @@
         <v>19</v>
       </c>
       <c r="G612" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H612" s="3" t="n">
         <v>-2</v>
@@ -27255,7 +27255,7 @@
         <v>391</v>
       </c>
       <c r="H639" s="3" t="n">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="I639" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -27571,7 +27571,7 @@
         <v>19</v>
       </c>
       <c r="G650" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H650" s="3" t="n">
         <v>0</v>
@@ -28035,7 +28035,7 @@
         <v>19</v>
       </c>
       <c r="G666" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H666" s="3" t="n">
         <v>0</v>
@@ -28444,7 +28444,7 @@
         <v>391</v>
       </c>
       <c r="H680" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I680" s="0" t="s">
         <v>21</v>
@@ -28702,13 +28702,13 @@
         <v>19</v>
       </c>
       <c r="G689" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="H689" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I689" s="0" t="s">
         <v>836</v>
-      </c>
-      <c r="H689" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="I689" s="0" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="690" spans="1:9" customHeight="1">
@@ -28731,13 +28731,13 @@
         <v>19</v>
       </c>
       <c r="G690" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="H690" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="I690" s="0" t="s">
         <v>836</v>
-      </c>
-      <c r="H690" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I690" s="0" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="691" spans="1:9" customHeight="1">
@@ -28760,13 +28760,13 @@
         <v>19</v>
       </c>
       <c r="G691" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="H691" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I691" s="0" t="s">
         <v>836</v>
-      </c>
-      <c r="H691" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="I691" s="0" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="692" spans="1:9" customHeight="1">
@@ -28786,7 +28786,7 @@
         <v>75</v>
       </c>
       <c r="F692" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G692" s="2" t="s">
         <v>391</v>
@@ -28934,10 +28934,10 @@
         <v>394</v>
       </c>
       <c r="G697" s="2" t="s">
-        <v>710</v>
+        <v>850</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -28963,10 +28963,10 @@
         <v>394</v>
       </c>
       <c r="G698" s="2" t="s">
-        <v>710</v>
+        <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -28992,7 +28992,7 @@
         <v>394</v>
       </c>
       <c r="G699" s="2" t="s">
-        <v>710</v>
+        <v>850</v>
       </c>
       <c r="H699" s="3" t="n">
         <v>0</v>
@@ -29021,7 +29021,7 @@
         <v>394</v>
       </c>
       <c r="G700" s="2" t="s">
-        <v>710</v>
+        <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
         <v>29</v>
@@ -29140,7 +29140,7 @@
         <v>391</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -30355,13 +30355,13 @@
         <v>19</v>
       </c>
       <c r="G746" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H746" s="3" t="n">
         <v>4</v>
       </c>
       <c r="I746" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="747" spans="1:9" customHeight="1">
@@ -30413,7 +30413,7 @@
         <v>19</v>
       </c>
       <c r="G748" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H748" s="3" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>394</v>
       </c>
       <c r="G751" s="2" t="s">
-        <v>710</v>
+        <v>850</v>
       </c>
       <c r="H751" s="3" t="n">
         <v>0</v>
@@ -30529,10 +30529,10 @@
         <v>394</v>
       </c>
       <c r="G752" s="2" t="s">
-        <v>710</v>
+        <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -30558,7 +30558,7 @@
         <v>394</v>
       </c>
       <c r="G753" s="2" t="s">
-        <v>710</v>
+        <v>850</v>
       </c>
       <c r="H753" s="3" t="n">
         <v>0</v>
@@ -30587,7 +30587,7 @@
         <v>394</v>
       </c>
       <c r="G754" s="2" t="s">
-        <v>710</v>
+        <v>850</v>
       </c>
       <c r="H754" s="3" t="n">
         <v>0</v>
@@ -30680,7 +30680,7 @@
         <v>-2</v>
       </c>
       <c r="I757" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="758" spans="1:9" customHeight="1">
@@ -30912,7 +30912,7 @@
         <v>0</v>
       </c>
       <c r="I765" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="766" spans="1:9" customHeight="1">
@@ -30941,7 +30941,7 @@
         <v>0</v>
       </c>
       <c r="I766" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="767" spans="1:9" customHeight="1">
@@ -30970,7 +30970,7 @@
         <v>0</v>
       </c>
       <c r="I767" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="768" spans="1:9" customHeight="1">
@@ -31057,7 +31057,7 @@
         <v>8</v>
       </c>
       <c r="I770" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="771" spans="1:9" customHeight="1">
@@ -31086,7 +31086,7 @@
         <v>19</v>
       </c>
       <c r="I771" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="772" spans="1:9" customHeight="1">
@@ -31115,7 +31115,7 @@
         <v>7</v>
       </c>
       <c r="I772" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="773" spans="1:9" customHeight="1">
@@ -31144,7 +31144,7 @@
         <v>10</v>
       </c>
       <c r="I773" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="774" spans="1:9" customHeight="1">
@@ -31173,7 +31173,7 @@
         <v>5</v>
       </c>
       <c r="I774" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="775" spans="1:9" customHeight="1">
@@ -31637,7 +31637,7 @@
         <v>0</v>
       </c>
       <c r="I790" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="791" spans="1:9" customHeight="1">
@@ -31985,7 +31985,7 @@
         <v>0</v>
       </c>
       <c r="I802" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="803" spans="1:9" customHeight="1">
@@ -32014,7 +32014,7 @@
         <v>0</v>
       </c>
       <c r="I803" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="804" spans="1:9" customHeight="1">
@@ -32043,7 +32043,7 @@
         <v>0</v>
       </c>
       <c r="I804" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="805" spans="1:9" customHeight="1">
@@ -32130,7 +32130,7 @@
         <v>7</v>
       </c>
       <c r="I807" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="808" spans="1:9" customHeight="1">
@@ -32159,7 +32159,7 @@
         <v>24</v>
       </c>
       <c r="I808" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="809" spans="1:9" customHeight="1">
@@ -32188,7 +32188,7 @@
         <v>7</v>
       </c>
       <c r="I809" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="810" spans="1:9" customHeight="1">
@@ -32217,7 +32217,7 @@
         <v>9</v>
       </c>
       <c r="I810" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="811" spans="1:9" customHeight="1">
@@ -32246,7 +32246,7 @@
         <v>10</v>
       </c>
       <c r="I811" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="812" spans="1:9" customHeight="1">
@@ -32536,7 +32536,7 @@
         <v>0</v>
       </c>
       <c r="I821" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="822" spans="1:9" customHeight="1">
@@ -32849,13 +32849,13 @@
         <v>19</v>
       </c>
       <c r="G832" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H832" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I832" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="833" spans="1:9" customHeight="1">
@@ -32878,13 +32878,13 @@
         <v>19</v>
       </c>
       <c r="G833" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H833" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I833" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="834" spans="1:9" customHeight="1">
@@ -32907,7 +32907,7 @@
         <v>19</v>
       </c>
       <c r="G834" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H834" s="3" t="n">
         <v>0</v>
@@ -32991,7 +32991,7 @@
         <v>40</v>
       </c>
       <c r="F837" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G837" s="2" t="s">
         <v>391</v>
@@ -33020,7 +33020,7 @@
         <v>1000</v>
       </c>
       <c r="F838" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G838" s="2" t="s">
         <v>391</v>
@@ -33078,7 +33078,7 @@
         <v>80</v>
       </c>
       <c r="F840" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="G840" s="2" t="s">
         <v>391</v>
@@ -33226,13 +33226,13 @@
         <v>19</v>
       </c>
       <c r="G845" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H845" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I845" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="846" spans="1:9" customHeight="1">
@@ -33574,7 +33574,7 @@
         <v>19</v>
       </c>
       <c r="G857" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H857" s="3" t="n">
         <v>0</v>
@@ -33603,7 +33603,7 @@
         <v>19</v>
       </c>
       <c r="G858" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H858" s="3" t="n">
         <v>0</v>
@@ -33632,7 +33632,7 @@
         <v>19</v>
       </c>
       <c r="G859" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H859" s="3" t="n">
         <v>0</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -35917,7 +35917,7 @@
         <v>20</v>
       </c>
       <c r="E938" s="3" t="n">
-        <v>14</v>
+        <v>14.33</v>
       </c>
       <c r="F938" s="2" t="s">
         <v>19</v>
@@ -35929,7 +35929,7 @@
         <v>3</v>
       </c>
       <c r="I938" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="939" spans="1:9" customHeight="1">
@@ -35984,7 +35984,7 @@
         <v>391</v>
       </c>
       <c r="H940" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I940" s="0" t="s">
         <v>21</v>
@@ -36973,7 +36973,7 @@
         <v>3</v>
       </c>
       <c r="I974" s="0" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="975" spans="1:9" customHeight="1">
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>10307</v>
+        <v>9998.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>28 September 2026</t>
+    <t>29 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -14292,7 +14292,7 @@
         <v>20</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I192" s="0" t="s">
         <v>21</v>
@@ -14408,7 +14408,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -34360,7 +34360,7 @@
         <v>391</v>
       </c>
       <c r="H884" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I884" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9998.4</v>
+        <v>9993.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9391,7 +9391,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -9420,7 +9420,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -9536,7 +9536,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I28" s="0" t="s">
         <v>21</v>
@@ -10377,7 +10377,7 @@
         <v>20</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I57" s="0" t="s">
         <v>21</v>
@@ -10406,7 +10406,7 @@
         <v>20</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I58" s="0" t="s">
         <v>21</v>
@@ -10522,7 +10522,7 @@
         <v>20</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I62" s="0" t="s">
         <v>21</v>
@@ -10812,7 +10812,7 @@
         <v>20</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I72" s="0" t="s">
         <v>21</v>
@@ -11769,7 +11769,7 @@
         <v>20</v>
       </c>
       <c r="H105" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I105" s="0" t="s">
         <v>21</v>
@@ -11972,7 +11972,7 @@
         <v>20</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I112" s="0" t="s">
         <v>21</v>
@@ -12001,7 +12001,7 @@
         <v>20</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I113" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12610,7 +12610,7 @@
         <v>20</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I134" s="0" t="s">
         <v>21</v>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -12958,7 +12958,7 @@
         <v>20</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>21</v>
@@ -13161,7 +13161,7 @@
         <v>20</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I153" s="0" t="s">
         <v>21</v>
@@ -13248,7 +13248,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -13422,7 +13422,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -13538,7 +13538,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -14176,7 +14176,7 @@
         <v>20</v>
       </c>
       <c r="H188" s="3" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="I188" s="0" t="s">
         <v>21</v>
@@ -20150,7 +20150,7 @@
         <v>20</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I394" s="0" t="s">
         <v>21</v>
@@ -20266,7 +20266,7 @@
         <v>20</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I398" s="0" t="s">
         <v>21</v>
@@ -20353,7 +20353,7 @@
         <v>20</v>
       </c>
       <c r="H401" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I401" s="0" t="s">
         <v>21</v>
@@ -20411,7 +20411,7 @@
         <v>20</v>
       </c>
       <c r="H403" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I403" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21948,7 +21948,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-482</v>
+        <v>-486</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -25196,7 +25196,7 @@
         <v>20</v>
       </c>
       <c r="H568" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I568" s="0" t="s">
         <v>21</v>
@@ -25370,7 +25370,7 @@
         <v>20</v>
       </c>
       <c r="H574" s="3" t="n">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="I574" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-741</v>
+        <v>-743</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -25921,7 +25921,7 @@
         <v>391</v>
       </c>
       <c r="H593" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I593" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28357,7 +28357,7 @@
         <v>391</v>
       </c>
       <c r="H677" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I677" s="0" t="s">
         <v>21</v>
@@ -28444,7 +28444,7 @@
         <v>391</v>
       </c>
       <c r="H680" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I680" s="0" t="s">
         <v>21</v>
@@ -28676,7 +28676,7 @@
         <v>391</v>
       </c>
       <c r="H688" s="3" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I688" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -31315,7 +31315,7 @@
         <v>391</v>
       </c>
       <c r="H779" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I779" s="0" t="s">
         <v>21</v>
@@ -31518,7 +31518,7 @@
         <v>391</v>
       </c>
       <c r="H786" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I786" s="0" t="s">
         <v>21</v>
@@ -32069,7 +32069,7 @@
         <v>391</v>
       </c>
       <c r="H805" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I805" s="0" t="s">
         <v>21</v>
@@ -33258,7 +33258,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-835</v>
+        <v>-843</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -34099,7 +34099,7 @@
         <v>391</v>
       </c>
       <c r="H875" s="3" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I875" s="0" t="s">
         <v>21</v>
@@ -34128,7 +34128,7 @@
         <v>391</v>
       </c>
       <c r="H876" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I876" s="0" t="s">
         <v>21</v>
@@ -34244,7 +34244,7 @@
         <v>391</v>
       </c>
       <c r="H880" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I880" s="0" t="s">
         <v>21</v>
@@ -35868,7 +35868,7 @@
         <v>20</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>-28</v>
+        <v>-38</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -35984,7 +35984,7 @@
         <v>391</v>
       </c>
       <c r="H940" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I940" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9993.4</v>
+        <v>9911.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14408,7 +14408,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -18439,7 +18439,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18497,7 +18497,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18555,7 +18555,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18584,7 +18584,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19483,7 +19483,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6361.6</v>
+        <v>-6372.6</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22412,7 +22412,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22528,7 +22528,7 @@
         <v>391</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>301</v>
+        <v>101</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22702,7 +22702,7 @@
         <v>391</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="I482" s="0" t="s">
         <v>21</v>
@@ -22789,7 +22789,7 @@
         <v>391</v>
       </c>
       <c r="H485" s="3" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="I485" s="0" t="s">
         <v>21</v>
@@ -22905,7 +22905,7 @@
         <v>391</v>
       </c>
       <c r="H489" s="3" t="n">
-        <v>-397</v>
+        <v>-400</v>
       </c>
       <c r="I489" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -26008,7 +26008,7 @@
         <v>391</v>
       </c>
       <c r="H596" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I596" s="0" t="s">
         <v>21</v>
@@ -26037,7 +26037,7 @@
         <v>391</v>
       </c>
       <c r="H597" s="3" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="I597" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28937,7 +28937,7 @@
         <v>850</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -30880,7 +30880,7 @@
         <v>391</v>
       </c>
       <c r="H764" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I764" s="0" t="s">
         <v>21</v>
@@ -31199,7 +31199,7 @@
         <v>391</v>
       </c>
       <c r="H775" s="3" t="n">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I775" s="0" t="s">
         <v>21</v>
@@ -31576,7 +31576,7 @@
         <v>391</v>
       </c>
       <c r="H788" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I788" s="0" t="s">
         <v>21</v>
@@ -31692,7 +31692,7 @@
         <v>391</v>
       </c>
       <c r="H792" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I792" s="0" t="s">
         <v>21</v>
@@ -32098,7 +32098,7 @@
         <v>391</v>
       </c>
       <c r="H806" s="3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I806" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9911.4</v>
+        <v>9584.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>29 September 2026</t>
+    <t>30 September 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9584.4</v>
+        <v>9583.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -1620,7 +1620,7 @@
   <si>
     <r>
       <rPr/>
-      <t xml:space="preserve">8851959144015</t>
+      <t xml:space="preserve">8851959005200</t>
     </r>
   </si>
   <si>
@@ -9304,7 +9304,7 @@
         <v>20</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I20" s="0" t="s">
         <v>21</v>
@@ -9536,7 +9536,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I28" s="0" t="s">
         <v>21</v>
@@ -10841,7 +10841,7 @@
         <v>20</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I73" s="0" t="s">
         <v>21</v>
@@ -11160,7 +11160,7 @@
         <v>20</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I84" s="0" t="s">
         <v>21</v>
@@ -11711,7 +11711,7 @@
         <v>20</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>21</v>
@@ -12059,7 +12059,7 @@
         <v>20</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12407,7 +12407,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -12639,7 +12639,7 @@
         <v>20</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I135" s="0" t="s">
         <v>21</v>
@@ -12668,7 +12668,7 @@
         <v>20</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I136" s="0" t="s">
         <v>21</v>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -13248,7 +13248,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -13886,7 +13886,7 @@
         <v>20</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>21</v>
@@ -13973,7 +13973,7 @@
         <v>20</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I181" s="0" t="s">
         <v>21</v>
@@ -15452,7 +15452,7 @@
         <v>20</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="I232" s="0" t="s">
         <v>21</v>
@@ -15742,7 +15742,7 @@
         <v>20</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I242" s="0" t="s">
         <v>21</v>
@@ -16235,7 +16235,7 @@
         <v>20</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I259" s="0" t="s">
         <v>21</v>
@@ -16844,7 +16844,7 @@
         <v>20</v>
       </c>
       <c r="H280" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I280" s="0" t="s">
         <v>21</v>
@@ -17221,7 +17221,7 @@
         <v>20</v>
       </c>
       <c r="H293" s="3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I293" s="0" t="s">
         <v>21</v>
@@ -17250,7 +17250,7 @@
         <v>20</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I294" s="0" t="s">
         <v>21</v>
@@ -20121,7 +20121,7 @@
         <v>20</v>
       </c>
       <c r="H393" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I393" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>61</v>
+        <v>205</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21716,7 +21716,7 @@
         <v>391</v>
       </c>
       <c r="H448" s="3" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I448" s="0" t="s">
         <v>21</v>
@@ -21948,7 +21948,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-486</v>
+        <v>-488</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22093,7 +22093,7 @@
         <v>391</v>
       </c>
       <c r="H461" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I461" s="0" t="s">
         <v>21</v>
@@ -22760,7 +22760,7 @@
         <v>391</v>
       </c>
       <c r="H484" s="3" t="n">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="I484" s="0" t="s">
         <v>21</v>
@@ -22789,7 +22789,7 @@
         <v>391</v>
       </c>
       <c r="H485" s="3" t="n">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="I485" s="0" t="s">
         <v>21</v>
@@ -23775,7 +23775,7 @@
         <v>391</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="I519" s="0" t="s">
         <v>21</v>
@@ -25196,7 +25196,7 @@
         <v>20</v>
       </c>
       <c r="H568" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I568" s="0" t="s">
         <v>21</v>
@@ -25341,7 +25341,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>-313</v>
+        <v>-316</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-743</v>
+        <v>-746</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -28676,7 +28676,7 @@
         <v>391</v>
       </c>
       <c r="H688" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I688" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -33258,7 +33258,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-843</v>
+        <v>-846</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -34099,7 +34099,7 @@
         <v>391</v>
       </c>
       <c r="H875" s="3" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I875" s="0" t="s">
         <v>21</v>
@@ -34302,7 +34302,7 @@
         <v>391</v>
       </c>
       <c r="H882" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I882" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9583.4</v>
+        <v>9672.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -11131,7 +11131,7 @@
         <v>20</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I83" s="0" t="s">
         <v>21</v>
@@ -14379,7 +14379,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14408,7 +14408,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14466,7 +14466,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -18439,7 +18439,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18555,7 +18555,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19483,7 +19483,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21513,7 +21513,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6372.6</v>
+        <v>-6381.6</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22412,7 +22412,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22760,7 +22760,7 @@
         <v>391</v>
       </c>
       <c r="H484" s="3" t="n">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="I484" s="0" t="s">
         <v>21</v>
@@ -22789,7 +22789,7 @@
         <v>391</v>
       </c>
       <c r="H485" s="3" t="n">
-        <v>295</v>
+        <v>265</v>
       </c>
       <c r="I485" s="0" t="s">
         <v>21</v>
@@ -23137,7 +23137,7 @@
         <v>391</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I497" s="0" t="s">
         <v>21</v>
@@ -23427,7 +23427,7 @@
         <v>391</v>
       </c>
       <c r="H507" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I507" s="0" t="s">
         <v>21</v>
@@ -23456,7 +23456,7 @@
         <v>391</v>
       </c>
       <c r="H508" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I508" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23543,7 +23543,7 @@
         <v>391</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I511" s="0" t="s">
         <v>21</v>
@@ -23775,7 +23775,7 @@
         <v>391</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I519" s="0" t="s">
         <v>21</v>
@@ -24819,7 +24819,7 @@
         <v>391</v>
       </c>
       <c r="H555" s="3" t="n">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="I555" s="0" t="s">
         <v>21</v>
@@ -26008,7 +26008,7 @@
         <v>391</v>
       </c>
       <c r="H596" s="3" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="I596" s="0" t="s">
         <v>21</v>
@@ -26037,7 +26037,7 @@
         <v>391</v>
       </c>
       <c r="H597" s="3" t="n">
-        <v>-1</v>
+        <v>-16</v>
       </c>
       <c r="I597" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28589,7 +28589,7 @@
         <v>391</v>
       </c>
       <c r="H685" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I685" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29343,7 +29343,7 @@
         <v>391</v>
       </c>
       <c r="H711" s="3" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="I711" s="0" t="s">
         <v>21</v>
@@ -30097,7 +30097,7 @@
         <v>391</v>
       </c>
       <c r="H737" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I737" s="0" t="s">
         <v>21</v>
@@ -30126,7 +30126,7 @@
         <v>391</v>
       </c>
       <c r="H738" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I738" s="0" t="s">
         <v>21</v>
@@ -30155,7 +30155,7 @@
         <v>391</v>
       </c>
       <c r="H739" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I739" s="0" t="s">
         <v>21</v>
@@ -31663,7 +31663,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -31779,7 +31779,7 @@
         <v>391</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I795" s="0" t="s">
         <v>21</v>
@@ -32504,7 +32504,7 @@
         <v>391</v>
       </c>
       <c r="H820" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I820" s="0" t="s">
         <v>21</v>
@@ -33055,7 +33055,7 @@
         <v>391</v>
       </c>
       <c r="H839" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I839" s="0" t="s">
         <v>21</v>
@@ -34099,7 +34099,7 @@
         <v>391</v>
       </c>
       <c r="H875" s="3" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I875" s="0" t="s">
         <v>21</v>
@@ -34360,7 +34360,7 @@
         <v>391</v>
       </c>
       <c r="H884" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I884" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -36100,7 +36100,7 @@
         <v>391</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I944" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9672.4</v>
+        <v>9463.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>30 September 2026</t>
+    <t>01 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9463.4</v>
+        <v>9462.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9101,7 +9101,7 @@
         <v>20</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" s="0" t="s">
         <v>21</v>
@@ -11131,7 +11131,7 @@
         <v>20</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83" s="0" t="s">
         <v>21</v>
@@ -11682,7 +11682,7 @@
         <v>20</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I102" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12610,7 +12610,7 @@
         <v>20</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I134" s="0" t="s">
         <v>21</v>
@@ -12668,7 +12668,7 @@
         <v>20</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I136" s="0" t="s">
         <v>21</v>
@@ -12726,7 +12726,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -12755,7 +12755,7 @@
         <v>20</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I139" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14466,7 +14466,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -15104,7 +15104,7 @@
         <v>20</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I220" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -20150,7 +20150,7 @@
         <v>20</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I394" s="0" t="s">
         <v>21</v>
@@ -20411,7 +20411,7 @@
         <v>20</v>
       </c>
       <c r="H403" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I403" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -23427,7 +23427,7 @@
         <v>391</v>
       </c>
       <c r="H507" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I507" s="0" t="s">
         <v>21</v>
@@ -25341,7 +25341,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>-316</v>
+        <v>-317</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -26008,7 +26008,7 @@
         <v>391</v>
       </c>
       <c r="H596" s="3" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="I596" s="0" t="s">
         <v>21</v>
@@ -26037,7 +26037,7 @@
         <v>391</v>
       </c>
       <c r="H597" s="3" t="n">
-        <v>-16</v>
+        <v>54</v>
       </c>
       <c r="I597" s="0" t="s">
         <v>21</v>
@@ -28676,7 +28676,7 @@
         <v>391</v>
       </c>
       <c r="H688" s="3" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I688" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -29749,7 +29749,7 @@
         <v>391</v>
       </c>
       <c r="H725" s="3" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I725" s="0" t="s">
         <v>21</v>
@@ -29778,7 +29778,7 @@
         <v>391</v>
       </c>
       <c r="H726" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I726" s="0" t="s">
         <v>21</v>
@@ -31663,7 +31663,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -34824,7 +34824,7 @@
         <v>391</v>
       </c>
       <c r="H900" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I900" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9462.4</v>
+        <v>9547.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -18439,7 +18439,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18613,7 +18613,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -18671,7 +18671,7 @@
         <v>391</v>
       </c>
       <c r="H343" s="3" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I343" s="0" t="s">
         <v>21</v>
@@ -19019,7 +19019,7 @@
         <v>391</v>
       </c>
       <c r="H355" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I355" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19454,7 +19454,7 @@
         <v>391</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6381.6</v>
+        <v>-6392.6</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22151,7 +22151,7 @@
         <v>391</v>
       </c>
       <c r="H463" s="3" t="n">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="I463" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -23775,7 +23775,7 @@
         <v>391</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I519" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9547.4</v>
+        <v>9470.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>01 October 2026</t>
+    <t>02 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12610,7 +12610,7 @@
         <v>20</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I134" s="0" t="s">
         <v>21</v>
@@ -12668,7 +12668,7 @@
         <v>20</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I136" s="0" t="s">
         <v>21</v>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -12871,7 +12871,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13886,7 +13886,7 @@
         <v>20</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>21</v>
@@ -16757,7 +16757,7 @@
         <v>20</v>
       </c>
       <c r="H277" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I277" s="0" t="s">
         <v>21</v>
@@ -20353,7 +20353,7 @@
         <v>20</v>
       </c>
       <c r="H401" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I401" s="0" t="s">
         <v>21</v>
@@ -20440,7 +20440,7 @@
         <v>20</v>
       </c>
       <c r="H404" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I404" s="0" t="s">
         <v>21</v>
@@ -25196,7 +25196,7 @@
         <v>20</v>
       </c>
       <c r="H568" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I568" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9470.4</v>
+        <v>9457.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9391,7 +9391,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -9420,7 +9420,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12726,7 +12726,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -12871,7 +12871,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13045,7 +13045,7 @@
         <v>20</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I149" s="0" t="s">
         <v>21</v>
@@ -13538,7 +13538,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -16844,7 +16844,7 @@
         <v>20</v>
       </c>
       <c r="H280" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I280" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -19135,7 +19135,7 @@
         <v>391</v>
       </c>
       <c r="H359" s="3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I359" s="0" t="s">
         <v>21</v>
@@ -20121,7 +20121,7 @@
         <v>20</v>
       </c>
       <c r="H393" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I393" s="0" t="s">
         <v>21</v>
@@ -20295,7 +20295,7 @@
         <v>20</v>
       </c>
       <c r="H399" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I399" s="0" t="s">
         <v>21</v>
@@ -20411,7 +20411,7 @@
         <v>20</v>
       </c>
       <c r="H403" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I403" s="0" t="s">
         <v>21</v>
@@ -25341,7 +25341,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>-317</v>
+        <v>-318</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-746</v>
+        <v>-747</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-16</v>
+        <v>-19</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -28908,7 +28908,7 @@
         <v>20</v>
       </c>
       <c r="H696" s="3" t="n">
-        <v>-164</v>
+        <v>-165</v>
       </c>
       <c r="I696" s="0" t="s">
         <v>21</v>
@@ -30822,7 +30822,7 @@
         <v>391</v>
       </c>
       <c r="H762" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I762" s="0" t="s">
         <v>21</v>
@@ -32562,7 +32562,7 @@
         <v>391</v>
       </c>
       <c r="H822" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I822" s="0" t="s">
         <v>21</v>
@@ -35955,7 +35955,7 @@
         <v>20</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9457.4</v>
+        <v>9421.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -19657,7 +19657,7 @@
         <v>391</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I377" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6392.6</v>
+        <v>-6398.6</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28444,7 +28444,7 @@
         <v>391</v>
       </c>
       <c r="H680" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I680" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30097,7 +30097,7 @@
         <v>391</v>
       </c>
       <c r="H737" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I737" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -36042,7 +36042,7 @@
         <v>391</v>
       </c>
       <c r="H942" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I942" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9421.4</v>
+        <v>9397.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>02 October 2026</t>
+    <t>03 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -16380,7 +16380,7 @@
         <v>20</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I264" s="0" t="s">
         <v>21</v>
@@ -17685,7 +17685,7 @@
         <v>20</v>
       </c>
       <c r="H309" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I309" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9397.4</v>
+        <v>9395.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9652,7 +9652,7 @@
         <v>20</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="0" t="s">
         <v>21</v>
@@ -11160,7 +11160,7 @@
         <v>20</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I84" s="0" t="s">
         <v>21</v>
@@ -11740,7 +11740,7 @@
         <v>20</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I104" s="0" t="s">
         <v>21</v>
@@ -12639,7 +12639,7 @@
         <v>20</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I135" s="0" t="s">
         <v>21</v>
@@ -12668,7 +12668,7 @@
         <v>20</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I136" s="0" t="s">
         <v>21</v>
@@ -12871,7 +12871,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13016,7 +13016,7 @@
         <v>20</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>21</v>
@@ -13132,7 +13132,7 @@
         <v>20</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I152" s="0" t="s">
         <v>21</v>
@@ -13335,7 +13335,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -20150,7 +20150,7 @@
         <v>20</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I394" s="0" t="s">
         <v>21</v>
@@ -20440,7 +20440,7 @@
         <v>20</v>
       </c>
       <c r="H404" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I404" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-19</v>
+        <v>-21</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9395.4</v>
+        <v>9378.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9304,7 +9304,7 @@
         <v>20</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="I20" s="0" t="s">
         <v>21</v>
@@ -9420,7 +9420,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -10000,7 +10000,7 @@
         <v>20</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44" s="0" t="s">
         <v>21</v>
@@ -11160,7 +11160,7 @@
         <v>20</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I84" s="0" t="s">
         <v>21</v>
@@ -11276,7 +11276,7 @@
         <v>20</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I88" s="0" t="s">
         <v>21</v>
@@ -12726,7 +12726,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -12871,7 +12871,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13393,7 +13393,7 @@
         <v>20</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I161" s="0" t="s">
         <v>21</v>
@@ -14408,7 +14408,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14466,7 +14466,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -15945,7 +15945,7 @@
         <v>20</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I249" s="0" t="s">
         <v>21</v>
@@ -17714,7 +17714,7 @@
         <v>20</v>
       </c>
       <c r="H310" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I310" s="0" t="s">
         <v>21</v>
@@ -18439,7 +18439,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19570,7 +19570,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21513,7 +21513,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6398.6</v>
+        <v>-6415.2</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22122,7 +22122,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22644,7 +22644,7 @@
         <v>391</v>
       </c>
       <c r="H480" s="3" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="I480" s="0" t="s">
         <v>21</v>
@@ -22673,7 +22673,7 @@
         <v>391</v>
       </c>
       <c r="H481" s="3" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I481" s="0" t="s">
         <v>21</v>
@@ -22702,7 +22702,7 @@
         <v>391</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="I482" s="0" t="s">
         <v>21</v>
@@ -23021,7 +23021,7 @@
         <v>391</v>
       </c>
       <c r="H493" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I493" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23543,7 +23543,7 @@
         <v>391</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I511" s="0" t="s">
         <v>21</v>
@@ -23775,7 +23775,7 @@
         <v>391</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I519" s="0" t="s">
         <v>21</v>
@@ -25921,7 +25921,7 @@
         <v>391</v>
       </c>
       <c r="H593" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I593" s="0" t="s">
         <v>21</v>
@@ -26008,7 +26008,7 @@
         <v>391</v>
       </c>
       <c r="H596" s="3" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="I596" s="0" t="s">
         <v>21</v>
@@ -26037,7 +26037,7 @@
         <v>391</v>
       </c>
       <c r="H597" s="3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I597" s="0" t="s">
         <v>21</v>
@@ -26385,7 +26385,7 @@
         <v>391</v>
       </c>
       <c r="H609" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I609" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28879,7 +28879,7 @@
         <v>391</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -28937,7 +28937,7 @@
         <v>850</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -30880,7 +30880,7 @@
         <v>391</v>
       </c>
       <c r="H764" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I764" s="0" t="s">
         <v>21</v>
@@ -31344,7 +31344,7 @@
         <v>391</v>
       </c>
       <c r="H780" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I780" s="0" t="s">
         <v>21</v>
@@ -31663,7 +31663,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -31779,7 +31779,7 @@
         <v>391</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I795" s="0" t="s">
         <v>21</v>
@@ -31953,7 +31953,7 @@
         <v>391</v>
       </c>
       <c r="H801" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I801" s="0" t="s">
         <v>21</v>
@@ -33055,7 +33055,7 @@
         <v>391</v>
       </c>
       <c r="H839" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I839" s="0" t="s">
         <v>21</v>
@@ -34302,7 +34302,7 @@
         <v>391</v>
       </c>
       <c r="H882" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I882" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9378.4</v>
+        <v>9268.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>03 October 2026</t>
+    <t>04 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -16757,7 +16757,7 @@
         <v>20</v>
       </c>
       <c r="H277" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I277" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9268.8</v>
+        <v>9266.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -13248,7 +13248,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9266.8</v>
+        <v>9265.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9681,7 +9681,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>21</v>
@@ -11276,7 +11276,7 @@
         <v>20</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I88" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9265.8</v>
+        <v>9262.8</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>04 October 2026</t>
+    <t>05 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -9391,7 +9391,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -9420,7 +9420,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -10841,7 +10841,7 @@
         <v>20</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I73" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12726,7 +12726,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -13016,7 +13016,7 @@
         <v>20</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>21</v>
@@ -13045,7 +13045,7 @@
         <v>20</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I149" s="0" t="s">
         <v>21</v>
@@ -14408,7 +14408,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14466,7 +14466,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -15307,7 +15307,7 @@
         <v>20</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I227" s="0" t="s">
         <v>21</v>
@@ -15945,7 +15945,7 @@
         <v>20</v>
       </c>
       <c r="H249" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I249" s="0" t="s">
         <v>21</v>
@@ -18439,7 +18439,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18497,7 +18497,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18555,7 +18555,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18584,7 +18584,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19454,7 +19454,7 @@
         <v>391</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19483,7 +19483,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19570,7 +19570,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -19657,7 +19657,7 @@
         <v>391</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I377" s="0" t="s">
         <v>21</v>
@@ -20150,7 +20150,7 @@
         <v>20</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I394" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21252,7 +21252,7 @@
         <v>391</v>
       </c>
       <c r="H432" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I432" s="0" t="s">
         <v>21</v>
@@ -21513,7 +21513,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6415.2</v>
+        <v>-6440.8</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -21948,7 +21948,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-488</v>
+        <v>-490</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22035,7 +22035,7 @@
         <v>391</v>
       </c>
       <c r="H459" s="3" t="n">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="I459" s="0" t="s">
         <v>21</v>
@@ -22064,7 +22064,7 @@
         <v>391</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22093,7 +22093,7 @@
         <v>391</v>
       </c>
       <c r="H461" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I461" s="0" t="s">
         <v>21</v>
@@ -22122,7 +22122,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>490</v>
+        <v>440</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22296,7 +22296,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22354,7 +22354,7 @@
         <v>391</v>
       </c>
       <c r="H470" s="3" t="n">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="I470" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22412,7 +22412,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22644,7 +22644,7 @@
         <v>391</v>
       </c>
       <c r="H480" s="3" t="n">
-        <v>-10</v>
+        <v>-20</v>
       </c>
       <c r="I480" s="0" t="s">
         <v>21</v>
@@ -22702,7 +22702,7 @@
         <v>391</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I482" s="0" t="s">
         <v>21</v>
@@ -23137,7 +23137,7 @@
         <v>391</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I497" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -25341,7 +25341,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>-318</v>
+        <v>-319</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-747</v>
+        <v>-748</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-21</v>
+        <v>-16</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -26008,7 +26008,7 @@
         <v>391</v>
       </c>
       <c r="H596" s="3" t="n">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="I596" s="0" t="s">
         <v>21</v>
@@ -26037,7 +26037,7 @@
         <v>391</v>
       </c>
       <c r="H597" s="3" t="n">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="I597" s="0" t="s">
         <v>21</v>
@@ -26385,7 +26385,7 @@
         <v>391</v>
       </c>
       <c r="H609" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I609" s="0" t="s">
         <v>21</v>
@@ -26675,7 +26675,7 @@
         <v>391</v>
       </c>
       <c r="H619" s="3" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I619" s="0" t="s">
         <v>21</v>
@@ -27255,7 +27255,7 @@
         <v>391</v>
       </c>
       <c r="H639" s="3" t="n">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="I639" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28792,7 +28792,7 @@
         <v>391</v>
       </c>
       <c r="H692" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I692" s="0" t="s">
         <v>21</v>
@@ -28937,7 +28937,7 @@
         <v>850</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30097,7 +30097,7 @@
         <v>391</v>
       </c>
       <c r="H737" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I737" s="0" t="s">
         <v>21</v>
@@ -30126,7 +30126,7 @@
         <v>391</v>
       </c>
       <c r="H738" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I738" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -30619,7 +30619,7 @@
         <v>391</v>
       </c>
       <c r="H755" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I755" s="0" t="s">
         <v>21</v>
@@ -30822,7 +30822,7 @@
         <v>391</v>
       </c>
       <c r="H762" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I762" s="0" t="s">
         <v>21</v>
@@ -30851,7 +30851,7 @@
         <v>391</v>
       </c>
       <c r="H763" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I763" s="0" t="s">
         <v>21</v>
@@ -31286,7 +31286,7 @@
         <v>391</v>
       </c>
       <c r="H778" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I778" s="0" t="s">
         <v>21</v>
@@ -31344,7 +31344,7 @@
         <v>391</v>
       </c>
       <c r="H780" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I780" s="0" t="s">
         <v>21</v>
@@ -31721,7 +31721,7 @@
         <v>391</v>
       </c>
       <c r="H793" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I793" s="0" t="s">
         <v>21</v>
@@ -31779,7 +31779,7 @@
         <v>391</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I795" s="0" t="s">
         <v>21</v>
@@ -31895,7 +31895,7 @@
         <v>391</v>
       </c>
       <c r="H799" s="3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I799" s="0" t="s">
         <v>21</v>
@@ -31924,7 +31924,7 @@
         <v>391</v>
       </c>
       <c r="H800" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I800" s="0" t="s">
         <v>21</v>
@@ -33026,7 +33026,7 @@
         <v>391</v>
       </c>
       <c r="H838" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I838" s="0" t="s">
         <v>21</v>
@@ -33055,7 +33055,7 @@
         <v>391</v>
       </c>
       <c r="H839" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I839" s="0" t="s">
         <v>21</v>
@@ -33258,7 +33258,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-846</v>
+        <v>-850</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -34186,7 +34186,7 @@
         <v>391</v>
       </c>
       <c r="H878" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I878" s="0" t="s">
         <v>21</v>
@@ -34244,7 +34244,7 @@
         <v>391</v>
       </c>
       <c r="H880" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I880" s="0" t="s">
         <v>21</v>
@@ -34679,7 +34679,7 @@
         <v>391</v>
       </c>
       <c r="H895" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I895" s="0" t="s">
         <v>21</v>
@@ -35607,7 +35607,7 @@
         <v>391</v>
       </c>
       <c r="H927" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I927" s="0" t="s">
         <v>21</v>
@@ -35636,7 +35636,7 @@
         <v>391</v>
       </c>
       <c r="H928" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I928" s="0" t="s">
         <v>21</v>
@@ -35665,7 +35665,7 @@
         <v>391</v>
       </c>
       <c r="H929" s="3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I929" s="0" t="s">
         <v>21</v>
@@ -35694,7 +35694,7 @@
         <v>391</v>
       </c>
       <c r="H930" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I930" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -35868,7 +35868,7 @@
         <v>20</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>-38</v>
+        <v>-48</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -36013,7 +36013,7 @@
         <v>391</v>
       </c>
       <c r="H941" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I941" s="0" t="s">
         <v>21</v>
@@ -36042,7 +36042,7 @@
         <v>391</v>
       </c>
       <c r="H942" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I942" s="0" t="s">
         <v>21</v>
@@ -36100,7 +36100,7 @@
         <v>391</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I944" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9262.8</v>
+        <v>8939.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>05 October 2026</t>
+    <t>06 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -15452,7 +15452,7 @@
         <v>20</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="I232" s="0" t="s">
         <v>21</v>
@@ -17250,7 +17250,7 @@
         <v>20</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I294" s="0" t="s">
         <v>21</v>
@@ -20121,7 +20121,7 @@
         <v>20</v>
       </c>
       <c r="H393" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I393" s="0" t="s">
         <v>21</v>
@@ -20266,7 +20266,7 @@
         <v>20</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I398" s="0" t="s">
         <v>21</v>
@@ -35955,7 +35955,7 @@
         <v>20</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8939.2</v>
+        <v>8930.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9449,7 +9449,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>21</v>
@@ -9681,7 +9681,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>21</v>
@@ -11711,7 +11711,7 @@
         <v>20</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12755,7 +12755,7 @@
         <v>20</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I139" s="0" t="s">
         <v>21</v>
@@ -13016,7 +13016,7 @@
         <v>20</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>21</v>
@@ -13538,7 +13538,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -14379,7 +14379,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14408,7 +14408,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14466,7 +14466,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -14495,7 +14495,7 @@
         <v>391</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I199" s="0" t="s">
         <v>21</v>
@@ -18439,7 +18439,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18497,7 +18497,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18613,7 +18613,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>-1</v>
+        <v>56</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19454,7 +19454,7 @@
         <v>391</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19512,7 +19512,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -20353,7 +20353,7 @@
         <v>20</v>
       </c>
       <c r="H401" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I401" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21310,7 +21310,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21513,7 +21513,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6440.8</v>
+        <v>-6458.8</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -21948,7 +21948,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-490</v>
+        <v>-492</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22093,7 +22093,7 @@
         <v>391</v>
       </c>
       <c r="H461" s="3" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="I461" s="0" t="s">
         <v>21</v>
@@ -22122,7 +22122,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>9</v>
+        <v>127</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22412,7 +22412,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22934,7 +22934,7 @@
         <v>391</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I490" s="0" t="s">
         <v>21</v>
@@ -23079,7 +23079,7 @@
         <v>391</v>
       </c>
       <c r="H495" s="3" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="I495" s="0" t="s">
         <v>21</v>
@@ -23456,7 +23456,7 @@
         <v>391</v>
       </c>
       <c r="H508" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I508" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -25341,7 +25341,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>-319</v>
+        <v>-320</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29140,7 +29140,7 @@
         <v>391</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -30097,7 +30097,7 @@
         <v>391</v>
       </c>
       <c r="H737" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I737" s="0" t="s">
         <v>21</v>
@@ -31518,7 +31518,7 @@
         <v>391</v>
       </c>
       <c r="H786" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I786" s="0" t="s">
         <v>21</v>
@@ -31663,7 +31663,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -33258,7 +33258,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-850</v>
+        <v>-852</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -34940,7 +34940,7 @@
         <v>391</v>
       </c>
       <c r="H904" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I904" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -35955,7 +35955,7 @@
         <v>20</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8930.2</v>
+        <v>9032.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>06 October 2026</t>
+    <t>07 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -13335,7 +13335,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -20063,7 +20063,7 @@
         <v>20</v>
       </c>
       <c r="H391" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I391" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9032.2</v>
+        <v>9030.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9275,7 +9275,7 @@
         <v>20</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I19" s="0" t="s">
         <v>21</v>
@@ -11740,7 +11740,7 @@
         <v>20</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I104" s="0" t="s">
         <v>21</v>
@@ -11972,7 +11972,7 @@
         <v>20</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I112" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12639,7 +12639,7 @@
         <v>20</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I135" s="0" t="s">
         <v>21</v>
@@ -12668,7 +12668,7 @@
         <v>20</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I136" s="0" t="s">
         <v>21</v>
@@ -12900,7 +12900,7 @@
         <v>20</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I144" s="0" t="s">
         <v>21</v>
@@ -12958,7 +12958,7 @@
         <v>20</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>21</v>
@@ -13538,7 +13538,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -17221,7 +17221,7 @@
         <v>20</v>
       </c>
       <c r="H293" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I293" s="0" t="s">
         <v>21</v>
@@ -20121,7 +20121,7 @@
         <v>20</v>
       </c>
       <c r="H393" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I393" s="0" t="s">
         <v>21</v>
@@ -20324,7 +20324,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -20730,7 +20730,7 @@
         <v>20</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>-296</v>
+        <v>-298</v>
       </c>
       <c r="I414" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21948,7 +21948,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-492</v>
+        <v>-494</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-748</v>
+        <v>-750</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -33258,7 +33258,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-852</v>
+        <v>-856</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -35955,7 +35955,7 @@
         <v>20</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9030.2</v>
+        <v>9001.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14379,7 +14379,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14408,7 +14408,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19454,7 +19454,7 @@
         <v>391</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21252,7 +21252,7 @@
         <v>391</v>
       </c>
       <c r="H432" s="3" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I432" s="0" t="s">
         <v>21</v>
@@ -21310,7 +21310,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>976</v>
+        <v>961</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6458.8</v>
+        <v>-6470.8</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22296,7 +22296,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22905,7 +22905,7 @@
         <v>391</v>
       </c>
       <c r="H489" s="3" t="n">
-        <v>-400</v>
+        <v>-402</v>
       </c>
       <c r="I489" s="0" t="s">
         <v>21</v>
@@ -23021,7 +23021,7 @@
         <v>391</v>
       </c>
       <c r="H493" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I493" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -23775,7 +23775,7 @@
         <v>391</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I519" s="0" t="s">
         <v>21</v>
@@ -26037,7 +26037,7 @@
         <v>391</v>
       </c>
       <c r="H597" s="3" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="I597" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28618,7 +28618,7 @@
         <v>391</v>
       </c>
       <c r="H686" s="3" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I686" s="0" t="s">
         <v>21</v>
@@ -28647,7 +28647,7 @@
         <v>391</v>
       </c>
       <c r="H687" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I687" s="0" t="s">
         <v>21</v>
@@ -28676,7 +28676,7 @@
         <v>391</v>
       </c>
       <c r="H688" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I688" s="0" t="s">
         <v>21</v>
@@ -28937,7 +28937,7 @@
         <v>850</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -31663,7 +31663,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -31750,7 +31750,7 @@
         <v>391</v>
       </c>
       <c r="H794" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I794" s="0" t="s">
         <v>21</v>
@@ -34215,7 +34215,7 @@
         <v>391</v>
       </c>
       <c r="H879" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I879" s="0" t="s">
         <v>21</v>
@@ -34679,7 +34679,7 @@
         <v>391</v>
       </c>
       <c r="H895" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I895" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -36100,7 +36100,7 @@
         <v>391</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I944" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>9001.2</v>
+        <v>8879.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>07 October 2026</t>
+    <t>08 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -11682,7 +11682,7 @@
         <v>20</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I102" s="0" t="s">
         <v>21</v>
@@ -11711,7 +11711,7 @@
         <v>20</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>21</v>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -13422,7 +13422,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -13886,7 +13886,7 @@
         <v>20</v>
       </c>
       <c r="H178" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I178" s="0" t="s">
         <v>21</v>
@@ -16380,7 +16380,7 @@
         <v>20</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I264" s="0" t="s">
         <v>21</v>
@@ -22789,7 +22789,7 @@
         <v>391</v>
       </c>
       <c r="H485" s="3" t="n">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="I485" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-750</v>
+        <v>-751</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8879.2</v>
+        <v>8862.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9275,7 +9275,7 @@
         <v>20</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I19" s="0" t="s">
         <v>21</v>
@@ -9333,7 +9333,7 @@
         <v>20</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I21" s="0" t="s">
         <v>21</v>
@@ -9391,7 +9391,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -9420,7 +9420,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -11711,7 +11711,7 @@
         <v>20</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>21</v>
@@ -11972,7 +11972,7 @@
         <v>20</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I112" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12349,7 +12349,7 @@
         <v>20</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125" s="0" t="s">
         <v>21</v>
@@ -12407,7 +12407,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -12610,7 +12610,7 @@
         <v>20</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I134" s="0" t="s">
         <v>21</v>
@@ -12668,7 +12668,7 @@
         <v>20</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I136" s="0" t="s">
         <v>21</v>
@@ -12697,7 +12697,7 @@
         <v>20</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I137" s="0" t="s">
         <v>21</v>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -13016,7 +13016,7 @@
         <v>20</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>21</v>
@@ -13393,7 +13393,7 @@
         <v>20</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I161" s="0" t="s">
         <v>21</v>
@@ -13538,7 +13538,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -13973,7 +13973,7 @@
         <v>20</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I181" s="0" t="s">
         <v>21</v>
@@ -15104,7 +15104,7 @@
         <v>20</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I220" s="0" t="s">
         <v>21</v>
@@ -15684,7 +15684,7 @@
         <v>20</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I240" s="0" t="s">
         <v>21</v>
@@ -15742,7 +15742,7 @@
         <v>20</v>
       </c>
       <c r="H242" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I242" s="0" t="s">
         <v>21</v>
@@ -16235,7 +16235,7 @@
         <v>20</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I259" s="0" t="s">
         <v>21</v>
@@ -17308,7 +17308,7 @@
         <v>20</v>
       </c>
       <c r="H296" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I296" s="0" t="s">
         <v>21</v>
@@ -18033,7 +18033,7 @@
         <v>20</v>
       </c>
       <c r="H321" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I321" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18555,7 +18555,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -19019,7 +19019,7 @@
         <v>391</v>
       </c>
       <c r="H355" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I355" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19483,7 +19483,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -20121,7 +20121,7 @@
         <v>20</v>
       </c>
       <c r="H393" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I393" s="0" t="s">
         <v>21</v>
@@ -20150,7 +20150,7 @@
         <v>20</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I394" s="0" t="s">
         <v>21</v>
@@ -20353,7 +20353,7 @@
         <v>20</v>
       </c>
       <c r="H401" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I401" s="0" t="s">
         <v>21</v>
@@ -21948,7 +21948,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-494</v>
+        <v>-498</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -25022,7 +25022,7 @@
         <v>20</v>
       </c>
       <c r="H562" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I562" s="0" t="s">
         <v>21</v>
@@ -25428,7 +25428,7 @@
         <v>20</v>
       </c>
       <c r="H576" s="3" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I576" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -31750,7 +31750,7 @@
         <v>391</v>
       </c>
       <c r="H794" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I794" s="0" t="s">
         <v>21</v>
@@ -33258,7 +33258,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-856</v>
+        <v>-863</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8862.2</v>
+        <v>8801.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -18439,7 +18439,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18497,7 +18497,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18584,7 +18584,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -19019,7 +19019,7 @@
         <v>391</v>
       </c>
       <c r="H355" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I355" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19657,7 +19657,7 @@
         <v>391</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I377" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6470.8</v>
+        <v>-6480.8</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22122,7 +22122,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -22151,7 +22151,7 @@
         <v>391</v>
       </c>
       <c r="H463" s="3" t="n">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="I463" s="0" t="s">
         <v>21</v>
@@ -22238,7 +22238,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22412,7 +22412,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -23021,7 +23021,7 @@
         <v>391</v>
       </c>
       <c r="H493" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I493" s="0" t="s">
         <v>21</v>
@@ -23456,7 +23456,7 @@
         <v>391</v>
       </c>
       <c r="H508" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I508" s="0" t="s">
         <v>21</v>
@@ -23485,7 +23485,7 @@
         <v>391</v>
       </c>
       <c r="H509" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I509" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -25921,7 +25921,7 @@
         <v>391</v>
       </c>
       <c r="H593" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I593" s="0" t="s">
         <v>21</v>
@@ -25950,7 +25950,7 @@
         <v>391</v>
       </c>
       <c r="H594" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I594" s="0" t="s">
         <v>21</v>
@@ -26675,7 +26675,7 @@
         <v>391</v>
       </c>
       <c r="H619" s="3" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="I619" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28357,7 +28357,7 @@
         <v>391</v>
       </c>
       <c r="H677" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I677" s="0" t="s">
         <v>21</v>
@@ -28415,7 +28415,7 @@
         <v>391</v>
       </c>
       <c r="H679" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I679" s="0" t="s">
         <v>21</v>
@@ -28444,7 +28444,7 @@
         <v>391</v>
       </c>
       <c r="H680" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I680" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -31199,7 +31199,7 @@
         <v>391</v>
       </c>
       <c r="H775" s="3" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="I775" s="0" t="s">
         <v>21</v>
@@ -31344,7 +31344,7 @@
         <v>391</v>
       </c>
       <c r="H780" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I780" s="0" t="s">
         <v>21</v>
@@ -31663,7 +31663,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -31750,7 +31750,7 @@
         <v>391</v>
       </c>
       <c r="H794" s="3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I794" s="0" t="s">
         <v>21</v>
@@ -31779,7 +31779,7 @@
         <v>391</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I795" s="0" t="s">
         <v>21</v>
@@ -32475,7 +32475,7 @@
         <v>391</v>
       </c>
       <c r="H819" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I819" s="0" t="s">
         <v>21</v>
@@ -33084,7 +33084,7 @@
         <v>391</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-60</v>
+        <v>-62</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8801.2</v>
+        <v>8617.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>08 October 2026</t>
+    <t>09 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -9391,7 +9391,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -10377,7 +10377,7 @@
         <v>20</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I57" s="0" t="s">
         <v>21</v>
@@ -12871,7 +12871,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -20121,7 +20121,7 @@
         <v>20</v>
       </c>
       <c r="H393" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I393" s="0" t="s">
         <v>21</v>
@@ -25370,7 +25370,7 @@
         <v>20</v>
       </c>
       <c r="H574" s="3" t="n">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="I574" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8617.2</v>
+        <v>8602.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -10000,7 +10000,7 @@
         <v>20</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" s="0" t="s">
         <v>21</v>
@@ -10406,7 +10406,7 @@
         <v>20</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I58" s="0" t="s">
         <v>21</v>
@@ -11160,7 +11160,7 @@
         <v>20</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I84" s="0" t="s">
         <v>21</v>
@@ -11276,7 +11276,7 @@
         <v>20</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I88" s="0" t="s">
         <v>21</v>
@@ -11682,7 +11682,7 @@
         <v>20</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I102" s="0" t="s">
         <v>21</v>
@@ -11711,7 +11711,7 @@
         <v>20</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>21</v>
@@ -11740,7 +11740,7 @@
         <v>20</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I104" s="0" t="s">
         <v>21</v>
@@ -12059,7 +12059,7 @@
         <v>20</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12465,7 +12465,7 @@
         <v>20</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I129" s="0" t="s">
         <v>21</v>
@@ -12639,7 +12639,7 @@
         <v>20</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I135" s="0" t="s">
         <v>21</v>
@@ -12697,7 +12697,7 @@
         <v>20</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="I137" s="0" t="s">
         <v>21</v>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -13045,7 +13045,7 @@
         <v>20</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I149" s="0" t="s">
         <v>21</v>
@@ -13335,7 +13335,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -13422,7 +13422,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -13538,7 +13538,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -14292,7 +14292,7 @@
         <v>20</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I192" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14466,7 +14466,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -15104,7 +15104,7 @@
         <v>20</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I220" s="0" t="s">
         <v>21</v>
@@ -17540,7 +17540,7 @@
         <v>20</v>
       </c>
       <c r="H304" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I304" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -20150,7 +20150,7 @@
         <v>20</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I394" s="0" t="s">
         <v>21</v>
@@ -20324,7 +20324,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21948,7 +21948,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-498</v>
+        <v>-500</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22180,7 +22180,7 @@
         <v>391</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>836</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22296,7 +22296,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -25341,7 +25341,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>-320</v>
+        <v>-321</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-751</v>
+        <v>-752</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-16</v>
+        <v>-7</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>-7</v>
+        <v>128</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28879,7 +28879,7 @@
         <v>391</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -30619,7 +30619,7 @@
         <v>391</v>
       </c>
       <c r="H755" s="3" t="n">
-        <v>-2</v>
+        <v>45</v>
       </c>
       <c r="I755" s="0" t="s">
         <v>21</v>
@@ -31286,7 +31286,7 @@
         <v>391</v>
       </c>
       <c r="H778" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I778" s="0" t="s">
         <v>21</v>
@@ -31779,7 +31779,7 @@
         <v>391</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I795" s="0" t="s">
         <v>21</v>
@@ -32504,7 +32504,7 @@
         <v>391</v>
       </c>
       <c r="H820" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I820" s="0" t="s">
         <v>21</v>
@@ -33258,7 +33258,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-863</v>
+        <v>-867</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -35868,7 +35868,7 @@
         <v>20</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>-48</v>
+        <v>-50</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8602.2</v>
+        <v>8818.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14379,7 +14379,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14408,7 +14408,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14466,7 +14466,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -18439,7 +18439,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18613,7 +18613,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -19483,7 +19483,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -19657,7 +19657,7 @@
         <v>391</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I377" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21252,7 +21252,7 @@
         <v>391</v>
       </c>
       <c r="H432" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I432" s="0" t="s">
         <v>21</v>
@@ -21310,7 +21310,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21513,7 +21513,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6480.8</v>
+        <v>-6497.8</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22238,7 +22238,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22296,7 +22296,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22673,7 +22673,7 @@
         <v>391</v>
       </c>
       <c r="H481" s="3" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="I481" s="0" t="s">
         <v>21</v>
@@ -22789,7 +22789,7 @@
         <v>391</v>
       </c>
       <c r="H485" s="3" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I485" s="0" t="s">
         <v>21</v>
@@ -22934,7 +22934,7 @@
         <v>391</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I490" s="0" t="s">
         <v>21</v>
@@ -23137,7 +23137,7 @@
         <v>391</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I497" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23543,7 +23543,7 @@
         <v>391</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I511" s="0" t="s">
         <v>21</v>
@@ -23775,7 +23775,7 @@
         <v>391</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I519" s="0" t="s">
         <v>21</v>
@@ -25921,7 +25921,7 @@
         <v>391</v>
       </c>
       <c r="H593" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I593" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -27864,7 +27864,7 @@
         <v>391</v>
       </c>
       <c r="H660" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I660" s="0" t="s">
         <v>21</v>
@@ -28357,7 +28357,7 @@
         <v>391</v>
       </c>
       <c r="H677" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I677" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -29749,7 +29749,7 @@
         <v>391</v>
       </c>
       <c r="H725" s="3" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I725" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -31344,7 +31344,7 @@
         <v>391</v>
       </c>
       <c r="H780" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I780" s="0" t="s">
         <v>21</v>
@@ -31373,7 +31373,7 @@
         <v>391</v>
       </c>
       <c r="H781" s="3" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I781" s="0" t="s">
         <v>21</v>
@@ -31489,7 +31489,7 @@
         <v>391</v>
       </c>
       <c r="H785" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I785" s="0" t="s">
         <v>21</v>
@@ -31750,7 +31750,7 @@
         <v>391</v>
       </c>
       <c r="H794" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I794" s="0" t="s">
         <v>21</v>
@@ -32707,7 +32707,7 @@
         <v>391</v>
       </c>
       <c r="H827" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I827" s="0" t="s">
         <v>21</v>
@@ -33084,7 +33084,7 @@
         <v>391</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-62</v>
+        <v>-63</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -34186,7 +34186,7 @@
         <v>391</v>
       </c>
       <c r="H878" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I878" s="0" t="s">
         <v>21</v>
@@ -34273,7 +34273,7 @@
         <v>391</v>
       </c>
       <c r="H881" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I881" s="0" t="s">
         <v>21</v>
@@ -34302,7 +34302,7 @@
         <v>391</v>
       </c>
       <c r="H882" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I882" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -36013,7 +36013,7 @@
         <v>391</v>
       </c>
       <c r="H941" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I941" s="0" t="s">
         <v>21</v>
@@ -36100,7 +36100,7 @@
         <v>391</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I944" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8818.2</v>
+        <v>8661.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>09 October 2026</t>
+    <t>10 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12842,7 +12842,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -13335,7 +13335,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -17250,7 +17250,7 @@
         <v>20</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I294" s="0" t="s">
         <v>21</v>
@@ -25370,7 +25370,7 @@
         <v>20</v>
       </c>
       <c r="H574" s="3" t="n">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="I574" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8661.2</v>
+        <v>8652.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9652,7 +9652,7 @@
         <v>20</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="0" t="s">
         <v>21</v>
@@ -11160,7 +11160,7 @@
         <v>20</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I84" s="0" t="s">
         <v>21</v>
@@ -11276,7 +11276,7 @@
         <v>20</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I88" s="0" t="s">
         <v>21</v>
@@ -11740,7 +11740,7 @@
         <v>20</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I104" s="0" t="s">
         <v>21</v>
@@ -11972,7 +11972,7 @@
         <v>20</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I112" s="0" t="s">
         <v>21</v>
@@ -12059,7 +12059,7 @@
         <v>20</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12465,7 +12465,7 @@
         <v>20</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" s="0" t="s">
         <v>21</v>
@@ -12697,7 +12697,7 @@
         <v>20</v>
       </c>
       <c r="H137" s="3" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="I137" s="0" t="s">
         <v>21</v>
@@ -12958,7 +12958,7 @@
         <v>20</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>21</v>
@@ -12987,7 +12987,7 @@
         <v>20</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I147" s="0" t="s">
         <v>21</v>
@@ -13016,7 +13016,7 @@
         <v>20</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>21</v>
@@ -13045,7 +13045,7 @@
         <v>20</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I149" s="0" t="s">
         <v>21</v>
@@ -13161,7 +13161,7 @@
         <v>20</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I153" s="0" t="s">
         <v>21</v>
@@ -13393,7 +13393,7 @@
         <v>20</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I161" s="0" t="s">
         <v>21</v>
@@ -13538,7 +13538,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -13973,7 +13973,7 @@
         <v>20</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I181" s="0" t="s">
         <v>21</v>
@@ -15104,7 +15104,7 @@
         <v>20</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I220" s="0" t="s">
         <v>21</v>
@@ -15452,7 +15452,7 @@
         <v>20</v>
       </c>
       <c r="H232" s="3" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="I232" s="0" t="s">
         <v>21</v>
@@ -20179,7 +20179,7 @@
         <v>20</v>
       </c>
       <c r="H395" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I395" s="0" t="s">
         <v>21</v>
@@ -20324,7 +20324,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -21948,7 +21948,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-500</v>
+        <v>-502</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -29604,7 +29604,7 @@
         <v>391</v>
       </c>
       <c r="H720" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I720" s="0" t="s">
         <v>21</v>
@@ -33258,7 +33258,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-867</v>
+        <v>-870</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -35868,7 +35868,7 @@
         <v>20</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>-50</v>
+        <v>-54</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8652.2</v>
+        <v>8599.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9681,7 +9681,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>21</v>
@@ -10000,7 +10000,7 @@
         <v>20</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" s="0" t="s">
         <v>21</v>
@@ -11160,7 +11160,7 @@
         <v>20</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I84" s="0" t="s">
         <v>21</v>
@@ -14379,7 +14379,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14466,7 +14466,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18555,7 +18555,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18584,7 +18584,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18613,7 +18613,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19512,7 +19512,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -19657,7 +19657,7 @@
         <v>391</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I377" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21310,7 +21310,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>955</v>
+        <v>925</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6497.8</v>
+        <v>-6505.8</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22586,7 +22586,7 @@
         <v>391</v>
       </c>
       <c r="H478" s="3" t="n">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="I478" s="0" t="s">
         <v>21</v>
@@ -22673,7 +22673,7 @@
         <v>391</v>
       </c>
       <c r="H481" s="3" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="I481" s="0" t="s">
         <v>21</v>
@@ -22702,7 +22702,7 @@
         <v>391</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I482" s="0" t="s">
         <v>21</v>
@@ -22847,7 +22847,7 @@
         <v>391</v>
       </c>
       <c r="H487" s="3" t="n">
-        <v>-8</v>
+        <v>-28</v>
       </c>
       <c r="I487" s="0" t="s">
         <v>21</v>
@@ -23137,7 +23137,7 @@
         <v>391</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I497" s="0" t="s">
         <v>21</v>
@@ -23427,7 +23427,7 @@
         <v>391</v>
       </c>
       <c r="H507" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I507" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -24790,7 +24790,7 @@
         <v>391</v>
       </c>
       <c r="H554" s="3" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="I554" s="0" t="s">
         <v>21</v>
@@ -25747,7 +25747,7 @@
         <v>391</v>
       </c>
       <c r="H587" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I587" s="0" t="s">
         <v>21</v>
@@ -27255,7 +27255,7 @@
         <v>391</v>
       </c>
       <c r="H639" s="3" t="n">
-        <v>-80</v>
+        <v>-81</v>
       </c>
       <c r="I639" s="0" t="s">
         <v>21</v>
@@ -28937,7 +28937,7 @@
         <v>850</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -30097,7 +30097,7 @@
         <v>391</v>
       </c>
       <c r="H737" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I737" s="0" t="s">
         <v>21</v>
@@ -30126,7 +30126,7 @@
         <v>391</v>
       </c>
       <c r="H738" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I738" s="0" t="s">
         <v>21</v>
@@ -31286,7 +31286,7 @@
         <v>391</v>
       </c>
       <c r="H778" s="3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I778" s="0" t="s">
         <v>21</v>
@@ -31315,7 +31315,7 @@
         <v>391</v>
       </c>
       <c r="H779" s="3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I779" s="0" t="s">
         <v>21</v>
@@ -31721,7 +31721,7 @@
         <v>391</v>
       </c>
       <c r="H793" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I793" s="0" t="s">
         <v>21</v>
@@ -31779,7 +31779,7 @@
         <v>391</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I795" s="0" t="s">
         <v>21</v>
@@ -31866,7 +31866,7 @@
         <v>391</v>
       </c>
       <c r="H798" s="3" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I798" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -36100,7 +36100,7 @@
         <v>391</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I944" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8599.2</v>
+        <v>8290.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>10 October 2026</t>
+    <t>11 October 2026</t>
   </si>
   <si>
     <t>To</t>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -13335,7 +13335,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -13538,7 +13538,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -14379,7 +14379,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -18497,7 +18497,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -31953,7 +31953,7 @@
         <v>391</v>
       </c>
       <c r="H801" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I801" s="0" t="s">
         <v>21</v>
@@ -34302,7 +34302,7 @@
         <v>391</v>
       </c>
       <c r="H882" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I882" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8290.2</v>
+        <v>8260.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>11 October 2026</t>
+    <t>12 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -13538,7 +13538,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -20150,7 +20150,7 @@
         <v>20</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I394" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -23137,7 +23137,7 @@
         <v>391</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I497" s="0" t="s">
         <v>21</v>
@@ -31431,7 +31431,7 @@
         <v>391</v>
       </c>
       <c r="H783" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I783" s="0" t="s">
         <v>21</v>
@@ -31460,7 +31460,7 @@
         <v>391</v>
       </c>
       <c r="H784" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I784" s="0" t="s">
         <v>21</v>
@@ -33026,7 +33026,7 @@
         <v>391</v>
       </c>
       <c r="H838" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I838" s="0" t="s">
         <v>21</v>
@@ -36100,7 +36100,7 @@
         <v>391</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I944" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8260.2</v>
+        <v>8249.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9333,7 +9333,7 @@
         <v>20</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="0" t="s">
         <v>21</v>
@@ -9391,7 +9391,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -9420,7 +9420,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -9449,7 +9449,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>21</v>
@@ -9536,7 +9536,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I28" s="0" t="s">
         <v>21</v>
@@ -9681,7 +9681,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>21</v>
@@ -10377,7 +10377,7 @@
         <v>20</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I57" s="0" t="s">
         <v>21</v>
@@ -10406,7 +10406,7 @@
         <v>20</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I58" s="0" t="s">
         <v>21</v>
@@ -10551,7 +10551,7 @@
         <v>20</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I63" s="0" t="s">
         <v>21</v>
@@ -11682,7 +11682,7 @@
         <v>20</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I102" s="0" t="s">
         <v>21</v>
@@ -11711,7 +11711,7 @@
         <v>20</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12610,7 +12610,7 @@
         <v>20</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I134" s="0" t="s">
         <v>21</v>
@@ -12871,7 +12871,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13016,7 +13016,7 @@
         <v>20</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>21</v>
@@ -13132,7 +13132,7 @@
         <v>20</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I152" s="0" t="s">
         <v>21</v>
@@ -13538,7 +13538,7 @@
         <v>20</v>
       </c>
       <c r="H166" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" s="0" t="s">
         <v>21</v>
@@ -13973,7 +13973,7 @@
         <v>20</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I181" s="0" t="s">
         <v>21</v>
@@ -14292,7 +14292,7 @@
         <v>20</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I192" s="0" t="s">
         <v>21</v>
@@ -14379,7 +14379,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14408,7 +14408,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14495,7 +14495,7 @@
         <v>391</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I199" s="0" t="s">
         <v>21</v>
@@ -15684,7 +15684,7 @@
         <v>20</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I240" s="0" t="s">
         <v>21</v>
@@ -18439,7 +18439,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18497,7 +18497,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18555,7 +18555,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18584,7 +18584,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18613,7 +18613,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -18729,7 +18729,7 @@
         <v>391</v>
       </c>
       <c r="H345" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I345" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19454,7 +19454,7 @@
         <v>391</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19483,7 +19483,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19512,7 +19512,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19570,7 +19570,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -19657,7 +19657,7 @@
         <v>391</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I377" s="0" t="s">
         <v>21</v>
@@ -19976,7 +19976,7 @@
         <v>20</v>
       </c>
       <c r="H388" s="3" t="n">
-        <v>-203</v>
+        <v>-205</v>
       </c>
       <c r="I388" s="0" t="s">
         <v>21</v>
@@ -20266,7 +20266,7 @@
         <v>20</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I398" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21252,7 +21252,7 @@
         <v>391</v>
       </c>
       <c r="H432" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I432" s="0" t="s">
         <v>21</v>
@@ -21513,7 +21513,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6505.8</v>
+        <v>-6525.8</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22206,13 +22206,13 @@
         <v>19</v>
       </c>
       <c r="G465" s="2" t="s">
-        <v>835</v>
+        <v>391</v>
       </c>
       <c r="H465" s="3" t="n">
         <v>10</v>
       </c>
       <c r="I465" s="0" t="s">
-        <v>836</v>
+        <v>21</v>
       </c>
     </row>
     <row r="466" spans="1:9" customHeight="1">
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22296,7 +22296,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22354,7 +22354,7 @@
         <v>391</v>
       </c>
       <c r="H470" s="3" t="n">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="I470" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22412,7 +22412,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22702,7 +22702,7 @@
         <v>391</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I482" s="0" t="s">
         <v>21</v>
@@ -22760,7 +22760,7 @@
         <v>391</v>
       </c>
       <c r="H484" s="3" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="I484" s="0" t="s">
         <v>21</v>
@@ -22789,7 +22789,7 @@
         <v>391</v>
       </c>
       <c r="H485" s="3" t="n">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="I485" s="0" t="s">
         <v>21</v>
@@ -22905,7 +22905,7 @@
         <v>391</v>
       </c>
       <c r="H489" s="3" t="n">
-        <v>-402</v>
+        <v>-407</v>
       </c>
       <c r="I489" s="0" t="s">
         <v>21</v>
@@ -22934,7 +22934,7 @@
         <v>391</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I490" s="0" t="s">
         <v>21</v>
@@ -23021,7 +23021,7 @@
         <v>391</v>
       </c>
       <c r="H493" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I493" s="0" t="s">
         <v>21</v>
@@ -23079,7 +23079,7 @@
         <v>391</v>
       </c>
       <c r="H495" s="3" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="I495" s="0" t="s">
         <v>21</v>
@@ -23137,7 +23137,7 @@
         <v>391</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I497" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -23862,7 +23862,7 @@
         <v>391</v>
       </c>
       <c r="H522" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I522" s="0" t="s">
         <v>21</v>
@@ -23891,7 +23891,7 @@
         <v>391</v>
       </c>
       <c r="H523" s="3" t="n">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="I523" s="0" t="s">
         <v>21</v>
@@ -23920,7 +23920,7 @@
         <v>391</v>
       </c>
       <c r="H524" s="3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I524" s="0" t="s">
         <v>21</v>
@@ -25341,7 +25341,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>-321</v>
+        <v>-323</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-752</v>
+        <v>-754</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25477,7 +25477,7 @@
         <v>10</v>
       </c>
       <c r="E578" s="3" t="n">
-        <v>5.83</v>
+        <v>5.38</v>
       </c>
       <c r="F578" s="2" t="s">
         <v>19</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -25544,7 +25544,7 @@
         <v>391</v>
       </c>
       <c r="H580" s="3" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I580" s="0" t="s">
         <v>21</v>
@@ -25747,7 +25747,7 @@
         <v>391</v>
       </c>
       <c r="H587" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I587" s="0" t="s">
         <v>21</v>
@@ -25921,7 +25921,7 @@
         <v>391</v>
       </c>
       <c r="H593" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I593" s="0" t="s">
         <v>21</v>
@@ -26675,7 +26675,7 @@
         <v>391</v>
       </c>
       <c r="H619" s="3" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I619" s="0" t="s">
         <v>21</v>
@@ -27255,7 +27255,7 @@
         <v>391</v>
       </c>
       <c r="H639" s="3" t="n">
-        <v>-81</v>
+        <v>-82</v>
       </c>
       <c r="I639" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28357,7 +28357,7 @@
         <v>391</v>
       </c>
       <c r="H677" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I677" s="0" t="s">
         <v>21</v>
@@ -28415,7 +28415,7 @@
         <v>391</v>
       </c>
       <c r="H679" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I679" s="0" t="s">
         <v>21</v>
@@ -28444,7 +28444,7 @@
         <v>391</v>
       </c>
       <c r="H680" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I680" s="0" t="s">
         <v>21</v>
@@ -28473,7 +28473,7 @@
         <v>391</v>
       </c>
       <c r="H681" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I681" s="0" t="s">
         <v>21</v>
@@ -28502,7 +28502,7 @@
         <v>391</v>
       </c>
       <c r="H682" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I682" s="0" t="s">
         <v>21</v>
@@ -28531,7 +28531,7 @@
         <v>391</v>
       </c>
       <c r="H683" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I683" s="0" t="s">
         <v>21</v>
@@ -28560,7 +28560,7 @@
         <v>391</v>
       </c>
       <c r="H684" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I684" s="0" t="s">
         <v>21</v>
@@ -28589,7 +28589,7 @@
         <v>391</v>
       </c>
       <c r="H685" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I685" s="0" t="s">
         <v>21</v>
@@ -28702,13 +28702,13 @@
         <v>19</v>
       </c>
       <c r="G689" s="2" t="s">
-        <v>835</v>
+        <v>391</v>
       </c>
       <c r="H689" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I689" s="0" t="s">
-        <v>836</v>
+        <v>21</v>
       </c>
     </row>
     <row r="690" spans="1:9" customHeight="1">
@@ -28731,13 +28731,13 @@
         <v>19</v>
       </c>
       <c r="G690" s="2" t="s">
-        <v>835</v>
+        <v>391</v>
       </c>
       <c r="H690" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I690" s="0" t="s">
-        <v>836</v>
+        <v>21</v>
       </c>
     </row>
     <row r="691" spans="1:9" customHeight="1">
@@ -28760,13 +28760,13 @@
         <v>19</v>
       </c>
       <c r="G691" s="2" t="s">
-        <v>835</v>
+        <v>391</v>
       </c>
       <c r="H691" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I691" s="0" t="s">
-        <v>836</v>
+        <v>21</v>
       </c>
     </row>
     <row r="692" spans="1:9" customHeight="1">
@@ -28792,7 +28792,7 @@
         <v>391</v>
       </c>
       <c r="H692" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I692" s="0" t="s">
         <v>21</v>
@@ -28821,7 +28821,7 @@
         <v>391</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I693" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30097,7 +30097,7 @@
         <v>391</v>
       </c>
       <c r="H737" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I737" s="0" t="s">
         <v>21</v>
@@ -30126,7 +30126,7 @@
         <v>391</v>
       </c>
       <c r="H738" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I738" s="0" t="s">
         <v>21</v>
@@ -30155,7 +30155,7 @@
         <v>391</v>
       </c>
       <c r="H739" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I739" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -30619,7 +30619,7 @@
         <v>391</v>
       </c>
       <c r="H755" s="3" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="I755" s="0" t="s">
         <v>21</v>
@@ -30822,7 +30822,7 @@
         <v>391</v>
       </c>
       <c r="H762" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I762" s="0" t="s">
         <v>21</v>
@@ -30851,7 +30851,7 @@
         <v>391</v>
       </c>
       <c r="H763" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I763" s="0" t="s">
         <v>21</v>
@@ -31199,7 +31199,7 @@
         <v>391</v>
       </c>
       <c r="H775" s="3" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I775" s="0" t="s">
         <v>21</v>
@@ -31344,7 +31344,7 @@
         <v>391</v>
       </c>
       <c r="H780" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I780" s="0" t="s">
         <v>21</v>
@@ -31402,7 +31402,7 @@
         <v>391</v>
       </c>
       <c r="H782" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I782" s="0" t="s">
         <v>21</v>
@@ -31431,7 +31431,7 @@
         <v>391</v>
       </c>
       <c r="H783" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I783" s="0" t="s">
         <v>21</v>
@@ -31460,7 +31460,7 @@
         <v>391</v>
       </c>
       <c r="H784" s="3" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I784" s="0" t="s">
         <v>21</v>
@@ -31663,7 +31663,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -31692,7 +31692,7 @@
         <v>391</v>
       </c>
       <c r="H792" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I792" s="0" t="s">
         <v>21</v>
@@ -31721,7 +31721,7 @@
         <v>391</v>
       </c>
       <c r="H793" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I793" s="0" t="s">
         <v>21</v>
@@ -31779,7 +31779,7 @@
         <v>391</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I795" s="0" t="s">
         <v>21</v>
@@ -31866,7 +31866,7 @@
         <v>391</v>
       </c>
       <c r="H798" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I798" s="0" t="s">
         <v>21</v>
@@ -31953,7 +31953,7 @@
         <v>391</v>
       </c>
       <c r="H801" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I801" s="0" t="s">
         <v>21</v>
@@ -32098,7 +32098,7 @@
         <v>391</v>
       </c>
       <c r="H806" s="3" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I806" s="0" t="s">
         <v>21</v>
@@ -32504,7 +32504,7 @@
         <v>391</v>
       </c>
       <c r="H820" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I820" s="0" t="s">
         <v>21</v>
@@ -32591,7 +32591,7 @@
         <v>391</v>
       </c>
       <c r="H823" s="3" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I823" s="0" t="s">
         <v>21</v>
@@ -32620,7 +32620,7 @@
         <v>391</v>
       </c>
       <c r="H824" s="3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I824" s="0" t="s">
         <v>21</v>
@@ -33084,7 +33084,7 @@
         <v>391</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-63</v>
+        <v>-64</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -34099,7 +34099,7 @@
         <v>391</v>
       </c>
       <c r="H875" s="3" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I875" s="0" t="s">
         <v>21</v>
@@ -34157,7 +34157,7 @@
         <v>391</v>
       </c>
       <c r="H877" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I877" s="0" t="s">
         <v>21</v>
@@ -34186,7 +34186,7 @@
         <v>391</v>
       </c>
       <c r="H878" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I878" s="0" t="s">
         <v>21</v>
@@ -34244,7 +34244,7 @@
         <v>391</v>
       </c>
       <c r="H880" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I880" s="0" t="s">
         <v>21</v>
@@ -34331,7 +34331,7 @@
         <v>391</v>
       </c>
       <c r="H883" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I883" s="0" t="s">
         <v>21</v>
@@ -34360,7 +34360,7 @@
         <v>391</v>
       </c>
       <c r="H884" s="3" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I884" s="0" t="s">
         <v>21</v>
@@ -34592,7 +34592,7 @@
         <v>391</v>
       </c>
       <c r="H892" s="3" t="n">
-        <v>-179</v>
+        <v>-199</v>
       </c>
       <c r="I892" s="0" t="s">
         <v>21</v>
@@ -34679,7 +34679,7 @@
         <v>391</v>
       </c>
       <c r="H895" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I895" s="0" t="s">
         <v>21</v>
@@ -34824,7 +34824,7 @@
         <v>391</v>
       </c>
       <c r="H900" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I900" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -35955,7 +35955,7 @@
         <v>20</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -36013,7 +36013,7 @@
         <v>391</v>
       </c>
       <c r="H941" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I941" s="0" t="s">
         <v>21</v>
@@ -36100,7 +36100,7 @@
         <v>391</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I944" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>8249.2</v>
+        <v>7894.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>12 October 2026</t>
+    <t>13 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -13161,7 +13161,7 @@
         <v>20</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I153" s="0" t="s">
         <v>21</v>
@@ -18671,7 +18671,7 @@
         <v>391</v>
       </c>
       <c r="H343" s="3" t="n">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="I343" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21310,7 +21310,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>925</v>
+        <v>915</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -22238,7 +22238,7 @@
         <v>391</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22296,7 +22296,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22905,7 +22905,7 @@
         <v>391</v>
       </c>
       <c r="H489" s="3" t="n">
-        <v>-407</v>
+        <v>-417</v>
       </c>
       <c r="I489" s="0" t="s">
         <v>21</v>
@@ -23021,7 +23021,7 @@
         <v>391</v>
       </c>
       <c r="H493" s="3" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="I493" s="0" t="s">
         <v>21</v>
@@ -25747,7 +25747,7 @@
         <v>391</v>
       </c>
       <c r="H587" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I587" s="0" t="s">
         <v>21</v>
@@ -28357,7 +28357,7 @@
         <v>391</v>
       </c>
       <c r="H677" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I677" s="0" t="s">
         <v>21</v>
@@ -28444,7 +28444,7 @@
         <v>391</v>
       </c>
       <c r="H680" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I680" s="0" t="s">
         <v>21</v>
@@ -28589,7 +28589,7 @@
         <v>391</v>
       </c>
       <c r="H685" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I685" s="0" t="s">
         <v>21</v>
@@ -28821,7 +28821,7 @@
         <v>391</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I693" s="0" t="s">
         <v>21</v>
@@ -28937,7 +28937,7 @@
         <v>850</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30822,7 +30822,7 @@
         <v>391</v>
       </c>
       <c r="H762" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I762" s="0" t="s">
         <v>21</v>
@@ -30880,7 +30880,7 @@
         <v>391</v>
       </c>
       <c r="H764" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I764" s="0" t="s">
         <v>21</v>
@@ -31083,7 +31083,7 @@
         <v>391</v>
       </c>
       <c r="H771" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I771" s="0" t="s">
         <v>836</v>
@@ -31663,7 +31663,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -31895,7 +31895,7 @@
         <v>391</v>
       </c>
       <c r="H799" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I799" s="0" t="s">
         <v>21</v>
@@ -31953,7 +31953,7 @@
         <v>391</v>
       </c>
       <c r="H801" s="3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I801" s="0" t="s">
         <v>21</v>
@@ -32504,7 +32504,7 @@
         <v>391</v>
       </c>
       <c r="H820" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I820" s="0" t="s">
         <v>21</v>
@@ -32620,7 +32620,7 @@
         <v>391</v>
       </c>
       <c r="H824" s="3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I824" s="0" t="s">
         <v>21</v>
@@ -32649,7 +32649,7 @@
         <v>391</v>
       </c>
       <c r="H825" s="3" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I825" s="0" t="s">
         <v>21</v>
@@ -34273,7 +34273,7 @@
         <v>391</v>
       </c>
       <c r="H881" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I881" s="0" t="s">
         <v>21</v>
@@ -35868,7 +35868,7 @@
         <v>20</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>-54</v>
+        <v>-24</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -36100,7 +36100,7 @@
         <v>391</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I944" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>7894.2</v>
+        <v>7830.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9449,7 +9449,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>21</v>
@@ -9536,7 +9536,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I28" s="0" t="s">
         <v>21</v>
@@ -10087,7 +10087,7 @@
         <v>20</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="I47" s="0" t="s">
         <v>21</v>
@@ -10377,7 +10377,7 @@
         <v>20</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I57" s="0" t="s">
         <v>21</v>
@@ -12987,7 +12987,7 @@
         <v>20</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I147" s="0" t="s">
         <v>21</v>
@@ -13016,7 +13016,7 @@
         <v>20</v>
       </c>
       <c r="H148" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I148" s="0" t="s">
         <v>21</v>
@@ -13045,7 +13045,7 @@
         <v>20</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I149" s="0" t="s">
         <v>21</v>
@@ -13393,7 +13393,7 @@
         <v>20</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I161" s="0" t="s">
         <v>21</v>
@@ -14379,7 +14379,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -17221,7 +17221,7 @@
         <v>20</v>
       </c>
       <c r="H293" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I293" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18584,7 +18584,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-15</v>
+        <v>-17</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -19512,7 +19512,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19570,7 +19570,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -20324,7 +20324,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21513,7 +21513,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6525.8</v>
+        <v>-6536.8</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -21948,7 +21948,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-502</v>
+        <v>-504</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22325,7 +22325,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22412,7 +22412,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22673,7 +22673,7 @@
         <v>391</v>
       </c>
       <c r="H481" s="3" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="I481" s="0" t="s">
         <v>21</v>
@@ -22934,7 +22934,7 @@
         <v>391</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I490" s="0" t="s">
         <v>21</v>
@@ -23137,7 +23137,7 @@
         <v>391</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I497" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -23891,7 +23891,7 @@
         <v>391</v>
       </c>
       <c r="H523" s="3" t="n">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="I523" s="0" t="s">
         <v>21</v>
@@ -23920,7 +23920,7 @@
         <v>391</v>
       </c>
       <c r="H524" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I524" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-754</v>
+        <v>-755</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -25863,7 +25863,7 @@
         <v>391</v>
       </c>
       <c r="H591" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I591" s="0" t="s">
         <v>21</v>
@@ -25921,7 +25921,7 @@
         <v>391</v>
       </c>
       <c r="H593" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I593" s="0" t="s">
         <v>21</v>
@@ -26675,7 +26675,7 @@
         <v>391</v>
       </c>
       <c r="H619" s="3" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I619" s="0" t="s">
         <v>21</v>
@@ -27255,7 +27255,7 @@
         <v>391</v>
       </c>
       <c r="H639" s="3" t="n">
-        <v>-82</v>
+        <v>-84</v>
       </c>
       <c r="I639" s="0" t="s">
         <v>21</v>
@@ -28937,7 +28937,7 @@
         <v>850</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30097,7 +30097,7 @@
         <v>391</v>
       </c>
       <c r="H737" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I737" s="0" t="s">
         <v>21</v>
@@ -30155,7 +30155,7 @@
         <v>391</v>
       </c>
       <c r="H739" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I739" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -30619,7 +30619,7 @@
         <v>391</v>
       </c>
       <c r="H755" s="3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I755" s="0" t="s">
         <v>21</v>
@@ -30851,7 +30851,7 @@
         <v>391</v>
       </c>
       <c r="H763" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I763" s="0" t="s">
         <v>21</v>
@@ -31344,7 +31344,7 @@
         <v>391</v>
       </c>
       <c r="H780" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I780" s="0" t="s">
         <v>21</v>
@@ -31431,7 +31431,7 @@
         <v>391</v>
       </c>
       <c r="H783" s="3" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I783" s="0" t="s">
         <v>21</v>
@@ -31663,7 +31663,7 @@
         <v>391</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -31692,7 +31692,7 @@
         <v>391</v>
       </c>
       <c r="H792" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I792" s="0" t="s">
         <v>21</v>
@@ -31721,7 +31721,7 @@
         <v>391</v>
       </c>
       <c r="H793" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I793" s="0" t="s">
         <v>21</v>
@@ -31779,7 +31779,7 @@
         <v>391</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I795" s="0" t="s">
         <v>21</v>
@@ -32591,7 +32591,7 @@
         <v>391</v>
       </c>
       <c r="H823" s="3" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I823" s="0" t="s">
         <v>21</v>
@@ -32620,7 +32620,7 @@
         <v>391</v>
       </c>
       <c r="H824" s="3" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I824" s="0" t="s">
         <v>21</v>
@@ -33258,7 +33258,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-870</v>
+        <v>-873</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -34186,7 +34186,7 @@
         <v>391</v>
       </c>
       <c r="H878" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I878" s="0" t="s">
         <v>21</v>
@@ -34679,7 +34679,7 @@
         <v>391</v>
       </c>
       <c r="H895" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I895" s="0" t="s">
         <v>21</v>
@@ -34882,7 +34882,7 @@
         <v>391</v>
       </c>
       <c r="H902" s="3" t="n">
-        <v>-7</v>
+        <v>-12</v>
       </c>
       <c r="I902" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>7830.2</v>
+        <v>7656.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>13 October 2026</t>
+    <t>14 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>7656.2</v>
+        <v>7655.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -13161,7 +13161,7 @@
         <v>20</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I153" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -15974,7 +15974,7 @@
         <v>20</v>
       </c>
       <c r="H250" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I250" s="0" t="s">
         <v>21</v>
@@ -16728,7 +16728,7 @@
         <v>20</v>
       </c>
       <c r="H276" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I276" s="0" t="s">
         <v>21</v>
@@ -20440,7 +20440,7 @@
         <v>20</v>
       </c>
       <c r="H404" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I404" s="0" t="s">
         <v>21</v>
@@ -20866,7 +20866,7 @@
         <v>260</v>
       </c>
       <c r="E419" s="3" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F419" s="2" t="s">
         <v>689</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21513,7 +21513,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21948,7 +21948,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-504</v>
+        <v>-506</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-755</v>
+        <v>-757</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -25854,7 +25854,7 @@
         <v>750</v>
       </c>
       <c r="E591" s="3" t="n">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="F591" s="2" t="s">
         <v>19</v>
@@ -25863,7 +25863,7 @@
         <v>391</v>
       </c>
       <c r="H591" s="3" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I591" s="0" t="s">
         <v>21</v>
@@ -28937,7 +28937,7 @@
         <v>850</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29749,7 +29749,7 @@
         <v>391</v>
       </c>
       <c r="H725" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I725" s="0" t="s">
         <v>21</v>
@@ -29778,7 +29778,7 @@
         <v>391</v>
       </c>
       <c r="H726" s="3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I726" s="0" t="s">
         <v>21</v>
@@ -33258,7 +33258,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-873</v>
+        <v>-876</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -35859,7 +35859,7 @@
         <v>5</v>
       </c>
       <c r="E936" s="3" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="F936" s="2" t="s">
         <v>19</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>7655.2</v>
+        <v>7846.2</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -10464,7 +10464,7 @@
         <v>20</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I60" s="0" t="s">
         <v>21</v>
@@ -12958,7 +12958,7 @@
         <v>20</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>21</v>
@@ -14379,7 +14379,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14408,7 +14408,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14495,7 +14495,7 @@
         <v>391</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I199" s="0" t="s">
         <v>21</v>
@@ -18439,7 +18439,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18555,7 +18555,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18613,7 +18613,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19483,7 +19483,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19512,7 +19512,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -20440,7 +20440,7 @@
         <v>20</v>
       </c>
       <c r="H404" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I404" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21252,7 +21252,7 @@
         <v>391</v>
       </c>
       <c r="H432" s="3" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I432" s="0" t="s">
         <v>21</v>
@@ -21310,7 +21310,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>915</v>
+        <v>895</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6536.8</v>
+        <v>-6550.4</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22151,7 +22151,7 @@
         <v>391</v>
       </c>
       <c r="H463" s="3" t="n">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="I463" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22296,7 +22296,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22412,7 +22412,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>9</v>
+        <v>-2</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22499,7 +22499,7 @@
         <v>391</v>
       </c>
       <c r="H475" s="3" t="n">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="I475" s="0" t="s">
         <v>21</v>
@@ -22528,7 +22528,7 @@
         <v>391</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22847,7 +22847,7 @@
         <v>391</v>
       </c>
       <c r="H487" s="3" t="n">
-        <v>-28</v>
+        <v>-58</v>
       </c>
       <c r="I487" s="0" t="s">
         <v>21</v>
@@ -23137,7 +23137,7 @@
         <v>391</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I497" s="0" t="s">
         <v>21</v>
@@ -23456,7 +23456,7 @@
         <v>391</v>
       </c>
       <c r="H508" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I508" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23543,7 +23543,7 @@
         <v>391</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I511" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -25196,7 +25196,7 @@
         <v>20</v>
       </c>
       <c r="H568" s="3" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="I568" s="0" t="s">
         <v>21</v>
@@ -25544,7 +25544,7 @@
         <v>391</v>
       </c>
       <c r="H580" s="3" t="n">
-        <v>25</v>
+        <v>-3</v>
       </c>
       <c r="I580" s="0" t="s">
         <v>21</v>
@@ -25863,7 +25863,7 @@
         <v>391</v>
       </c>
       <c r="H591" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I591" s="0" t="s">
         <v>21</v>
@@ -26385,7 +26385,7 @@
         <v>391</v>
       </c>
       <c r="H609" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I609" s="0" t="s">
         <v>21</v>
@@ -27255,7 +27255,7 @@
         <v>391</v>
       </c>
       <c r="H639" s="3" t="n">
-        <v>-84</v>
+        <v>-85</v>
       </c>
       <c r="I639" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -27980,7 +27980,7 @@
         <v>391</v>
       </c>
       <c r="H664" s="3" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="I664" s="0" t="s">
         <v>21</v>
@@ -28357,7 +28357,7 @@
         <v>391</v>
       </c>
       <c r="H677" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I677" s="0" t="s">
         <v>21</v>
@@ -28879,7 +28879,7 @@
         <v>391</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>-9</v>
+        <v>-21</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -28937,7 +28937,7 @@
         <v>850</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -30880,7 +30880,7 @@
         <v>391</v>
       </c>
       <c r="H764" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I764" s="0" t="s">
         <v>21</v>
@@ -31025,7 +31025,7 @@
         <v>391</v>
       </c>
       <c r="H769" s="3" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I769" s="0" t="s">
         <v>21</v>
@@ -31344,7 +31344,7 @@
         <v>391</v>
       </c>
       <c r="H780" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I780" s="0" t="s">
         <v>21</v>
@@ -31779,7 +31779,7 @@
         <v>391</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I795" s="0" t="s">
         <v>21</v>
@@ -31953,7 +31953,7 @@
         <v>391</v>
       </c>
       <c r="H801" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I801" s="0" t="s">
         <v>21</v>
@@ -32098,7 +32098,7 @@
         <v>391</v>
       </c>
       <c r="H806" s="3" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I806" s="0" t="s">
         <v>21</v>
@@ -32620,7 +32620,7 @@
         <v>391</v>
       </c>
       <c r="H824" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I824" s="0" t="s">
         <v>21</v>
@@ -33084,7 +33084,7 @@
         <v>391</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-64</v>
+        <v>-65</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -34360,7 +34360,7 @@
         <v>391</v>
       </c>
       <c r="H884" s="3" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I884" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -36100,7 +36100,7 @@
         <v>391</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I944" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>7846.2</v>
+        <v>7497.6</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>14 October 2026</t>
+    <t>15 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -16757,7 +16757,7 @@
         <v>20</v>
       </c>
       <c r="H277" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I277" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>7497.6</v>
+        <v>7495.6</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9536,7 +9536,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I28" s="0" t="s">
         <v>21</v>
@@ -11160,7 +11160,7 @@
         <v>20</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I84" s="0" t="s">
         <v>21</v>
@@ -11972,7 +11972,7 @@
         <v>20</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I112" s="0" t="s">
         <v>21</v>
@@ -12175,7 +12175,7 @@
         <v>20</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I119" s="0" t="s">
         <v>21</v>
@@ -12639,7 +12639,7 @@
         <v>20</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I135" s="0" t="s">
         <v>21</v>
@@ -12668,7 +12668,7 @@
         <v>20</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I136" s="0" t="s">
         <v>21</v>
@@ -12958,7 +12958,7 @@
         <v>20</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>21</v>
@@ -13335,7 +13335,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -14466,7 +14466,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -17250,7 +17250,7 @@
         <v>20</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I294" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -20063,7 +20063,7 @@
         <v>20</v>
       </c>
       <c r="H391" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I391" s="0" t="s">
         <v>21</v>
@@ -20324,7 +20324,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21513,7 +21513,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-757</v>
+        <v>-758</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -31402,7 +31402,7 @@
         <v>391</v>
       </c>
       <c r="H782" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I782" s="0" t="s">
         <v>21</v>
@@ -31518,7 +31518,7 @@
         <v>391</v>
       </c>
       <c r="H786" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I786" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>7495.6</v>
+        <v>7462.6</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -13161,7 +13161,7 @@
         <v>20</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I153" s="0" t="s">
         <v>21</v>
@@ -15684,7 +15684,7 @@
         <v>20</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I240" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18555,7 +18555,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18584,7 +18584,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18613,7 +18613,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -19048,7 +19048,7 @@
         <v>391</v>
       </c>
       <c r="H356" s="3" t="n">
-        <v>45</v>
+        <v>245</v>
       </c>
       <c r="I356" s="0" t="s">
         <v>21</v>
@@ -19135,7 +19135,7 @@
         <v>391</v>
       </c>
       <c r="H359" s="3" t="n">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="I359" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19483,7 +19483,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -20469,7 +20469,7 @@
         <v>20</v>
       </c>
       <c r="H405" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I405" s="0" t="s">
         <v>21</v>
@@ -20817,7 +20817,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21252,7 +21252,7 @@
         <v>391</v>
       </c>
       <c r="H432" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I432" s="0" t="s">
         <v>21</v>
@@ -21310,7 +21310,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6550.4</v>
+        <v>-6560</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -22267,7 +22267,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22383,7 +22383,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22412,7 +22412,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22905,7 +22905,7 @@
         <v>391</v>
       </c>
       <c r="H489" s="3" t="n">
-        <v>-417</v>
+        <v>-418</v>
       </c>
       <c r="I489" s="0" t="s">
         <v>21</v>
@@ -23137,7 +23137,7 @@
         <v>391</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I497" s="0" t="s">
         <v>21</v>
@@ -23427,7 +23427,7 @@
         <v>391</v>
       </c>
       <c r="H507" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I507" s="0" t="s">
         <v>21</v>
@@ -23456,7 +23456,7 @@
         <v>391</v>
       </c>
       <c r="H508" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I508" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -25544,7 +25544,7 @@
         <v>391</v>
       </c>
       <c r="H580" s="3" t="n">
-        <v>-3</v>
+        <v>97</v>
       </c>
       <c r="I580" s="0" t="s">
         <v>21</v>
@@ -25921,7 +25921,7 @@
         <v>391</v>
       </c>
       <c r="H593" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I593" s="0" t="s">
         <v>21</v>
@@ -26385,7 +26385,7 @@
         <v>391</v>
       </c>
       <c r="H609" s="3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I609" s="0" t="s">
         <v>21</v>
@@ -26443,7 +26443,7 @@
         <v>391</v>
       </c>
       <c r="H611" s="3" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I611" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28937,7 +28937,7 @@
         <v>850</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30097,7 +30097,7 @@
         <v>391</v>
       </c>
       <c r="H737" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I737" s="0" t="s">
         <v>21</v>
@@ -30822,7 +30822,7 @@
         <v>391</v>
       </c>
       <c r="H762" s="3" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="I762" s="0" t="s">
         <v>21</v>
@@ -30851,7 +30851,7 @@
         <v>391</v>
       </c>
       <c r="H763" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I763" s="0" t="s">
         <v>21</v>
@@ -30880,7 +30880,7 @@
         <v>391</v>
       </c>
       <c r="H764" s="3" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I764" s="0" t="s">
         <v>21</v>
@@ -31025,7 +31025,7 @@
         <v>391</v>
       </c>
       <c r="H769" s="3" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="I769" s="0" t="s">
         <v>21</v>
@@ -31083,7 +31083,7 @@
         <v>391</v>
       </c>
       <c r="H771" s="3" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I771" s="0" t="s">
         <v>836</v>
@@ -31286,7 +31286,7 @@
         <v>391</v>
       </c>
       <c r="H778" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I778" s="0" t="s">
         <v>21</v>
@@ -34360,7 +34360,7 @@
         <v>391</v>
       </c>
       <c r="H884" s="3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I884" s="0" t="s">
         <v>21</v>
@@ -34679,7 +34679,7 @@
         <v>391</v>
       </c>
       <c r="H895" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I895" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -36013,7 +36013,7 @@
         <v>391</v>
       </c>
       <c r="H941" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I941" s="0" t="s">
         <v>21</v>
@@ -36100,7 +36100,7 @@
         <v>391</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I944" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>7462.6</v>
+        <v>7919</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>15 October 2026</t>
+    <t>16 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -13335,7 +13335,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>7919</v>
+        <v>7918</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -12610,7 +12610,7 @@
         <v>20</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I134" s="0" t="s">
         <v>21</v>
@@ -12871,7 +12871,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -12958,7 +12958,7 @@
         <v>20</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>21</v>
@@ -13248,7 +13248,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -15684,7 +15684,7 @@
         <v>20</v>
       </c>
       <c r="H240" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I240" s="0" t="s">
         <v>21</v>
@@ -16235,7 +16235,7 @@
         <v>20</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I259" s="0" t="s">
         <v>21</v>
@@ -16757,7 +16757,7 @@
         <v>20</v>
       </c>
       <c r="H277" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I277" s="0" t="s">
         <v>21</v>
@@ -16844,7 +16844,7 @@
         <v>20</v>
       </c>
       <c r="H280" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I280" s="0" t="s">
         <v>21</v>
@@ -17221,7 +17221,7 @@
         <v>20</v>
       </c>
       <c r="H293" s="3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I293" s="0" t="s">
         <v>21</v>
@@ -17250,7 +17250,7 @@
         <v>20</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I294" s="0" t="s">
         <v>21</v>
@@ -18903,7 +18903,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -20208,7 +20208,7 @@
         <v>20</v>
       </c>
       <c r="H396" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I396" s="0" t="s">
         <v>21</v>
@@ -20324,7 +20324,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -20469,7 +20469,7 @@
         <v>20</v>
       </c>
       <c r="H405" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I405" s="0" t="s">
         <v>21</v>
@@ -20730,7 +20730,7 @@
         <v>20</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>-298</v>
+        <v>-302</v>
       </c>
       <c r="I414" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -22180,7 +22180,7 @@
         <v>391</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>836</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23543,7 +23543,7 @@
         <v>391</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="I511" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -25341,7 +25341,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>-323</v>
+        <v>-326</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25399,7 +25399,7 @@
         <v>20</v>
       </c>
       <c r="H575" s="3" t="n">
-        <v>-758</v>
+        <v>-760</v>
       </c>
       <c r="I575" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -28647,7 +28647,7 @@
         <v>391</v>
       </c>
       <c r="H687" s="3" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I687" s="0" t="s">
         <v>21</v>
@@ -28879,7 +28879,7 @@
         <v>391</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>-21</v>
+        <v>-23</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -30619,7 +30619,7 @@
         <v>391</v>
       </c>
       <c r="H755" s="3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I755" s="0" t="s">
         <v>21</v>
@@ -31054,7 +31054,7 @@
         <v>391</v>
       </c>
       <c r="H770" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I770" s="0" t="s">
         <v>836</v>
@@ -31083,7 +31083,7 @@
         <v>391</v>
       </c>
       <c r="H771" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I771" s="0" t="s">
         <v>836</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>7918</v>
+        <v>7870</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9333,7 +9333,7 @@
         <v>20</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="0" t="s">
         <v>21</v>
@@ -10841,7 +10841,7 @@
         <v>20</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I73" s="0" t="s">
         <v>21</v>
@@ -14437,7 +14437,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14466,7 +14466,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -14930,7 +14930,7 @@
         <v>20</v>
       </c>
       <c r="H214" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I214" s="0" t="s">
         <v>21</v>
@@ -18468,7 +18468,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18526,7 +18526,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18555,7 +18555,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18584,7 +18584,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18729,7 +18729,7 @@
         <v>391</v>
       </c>
       <c r="H345" s="3" t="n">
-        <v>-2</v>
+        <v>6</v>
       </c>
       <c r="I345" s="0" t="s">
         <v>21</v>
@@ -19338,7 +19338,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19367,7 +19367,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19396,7 +19396,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19570,7 +19570,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -19599,7 +19599,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19628,7 +19628,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -19657,7 +19657,7 @@
         <v>391</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I377" s="0" t="s">
         <v>21</v>
@@ -20121,7 +20121,7 @@
         <v>20</v>
       </c>
       <c r="H393" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I393" s="0" t="s">
         <v>21</v>
@@ -20875,7 +20875,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21310,7 +21310,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>891</v>
+        <v>881</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21919,7 +21919,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6560</v>
+        <v>-6568</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -21948,7 +21948,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-506</v>
+        <v>-510</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22122,7 +22122,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -22615,7 +22615,7 @@
         <v>391</v>
       </c>
       <c r="H479" s="3" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I479" s="0" t="s">
         <v>21</v>
@@ -22644,7 +22644,7 @@
         <v>391</v>
       </c>
       <c r="H480" s="3" t="n">
-        <v>-20</v>
+        <v>-40</v>
       </c>
       <c r="I480" s="0" t="s">
         <v>21</v>
@@ -22702,7 +22702,7 @@
         <v>391</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I482" s="0" t="s">
         <v>21</v>
@@ -23427,7 +23427,7 @@
         <v>391</v>
       </c>
       <c r="H507" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I507" s="0" t="s">
         <v>21</v>
@@ -23456,7 +23456,7 @@
         <v>391</v>
       </c>
       <c r="H508" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I508" s="0" t="s">
         <v>21</v>
@@ -23485,7 +23485,7 @@
         <v>391</v>
       </c>
       <c r="H509" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I509" s="0" t="s">
         <v>21</v>
@@ -23514,7 +23514,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23543,7 +23543,7 @@
         <v>391</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I511" s="0" t="s">
         <v>21</v>
@@ -23572,7 +23572,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -23775,7 +23775,7 @@
         <v>391</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I519" s="0" t="s">
         <v>21</v>
@@ -25486,7 +25486,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -27255,7 +27255,7 @@
         <v>391</v>
       </c>
       <c r="H639" s="3" t="n">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="I639" s="0" t="s">
         <v>21</v>
@@ -27284,7 +27284,7 @@
         <v>391</v>
       </c>
       <c r="H640" s="3" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I640" s="0" t="s">
         <v>21</v>
@@ -28589,7 +28589,7 @@
         <v>391</v>
       </c>
       <c r="H685" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I685" s="0" t="s">
         <v>21</v>
@@ -28821,7 +28821,7 @@
         <v>391</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I693" s="0" t="s">
         <v>21</v>
@@ -28879,7 +28879,7 @@
         <v>391</v>
       </c>
       <c r="H695" s="3" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="I695" s="0" t="s">
         <v>21</v>
@@ -28966,7 +28966,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29024,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29285,7 +29285,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30532,7 +30532,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -31460,7 +31460,7 @@
         <v>391</v>
       </c>
       <c r="H784" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I784" s="0" t="s">
         <v>21</v>
@@ -31779,7 +31779,7 @@
         <v>391</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I795" s="0" t="s">
         <v>21</v>
@@ -31866,7 +31866,7 @@
         <v>391</v>
       </c>
       <c r="H798" s="3" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I798" s="0" t="s">
         <v>21</v>
@@ -32475,7 +32475,7 @@
         <v>391</v>
       </c>
       <c r="H819" s="3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I819" s="0" t="s">
         <v>21</v>
@@ -32707,7 +32707,7 @@
         <v>391</v>
       </c>
       <c r="H827" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I827" s="0" t="s">
         <v>21</v>
@@ -33258,7 +33258,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-876</v>
+        <v>-881</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -34679,7 +34679,7 @@
         <v>391</v>
       </c>
       <c r="H895" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I895" s="0" t="s">
         <v>21</v>
@@ -35781,7 +35781,7 @@
         <v>391</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -37007,7 +37007,7 @@
     </row>
     <row r="976" spans="8:8" customHeight="1">
       <c r="H976" s="3" t="n">
-        <v>7870</v>
+        <v>7665</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>16 October 2026</t>
+    <t>17 October 2026</t>
   </si>
   <si>
     <t>To</t>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="1971">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1973" uniqueCount="1973">
   <si>
     <t>รายงานสินค้าคงเหลือตาม SKU</t>
   </si>
@@ -8030,6 +8030,15 @@
   </si>
   <si>
     <t>เอมเค ข้าวโพดแท่งอบกรอบ รสนม</t>
+  </si>
+  <si>
+    <r>
+      <rPr/>
+      <t xml:space="preserve">8851123241274</t>
+    </r>
+  </si>
+  <si>
+    <t>เอ็มร้อยห้าสิบ M-150</t>
   </si>
   <si>
     <r>
@@ -8889,7 +8898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I976"/>
+  <dimension ref="A1:I977"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="15" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -10058,7 +10067,7 @@
         <v>20</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I46" s="0" t="s">
         <v>21</v>
@@ -11276,7 +11285,7 @@
         <v>20</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I88" s="0" t="s">
         <v>21</v>
@@ -11682,7 +11691,7 @@
         <v>20</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I102" s="0" t="s">
         <v>21</v>
@@ -11711,7 +11720,7 @@
         <v>20</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>21</v>
@@ -12117,7 +12126,7 @@
         <v>20</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I117" s="0" t="s">
         <v>21</v>
@@ -12407,7 +12416,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -12639,7 +12648,7 @@
         <v>20</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I135" s="0" t="s">
         <v>21</v>
@@ -12871,7 +12880,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13161,7 +13170,7 @@
         <v>20</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I153" s="0" t="s">
         <v>21</v>
@@ -13335,7 +13344,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -13393,7 +13402,7 @@
         <v>20</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" s="0" t="s">
         <v>21</v>
@@ -13422,7 +13431,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -16380,7 +16389,7 @@
         <v>20</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I264" s="0" t="s">
         <v>21</v>
@@ -25477,7 +25486,7 @@
         <v>10</v>
       </c>
       <c r="E578" s="3" t="n">
-        <v>5.38</v>
+        <v>5.83</v>
       </c>
       <c r="F578" s="2" t="s">
         <v>19</v>
@@ -25486,7 +25495,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-18</v>
+        <v>-14</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -29024,7 +29033,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -34464,10 +34473,10 @@
         <v>1795</v>
       </c>
       <c r="D888" s="3" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E888" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F888" s="2" t="s">
         <v>19</v>
@@ -34476,10 +34485,10 @@
         <v>20</v>
       </c>
       <c r="H888" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I888" s="0" t="s">
-        <v>21</v>
+        <v>836</v>
       </c>
     </row>
     <row r="889" spans="1:9" customHeight="1">
@@ -34496,7 +34505,7 @@
         <v>25</v>
       </c>
       <c r="E889" s="3" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F889" s="2" t="s">
         <v>19</v>
@@ -34505,7 +34514,7 @@
         <v>20</v>
       </c>
       <c r="H889" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I889" s="0" t="s">
         <v>21</v>
@@ -34522,10 +34531,10 @@
         <v>1799</v>
       </c>
       <c r="D890" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E890" s="3" t="n">
-        <v>4.08</v>
+        <v>21</v>
       </c>
       <c r="F890" s="2" t="s">
         <v>19</v>
@@ -34554,16 +34563,16 @@
         <v>5</v>
       </c>
       <c r="E891" s="3" t="n">
-        <v>2.5</v>
+        <v>4.08</v>
       </c>
       <c r="F891" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G891" s="2" t="s">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="H891" s="3" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="I891" s="0" t="s">
         <v>21</v>
@@ -34592,7 +34601,7 @@
         <v>391</v>
       </c>
       <c r="H892" s="3" t="n">
-        <v>-199</v>
+        <v>-30</v>
       </c>
       <c r="I892" s="0" t="s">
         <v>21</v>
@@ -34621,7 +34630,7 @@
         <v>391</v>
       </c>
       <c r="H893" s="3" t="n">
-        <v>0</v>
+        <v>-199</v>
       </c>
       <c r="I893" s="0" t="s">
         <v>21</v>
@@ -34638,10 +34647,10 @@
         <v>1807</v>
       </c>
       <c r="D894" s="3" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="E894" s="3" t="n">
-        <v>9</v>
+        <v>2.5</v>
       </c>
       <c r="F894" s="2" t="s">
         <v>19</v>
@@ -34667,10 +34676,10 @@
         <v>1809</v>
       </c>
       <c r="D895" s="3" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E895" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F895" s="2" t="s">
         <v>19</v>
@@ -34679,7 +34688,7 @@
         <v>391</v>
       </c>
       <c r="H895" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I895" s="0" t="s">
         <v>21</v>
@@ -34699,16 +34708,16 @@
         <v>20</v>
       </c>
       <c r="E896" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F896" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G896" s="2" t="s">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="H896" s="3" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="I896" s="0" t="s">
         <v>21</v>
@@ -34728,7 +34737,7 @@
         <v>20</v>
       </c>
       <c r="E897" s="3" t="n">
-        <v>16.67</v>
+        <v>15</v>
       </c>
       <c r="F897" s="2" t="s">
         <v>19</v>
@@ -34737,7 +34746,7 @@
         <v>20</v>
       </c>
       <c r="H897" s="3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I897" s="0" t="s">
         <v>21</v>
@@ -34754,10 +34763,10 @@
         <v>1815</v>
       </c>
       <c r="D898" s="3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E898" s="3" t="n">
-        <v>13</v>
+        <v>16.67</v>
       </c>
       <c r="F898" s="2" t="s">
         <v>19</v>
@@ -34766,7 +34775,7 @@
         <v>20</v>
       </c>
       <c r="H898" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I898" s="0" t="s">
         <v>21</v>
@@ -34783,10 +34792,10 @@
         <v>1817</v>
       </c>
       <c r="D899" s="3" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="E899" s="3" t="n">
-        <v>25.66</v>
+        <v>13</v>
       </c>
       <c r="F899" s="2" t="s">
         <v>19</v>
@@ -34812,16 +34821,16 @@
         <v>1819</v>
       </c>
       <c r="D900" s="3" t="n">
-        <v>9000</v>
+        <v>37</v>
       </c>
       <c r="E900" s="3" t="n">
-        <v>5400</v>
+        <v>25.66</v>
       </c>
       <c r="F900" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G900" s="2" t="s">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="H900" s="3" t="n">
         <v>0</v>
@@ -34841,10 +34850,10 @@
         <v>1821</v>
       </c>
       <c r="D901" s="3" t="n">
-        <v>40</v>
+        <v>9000</v>
       </c>
       <c r="E901" s="3" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="F901" s="2" t="s">
         <v>19</v>
@@ -34853,7 +34862,7 @@
         <v>391</v>
       </c>
       <c r="H901" s="3" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="I901" s="0" t="s">
         <v>21</v>
@@ -34870,7 +34879,7 @@
         <v>1823</v>
       </c>
       <c r="D902" s="3" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E902" s="3" t="n">
         <v>0</v>
@@ -34882,7 +34891,7 @@
         <v>391</v>
       </c>
       <c r="H902" s="3" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="I902" s="0" t="s">
         <v>21</v>
@@ -34899,10 +34908,10 @@
         <v>1825</v>
       </c>
       <c r="D903" s="3" t="n">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="E903" s="3" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F903" s="2" t="s">
         <v>19</v>
@@ -34911,7 +34920,7 @@
         <v>391</v>
       </c>
       <c r="H903" s="3" t="n">
-        <v>49</v>
+        <v>-12</v>
       </c>
       <c r="I903" s="0" t="s">
         <v>21</v>
@@ -34940,7 +34949,7 @@
         <v>391</v>
       </c>
       <c r="H904" s="3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I904" s="0" t="s">
         <v>21</v>
@@ -34957,19 +34966,19 @@
         <v>1829</v>
       </c>
       <c r="D905" s="3" t="n">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="E905" s="3" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F905" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G905" s="2" t="s">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="H905" s="3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I905" s="0" t="s">
         <v>21</v>
@@ -34989,7 +34998,7 @@
         <v>20</v>
       </c>
       <c r="E906" s="3" t="n">
-        <v>16.33</v>
+        <v>18</v>
       </c>
       <c r="F906" s="2" t="s">
         <v>19</v>
@@ -35015,10 +35024,10 @@
         <v>1833</v>
       </c>
       <c r="D907" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E907" s="3" t="n">
-        <v>3</v>
+        <v>16.33</v>
       </c>
       <c r="F907" s="2" t="s">
         <v>19</v>
@@ -35044,10 +35053,10 @@
         <v>1835</v>
       </c>
       <c r="D908" s="3" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E908" s="3" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F908" s="2" t="s">
         <v>19</v>
@@ -35073,10 +35082,10 @@
         <v>1837</v>
       </c>
       <c r="D909" s="3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E909" s="3" t="n">
-        <v>12.16</v>
+        <v>14</v>
       </c>
       <c r="F909" s="2" t="s">
         <v>19</v>
@@ -35105,7 +35114,7 @@
         <v>15</v>
       </c>
       <c r="E910" s="3" t="n">
-        <v>10.5</v>
+        <v>12.16</v>
       </c>
       <c r="F910" s="2" t="s">
         <v>19</v>
@@ -35131,10 +35140,10 @@
         <v>1841</v>
       </c>
       <c r="D911" s="3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E911" s="3" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="F911" s="2" t="s">
         <v>19</v>
@@ -35160,10 +35169,10 @@
         <v>1843</v>
       </c>
       <c r="D912" s="3" t="n">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="E912" s="3" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="F912" s="2" t="s">
         <v>19</v>
@@ -35189,10 +35198,10 @@
         <v>1845</v>
       </c>
       <c r="D913" s="3" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E913" s="3" t="n">
-        <v>16.66</v>
+        <v>70</v>
       </c>
       <c r="F913" s="2" t="s">
         <v>19</v>
@@ -35218,10 +35227,10 @@
         <v>1847</v>
       </c>
       <c r="D914" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E914" s="3" t="n">
-        <v>4.08</v>
+        <v>16.66</v>
       </c>
       <c r="F914" s="2" t="s">
         <v>19</v>
@@ -35247,10 +35256,10 @@
         <v>1849</v>
       </c>
       <c r="D915" s="3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E915" s="3" t="n">
-        <v>17.16</v>
+        <v>4.08</v>
       </c>
       <c r="F915" s="2" t="s">
         <v>19</v>
@@ -35279,7 +35288,7 @@
         <v>20</v>
       </c>
       <c r="E916" s="3" t="n">
-        <v>17</v>
+        <v>17.16</v>
       </c>
       <c r="F916" s="2" t="s">
         <v>19</v>
@@ -35288,7 +35297,7 @@
         <v>20</v>
       </c>
       <c r="H916" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I916" s="0" t="s">
         <v>21</v>
@@ -35308,7 +35317,7 @@
         <v>20</v>
       </c>
       <c r="E917" s="3" t="n">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="F917" s="2" t="s">
         <v>19</v>
@@ -35317,7 +35326,7 @@
         <v>20</v>
       </c>
       <c r="H917" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I917" s="0" t="s">
         <v>21</v>
@@ -35337,7 +35346,7 @@
         <v>20</v>
       </c>
       <c r="E918" s="3" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="F918" s="2" t="s">
         <v>19</v>
@@ -35363,10 +35372,10 @@
         <v>1857</v>
       </c>
       <c r="D919" s="3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E919" s="3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F919" s="2" t="s">
         <v>19</v>
@@ -35392,10 +35401,10 @@
         <v>1859</v>
       </c>
       <c r="D920" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E920" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F920" s="2" t="s">
         <v>19</v>
@@ -35421,10 +35430,10 @@
         <v>1861</v>
       </c>
       <c r="D921" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E921" s="3" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="F921" s="2" t="s">
         <v>19</v>
@@ -35453,7 +35462,7 @@
         <v>5</v>
       </c>
       <c r="E922" s="3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="F922" s="2" t="s">
         <v>19</v>
@@ -35479,10 +35488,10 @@
         <v>1865</v>
       </c>
       <c r="D923" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E923" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F923" s="2" t="s">
         <v>19</v>
@@ -35508,10 +35517,10 @@
         <v>1867</v>
       </c>
       <c r="D924" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E924" s="3" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="F924" s="2" t="s">
         <v>19</v>
@@ -35537,10 +35546,10 @@
         <v>1869</v>
       </c>
       <c r="D925" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E925" s="3" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="F925" s="2" t="s">
         <v>19</v>
@@ -35566,10 +35575,10 @@
         <v>1871</v>
       </c>
       <c r="D926" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E926" s="3" t="n">
-        <v>4.13</v>
+        <v>9.5</v>
       </c>
       <c r="F926" s="2" t="s">
         <v>19</v>
@@ -35578,7 +35587,7 @@
         <v>20</v>
       </c>
       <c r="H926" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I926" s="0" t="s">
         <v>21</v>
@@ -35595,19 +35604,19 @@
         <v>1873</v>
       </c>
       <c r="D927" s="3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="E927" s="3" t="n">
-        <v>40</v>
+        <v>4.13</v>
       </c>
       <c r="F927" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G927" s="2" t="s">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="H927" s="3" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I927" s="0" t="s">
         <v>21</v>
@@ -35636,7 +35645,7 @@
         <v>391</v>
       </c>
       <c r="H928" s="3" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I928" s="0" t="s">
         <v>21</v>
@@ -35665,7 +35674,7 @@
         <v>391</v>
       </c>
       <c r="H929" s="3" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="I929" s="0" t="s">
         <v>21</v>
@@ -35694,7 +35703,7 @@
         <v>391</v>
       </c>
       <c r="H930" s="3" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="I930" s="0" t="s">
         <v>21</v>
@@ -35711,19 +35720,19 @@
         <v>1881</v>
       </c>
       <c r="D931" s="3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E931" s="3" t="n">
-        <v>20.83</v>
+        <v>40</v>
       </c>
       <c r="F931" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G931" s="2" t="s">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="H931" s="3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I931" s="0" t="s">
         <v>21</v>
@@ -35740,10 +35749,10 @@
         <v>1883</v>
       </c>
       <c r="D932" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E932" s="3" t="n">
-        <v>4.16</v>
+        <v>20.83</v>
       </c>
       <c r="F932" s="2" t="s">
         <v>19</v>
@@ -35752,7 +35761,7 @@
         <v>20</v>
       </c>
       <c r="H932" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I932" s="0" t="s">
         <v>21</v>
@@ -35769,19 +35778,19 @@
         <v>1885</v>
       </c>
       <c r="D933" s="3" t="n">
-        <v>170</v>
+        <v>5</v>
       </c>
       <c r="E933" s="3" t="n">
-        <v>52</v>
+        <v>4.16</v>
       </c>
       <c r="F933" s="2" t="s">
-        <v>394</v>
+        <v>19</v>
       </c>
       <c r="G933" s="2" t="s">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="H933" s="3" t="n">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="I933" s="0" t="s">
         <v>21</v>
@@ -35798,10 +35807,10 @@
         <v>1887</v>
       </c>
       <c r="D934" s="3" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="E934" s="3" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F934" s="2" t="s">
         <v>394</v>
@@ -35810,7 +35819,7 @@
         <v>391</v>
       </c>
       <c r="H934" s="3" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="I934" s="0" t="s">
         <v>21</v>
@@ -35827,16 +35836,16 @@
         <v>1889</v>
       </c>
       <c r="D935" s="3" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E935" s="3" t="n">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="F935" s="2" t="s">
-        <v>19</v>
+        <v>394</v>
       </c>
       <c r="G935" s="2" t="s">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="H935" s="3" t="n">
         <v>0</v>
@@ -35856,10 +35865,10 @@
         <v>1891</v>
       </c>
       <c r="D936" s="3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E936" s="3" t="n">
-        <v>4.5</v>
+        <v>17</v>
       </c>
       <c r="F936" s="2" t="s">
         <v>19</v>
@@ -35868,7 +35877,7 @@
         <v>20</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -35885,10 +35894,10 @@
         <v>1893</v>
       </c>
       <c r="D937" s="3" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E937" s="3" t="n">
-        <v>25</v>
+        <v>4.5</v>
       </c>
       <c r="F937" s="2" t="s">
         <v>19</v>
@@ -35897,7 +35906,7 @@
         <v>20</v>
       </c>
       <c r="H937" s="3" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="I937" s="0" t="s">
         <v>21</v>
@@ -35914,10 +35923,10 @@
         <v>1895</v>
       </c>
       <c r="D938" s="3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E938" s="3" t="n">
-        <v>14.33</v>
+        <v>25</v>
       </c>
       <c r="F938" s="2" t="s">
         <v>19</v>
@@ -35926,10 +35935,10 @@
         <v>20</v>
       </c>
       <c r="H938" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I938" s="0" t="s">
-        <v>836</v>
+        <v>21</v>
       </c>
     </row>
     <row r="939" spans="1:9" customHeight="1">
@@ -35943,10 +35952,10 @@
         <v>1897</v>
       </c>
       <c r="D939" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E939" s="3" t="n">
-        <v>4.98</v>
+        <v>14.33</v>
       </c>
       <c r="F939" s="2" t="s">
         <v>19</v>
@@ -35955,10 +35964,10 @@
         <v>20</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I939" s="0" t="s">
-        <v>21</v>
+        <v>836</v>
       </c>
     </row>
     <row r="940" spans="1:9" customHeight="1">
@@ -35972,19 +35981,19 @@
         <v>1899</v>
       </c>
       <c r="D940" s="3" t="n">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="E940" s="3" t="n">
-        <v>30</v>
+        <v>4.98</v>
       </c>
       <c r="F940" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G940" s="2" t="s">
-        <v>391</v>
+        <v>20</v>
       </c>
       <c r="H940" s="3" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="I940" s="0" t="s">
         <v>21</v>
@@ -36001,10 +36010,10 @@
         <v>1901</v>
       </c>
       <c r="D941" s="3" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="E941" s="3" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F941" s="2" t="s">
         <v>19</v>
@@ -36013,7 +36022,7 @@
         <v>391</v>
       </c>
       <c r="H941" s="3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I941" s="0" t="s">
         <v>21</v>
@@ -36030,10 +36039,10 @@
         <v>1903</v>
       </c>
       <c r="D942" s="3" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E942" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F942" s="2" t="s">
         <v>19</v>
@@ -36042,7 +36051,7 @@
         <v>391</v>
       </c>
       <c r="H942" s="3" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I942" s="0" t="s">
         <v>21</v>
@@ -36059,10 +36068,10 @@
         <v>1905</v>
       </c>
       <c r="D943" s="3" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="E943" s="3" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F943" s="2" t="s">
         <v>19</v>
@@ -36071,7 +36080,7 @@
         <v>391</v>
       </c>
       <c r="H943" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I943" s="0" t="s">
         <v>21</v>
@@ -36088,10 +36097,10 @@
         <v>1907</v>
       </c>
       <c r="D944" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E944" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F944" s="2" t="s">
         <v>19</v>
@@ -36100,7 +36109,7 @@
         <v>391</v>
       </c>
       <c r="H944" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I944" s="0" t="s">
         <v>21</v>
@@ -36117,19 +36126,19 @@
         <v>1909</v>
       </c>
       <c r="D945" s="3" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E945" s="3" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F945" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G945" s="2" t="s">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="H945" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I945" s="0" t="s">
         <v>21</v>
@@ -36146,10 +36155,10 @@
         <v>1911</v>
       </c>
       <c r="D946" s="3" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E946" s="3" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="F946" s="2" t="s">
         <v>19</v>
@@ -36175,10 +36184,10 @@
         <v>1913</v>
       </c>
       <c r="D947" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E947" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F947" s="2" t="s">
         <v>19</v>
@@ -36204,19 +36213,19 @@
         <v>1915</v>
       </c>
       <c r="D948" s="3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E948" s="3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F948" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G948" s="2" t="s">
-        <v>1916</v>
+        <v>20</v>
       </c>
       <c r="H948" s="3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I948" s="0" t="s">
         <v>21</v>
@@ -36227,10 +36236,10 @@
         <v>941</v>
       </c>
       <c r="B949" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="C949" s="2" t="s">
         <v>1917</v>
-      </c>
-      <c r="C949" s="2" t="s">
-        <v>1918</v>
       </c>
       <c r="D949" s="3" t="n">
         <v>20</v>
@@ -36242,10 +36251,10 @@
         <v>19</v>
       </c>
       <c r="G949" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H949" s="3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="I949" s="0" t="s">
         <v>21</v>
@@ -36271,10 +36280,10 @@
         <v>19</v>
       </c>
       <c r="G950" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H950" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I950" s="0" t="s">
         <v>21</v>
@@ -36291,16 +36300,16 @@
         <v>1922</v>
       </c>
       <c r="D951" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E951" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F951" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G951" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H951" s="3" t="n">
         <v>0</v>
@@ -36323,13 +36332,13 @@
         <v>10</v>
       </c>
       <c r="E952" s="3" t="n">
-        <v>7.47</v>
+        <v>8</v>
       </c>
       <c r="F952" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G952" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H952" s="3" t="n">
         <v>0</v>
@@ -36349,19 +36358,19 @@
         <v>1926</v>
       </c>
       <c r="D953" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E953" s="3" t="n">
-        <v>16</v>
+        <v>7.47</v>
       </c>
       <c r="F953" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G953" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H953" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I953" s="0" t="s">
         <v>21</v>
@@ -36381,16 +36390,16 @@
         <v>20</v>
       </c>
       <c r="E954" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F954" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G954" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H954" s="3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I954" s="0" t="s">
         <v>21</v>
@@ -36410,16 +36419,16 @@
         <v>20</v>
       </c>
       <c r="E955" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F955" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G955" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H955" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I955" s="0" t="s">
         <v>21</v>
@@ -36445,7 +36454,7 @@
         <v>19</v>
       </c>
       <c r="G956" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H956" s="3" t="n">
         <v>0</v>
@@ -36474,10 +36483,10 @@
         <v>19</v>
       </c>
       <c r="G957" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H957" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I957" s="0" t="s">
         <v>21</v>
@@ -36494,19 +36503,19 @@
         <v>1936</v>
       </c>
       <c r="D958" s="3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E958" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F958" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G958" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H958" s="3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I958" s="0" t="s">
         <v>21</v>
@@ -36532,10 +36541,10 @@
         <v>19</v>
       </c>
       <c r="G959" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H959" s="3" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I959" s="0" t="s">
         <v>21</v>
@@ -36561,10 +36570,10 @@
         <v>19</v>
       </c>
       <c r="G960" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H960" s="3" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I960" s="0" t="s">
         <v>21</v>
@@ -36581,19 +36590,19 @@
         <v>1942</v>
       </c>
       <c r="D961" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="E961" s="2" t="s">
-        <v>707</v>
+        <v>10</v>
+      </c>
+      <c r="E961" s="3" t="n">
+        <v>8</v>
       </c>
       <c r="F961" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G961" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H961" s="3" t="n">
-        <v>-6</v>
+        <v>13</v>
       </c>
       <c r="I961" s="0" t="s">
         <v>21</v>
@@ -36610,19 +36619,19 @@
         <v>1944</v>
       </c>
       <c r="D962" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E962" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="E962" s="2" t="s">
+        <v>707</v>
       </c>
       <c r="F962" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G962" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H962" s="3" t="n">
-        <v>4</v>
+        <v>-6</v>
       </c>
       <c r="I962" s="0" t="s">
         <v>21</v>
@@ -36639,19 +36648,19 @@
         <v>1946</v>
       </c>
       <c r="D963" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E963" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F963" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G963" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H963" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I963" s="0" t="s">
         <v>21</v>
@@ -36677,7 +36686,7 @@
         <v>19</v>
       </c>
       <c r="G964" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H964" s="3" t="n">
         <v>0</v>
@@ -36700,16 +36709,16 @@
         <v>20</v>
       </c>
       <c r="E965" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F965" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G965" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H965" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I965" s="0" t="s">
         <v>21</v>
@@ -36729,16 +36738,16 @@
         <v>20</v>
       </c>
       <c r="E966" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F966" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G966" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H966" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I966" s="0" t="s">
         <v>21</v>
@@ -36764,10 +36773,10 @@
         <v>19</v>
       </c>
       <c r="G967" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H967" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I967" s="0" t="s">
         <v>21</v>
@@ -36793,10 +36802,10 @@
         <v>19</v>
       </c>
       <c r="G968" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H968" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I968" s="0" t="s">
         <v>21</v>
@@ -36813,16 +36822,16 @@
         <v>1958</v>
       </c>
       <c r="D969" s="3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E969" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F969" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G969" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H969" s="3" t="n">
         <v>5</v>
@@ -36842,19 +36851,19 @@
         <v>1960</v>
       </c>
       <c r="D970" s="3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E970" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F970" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G970" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H970" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I970" s="0" t="s">
         <v>21</v>
@@ -36880,10 +36889,10 @@
         <v>19</v>
       </c>
       <c r="G971" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H971" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I971" s="0" t="s">
         <v>21</v>
@@ -36909,10 +36918,10 @@
         <v>19</v>
       </c>
       <c r="G972" s="2" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="H972" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I972" s="0" t="s">
         <v>21</v>
@@ -36929,19 +36938,19 @@
         <v>1966</v>
       </c>
       <c r="D973" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E973" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F973" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G973" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="H973" s="3" t="n">
         <v>4</v>
-      </c>
-      <c r="F973" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G973" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H973" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="I973" s="0" t="s">
         <v>21</v>
@@ -36958,10 +36967,10 @@
         <v>1968</v>
       </c>
       <c r="D974" s="3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E974" s="3" t="n">
-        <v>14.33</v>
+        <v>4</v>
       </c>
       <c r="F974" s="2" t="s">
         <v>19</v>
@@ -36970,10 +36979,10 @@
         <v>20</v>
       </c>
       <c r="H974" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I974" s="0" t="s">
-        <v>836</v>
+        <v>21</v>
       </c>
     </row>
     <row r="975" spans="1:9" customHeight="1">
@@ -36990,24 +36999,53 @@
         <v>20</v>
       </c>
       <c r="E975" s="3" t="n">
+        <v>14.33</v>
+      </c>
+      <c r="F975" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G975" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H975" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I975" s="0" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9" customHeight="1">
+      <c r="A976" s="0" t="n">
+        <v>968</v>
+      </c>
+      <c r="B976" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="C976" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D976" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E976" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="F975" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G975" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H975" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I975" s="0" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="976" spans="8:8" customHeight="1">
+      <c r="F976" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G976" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="H976" s="3" t="n">
-        <v>7665</v>
+        <v>0</v>
+      </c>
+      <c r="I976" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="977" spans="8:8" customHeight="1">
+      <c r="H977" s="3" t="n">
+        <v>7650</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9545,7 +9545,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I28" s="0" t="s">
         <v>21</v>
@@ -9690,7 +9690,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>21</v>
@@ -10154,7 +10154,7 @@
         <v>20</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I49" s="0" t="s">
         <v>21</v>
@@ -11981,7 +11981,7 @@
         <v>20</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I112" s="0" t="s">
         <v>21</v>
@@ -12068,7 +12068,7 @@
         <v>20</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>21</v>
@@ -13344,7 +13344,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -13431,7 +13431,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -14388,7 +14388,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14446,7 +14446,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14475,7 +14475,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -15316,7 +15316,7 @@
         <v>20</v>
       </c>
       <c r="H227" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I227" s="0" t="s">
         <v>21</v>
@@ -17259,7 +17259,7 @@
         <v>20</v>
       </c>
       <c r="H294" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I294" s="0" t="s">
         <v>21</v>
@@ -18448,7 +18448,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18477,7 +18477,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18535,7 +18535,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18622,7 +18622,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -19347,7 +19347,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19405,7 +19405,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19463,7 +19463,7 @@
         <v>391</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19608,7 +19608,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19637,7 +19637,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -19666,7 +19666,7 @@
         <v>391</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I377" s="0" t="s">
         <v>21</v>
@@ -20884,7 +20884,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21522,7 +21522,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21928,7 +21928,7 @@
         <v>391</v>
       </c>
       <c r="H455" s="3" t="n">
-        <v>-6568</v>
+        <v>-6586</v>
       </c>
       <c r="I455" s="0" t="s">
         <v>21</v>
@@ -21957,7 +21957,7 @@
         <v>20</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-510</v>
+        <v>-512</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22044,7 +22044,7 @@
         <v>391</v>
       </c>
       <c r="H459" s="3" t="n">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="I459" s="0" t="s">
         <v>21</v>
@@ -22160,7 +22160,7 @@
         <v>391</v>
       </c>
       <c r="H463" s="3" t="n">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="I463" s="0" t="s">
         <v>21</v>
@@ -22334,7 +22334,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22392,7 +22392,7 @@
         <v>391</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22450,7 +22450,7 @@
         <v>391</v>
       </c>
       <c r="H473" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I473" s="0" t="s">
         <v>21</v>
@@ -22537,7 +22537,7 @@
         <v>391</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22566,7 +22566,7 @@
         <v>391</v>
       </c>
       <c r="H477" s="3" t="n">
-        <v>354</v>
+        <v>324</v>
       </c>
       <c r="I477" s="0" t="s">
         <v>21</v>
@@ -23146,7 +23146,7 @@
         <v>391</v>
       </c>
       <c r="H497" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I497" s="0" t="s">
         <v>21</v>
@@ -23784,7 +23784,7 @@
         <v>391</v>
       </c>
       <c r="H519" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I519" s="0" t="s">
         <v>21</v>
@@ -25495,7 +25495,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -27264,7 +27264,7 @@
         <v>391</v>
       </c>
       <c r="H639" s="3" t="n">
-        <v>-86</v>
+        <v>-90</v>
       </c>
       <c r="I639" s="0" t="s">
         <v>21</v>
@@ -28627,7 +28627,7 @@
         <v>391</v>
       </c>
       <c r="H686" s="3" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I686" s="0" t="s">
         <v>21</v>
@@ -28975,7 +28975,7 @@
         <v>850</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29033,7 +29033,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29294,7 +29294,7 @@
         <v>391</v>
       </c>
       <c r="H709" s="3" t="n">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="I709" s="0" t="s">
         <v>21</v>
@@ -30106,7 +30106,7 @@
         <v>391</v>
       </c>
       <c r="H737" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I737" s="0" t="s">
         <v>21</v>
@@ -30541,7 +30541,7 @@
         <v>850</v>
       </c>
       <c r="H752" s="3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I752" s="0" t="s">
         <v>21</v>
@@ -30860,7 +30860,7 @@
         <v>391</v>
       </c>
       <c r="H763" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I763" s="0" t="s">
         <v>21</v>
@@ -31353,7 +31353,7 @@
         <v>391</v>
       </c>
       <c r="H780" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I780" s="0" t="s">
         <v>21</v>
@@ -31469,7 +31469,7 @@
         <v>391</v>
       </c>
       <c r="H784" s="3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I784" s="0" t="s">
         <v>21</v>
@@ -31788,7 +31788,7 @@
         <v>391</v>
       </c>
       <c r="H795" s="3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I795" s="0" t="s">
         <v>21</v>
@@ -31933,7 +31933,7 @@
         <v>391</v>
       </c>
       <c r="H800" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I800" s="0" t="s">
         <v>21</v>
@@ -33093,7 +33093,7 @@
         <v>391</v>
       </c>
       <c r="H840" s="3" t="n">
-        <v>-65</v>
+        <v>-66</v>
       </c>
       <c r="I840" s="0" t="s">
         <v>21</v>
@@ -33267,7 +33267,7 @@
         <v>20</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-881</v>
+        <v>-885</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -34340,7 +34340,7 @@
         <v>391</v>
       </c>
       <c r="H883" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I883" s="0" t="s">
         <v>21</v>
@@ -35819,7 +35819,7 @@
         <v>391</v>
       </c>
       <c r="H934" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I934" s="0" t="s">
         <v>21</v>
@@ -36138,7 +36138,7 @@
         <v>391</v>
       </c>
       <c r="H945" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I945" s="0" t="s">
         <v>21</v>
@@ -37045,7 +37045,7 @@
     </row>
     <row r="977" spans="8:8" customHeight="1">
       <c r="H977" s="3" t="n">
-        <v>7650</v>
+        <v>7430</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>17 October 2026</t>
+    <t>18 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -11169,7 +11169,7 @@
         <v>20</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I84" s="0" t="s">
         <v>21</v>
@@ -12851,7 +12851,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -37045,7 +37045,7 @@
     </row>
     <row r="977" spans="8:8" customHeight="1">
       <c r="H977" s="3" t="n">
-        <v>7430</v>
+        <v>7428</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -12387,7 +12387,7 @@
         <v>20</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126" s="0" t="s">
         <v>21</v>
@@ -16447,7 +16447,7 @@
         <v>20</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I266" s="0" t="s">
         <v>21</v>
@@ -18535,7 +18535,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -37045,7 +37045,7 @@
     </row>
     <row r="977" spans="8:8" customHeight="1">
       <c r="H977" s="3" t="n">
-        <v>7428</v>
+        <v>7424</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9400,7 +9400,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -9864,7 +9864,7 @@
         <v>20</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I39" s="0" t="s">
         <v>21</v>
@@ -16766,7 +16766,7 @@
         <v>20</v>
       </c>
       <c r="H277" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I277" s="0" t="s">
         <v>21</v>
@@ -37045,7 +37045,7 @@
     </row>
     <row r="977" spans="8:8" customHeight="1">
       <c r="H977" s="3" t="n">
-        <v>7424</v>
+        <v>7419</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>18 October 2026</t>
+    <t>19 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12851,7 +12851,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -37045,7 +37045,7 @@
     </row>
     <row r="977" spans="8:8" customHeight="1">
       <c r="H977" s="3" t="n">
-        <v>7419</v>
+        <v>7418</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -11277,7 +11277,7 @@
         <v>20</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I87" s="0" t="s">
         <v>21</v>
@@ -11538,7 +11538,7 @@
         <v>20</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I96" s="0" t="s">
         <v>21</v>
@@ -14438,7 +14438,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>-6</v>
+        <v>59</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14525,7 +14525,7 @@
         <v>391</v>
       </c>
       <c r="H199" s="3" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I199" s="0" t="s">
         <v>21</v>
@@ -18469,7 +18469,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18498,7 +18498,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18527,7 +18527,7 @@
         <v>391</v>
       </c>
       <c r="H337" s="3" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="I337" s="0" t="s">
         <v>21</v>
@@ -18556,7 +18556,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18585,7 +18585,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18614,7 +18614,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18643,7 +18643,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -19368,7 +19368,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19600,7 +19600,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -19629,7 +19629,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19658,7 +19658,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -20847,7 +20847,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20905,7 +20905,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21340,7 +21340,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21978,7 +21978,7 @@
         <v>391</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-6586</v>
+        <v>-6603</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22326,7 +22326,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22384,7 +22384,7 @@
         <v>391</v>
       </c>
       <c r="H470" s="3" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="I470" s="0" t="s">
         <v>21</v>
@@ -22442,7 +22442,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22471,7 +22471,7 @@
         <v>391</v>
       </c>
       <c r="H473" s="3" t="n">
-        <v>-3</v>
+        <v>75</v>
       </c>
       <c r="I473" s="0" t="s">
         <v>21</v>
@@ -22645,7 +22645,7 @@
         <v>391</v>
       </c>
       <c r="H479" s="3" t="n">
-        <v>301</v>
+        <v>1</v>
       </c>
       <c r="I479" s="0" t="s">
         <v>21</v>
@@ -22848,7 +22848,7 @@
         <v>391</v>
       </c>
       <c r="H486" s="3" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I486" s="0" t="s">
         <v>21</v>
@@ -23196,7 +23196,7 @@
         <v>391</v>
       </c>
       <c r="H498" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I498" s="0" t="s">
         <v>21</v>
@@ -23515,7 +23515,7 @@
         <v>391</v>
       </c>
       <c r="H509" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I509" s="0" t="s">
         <v>21</v>
@@ -23544,7 +23544,7 @@
         <v>391</v>
       </c>
       <c r="H510" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I510" s="0" t="s">
         <v>21</v>
@@ -23573,7 +23573,7 @@
         <v>391</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>-2</v>
+        <v>46</v>
       </c>
       <c r="I511" s="0" t="s">
         <v>21</v>
@@ -23602,7 +23602,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -23631,7 +23631,7 @@
         <v>391</v>
       </c>
       <c r="H513" s="3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I513" s="0" t="s">
         <v>21</v>
@@ -26009,7 +26009,7 @@
         <v>391</v>
       </c>
       <c r="H595" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I595" s="0" t="s">
         <v>21</v>
@@ -26096,7 +26096,7 @@
         <v>391</v>
       </c>
       <c r="H598" s="3" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I598" s="0" t="s">
         <v>21</v>
@@ -27372,7 +27372,7 @@
         <v>391</v>
       </c>
       <c r="H642" s="3" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I642" s="0" t="s">
         <v>21</v>
@@ -28532,7 +28532,7 @@
         <v>391</v>
       </c>
       <c r="H682" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I682" s="0" t="s">
         <v>21</v>
@@ -29025,7 +29025,7 @@
         <v>850</v>
       </c>
       <c r="H699" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I699" s="0" t="s">
         <v>21</v>
@@ -29054,7 +29054,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29373,7 +29373,7 @@
         <v>391</v>
       </c>
       <c r="H711" s="3" t="n">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="I711" s="0" t="s">
         <v>21</v>
@@ -30185,7 +30185,7 @@
         <v>391</v>
       </c>
       <c r="H739" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I739" s="0" t="s">
         <v>21</v>
@@ -30620,7 +30620,7 @@
         <v>850</v>
       </c>
       <c r="H754" s="3" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="I754" s="0" t="s">
         <v>21</v>
@@ -31432,7 +31432,7 @@
         <v>391</v>
       </c>
       <c r="H782" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I782" s="0" t="s">
         <v>21</v>
@@ -31867,7 +31867,7 @@
         <v>391</v>
       </c>
       <c r="H797" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I797" s="0" t="s">
         <v>21</v>
@@ -33143,7 +33143,7 @@
         <v>391</v>
       </c>
       <c r="H841" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I841" s="0" t="s">
         <v>21</v>
@@ -35898,7 +35898,7 @@
         <v>391</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>7316</v>
+        <v>7339</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>19 October 2026</t>
+    <t>20 October 2026</t>
   </si>
   <si>
     <t>To</t>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9421,7 +9421,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -9450,7 +9450,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -11161,7 +11161,7 @@
         <v>20</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I83" s="0" t="s">
         <v>21</v>
@@ -11190,7 +11190,7 @@
         <v>20</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" s="0" t="s">
         <v>21</v>
@@ -11741,7 +11741,7 @@
         <v>20</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>21</v>
@@ -12089,7 +12089,7 @@
         <v>20</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>21</v>
@@ -12147,7 +12147,7 @@
         <v>20</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I117" s="0" t="s">
         <v>21</v>
@@ -12408,7 +12408,7 @@
         <v>20</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="I126" s="0" t="s">
         <v>21</v>
@@ -12669,7 +12669,7 @@
         <v>20</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I135" s="0" t="s">
         <v>21</v>
@@ -13017,7 +13017,7 @@
         <v>20</v>
       </c>
       <c r="H147" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I147" s="0" t="s">
         <v>21</v>
@@ -13278,7 +13278,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -13365,7 +13365,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -13800,7 +13800,7 @@
         <v>20</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I174" s="0" t="s">
         <v>21</v>
@@ -14003,7 +14003,7 @@
         <v>20</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I181" s="0" t="s">
         <v>21</v>
@@ -14409,7 +14409,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14438,7 +14438,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14467,7 +14467,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14496,7 +14496,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -17251,7 +17251,7 @@
         <v>20</v>
       </c>
       <c r="H293" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I293" s="0" t="s">
         <v>21</v>
@@ -19368,7 +19368,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19397,7 +19397,7 @@
         <v>391</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I367" s="0" t="s">
         <v>21</v>
@@ -19426,7 +19426,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19484,7 +19484,7 @@
         <v>391</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -20354,7 +20354,7 @@
         <v>20</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I400" s="0" t="s">
         <v>21</v>
@@ -20905,7 +20905,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21282,7 +21282,7 @@
         <v>391</v>
       </c>
       <c r="H432" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I432" s="0" t="s">
         <v>21</v>
@@ -21340,7 +21340,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21543,7 +21543,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21891,7 +21891,7 @@
         <v>919</v>
       </c>
       <c r="H453" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I453" s="0" t="s">
         <v>836</v>
@@ -22007,7 +22007,7 @@
         <v>20</v>
       </c>
       <c r="H457" s="3" t="n">
-        <v>-512</v>
+        <v>-514</v>
       </c>
       <c r="I457" s="0" t="s">
         <v>21</v>
@@ -22326,7 +22326,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22964,7 +22964,7 @@
         <v>391</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>-425</v>
+        <v>-428</v>
       </c>
       <c r="I490" s="0" t="s">
         <v>21</v>
@@ -25400,7 +25400,7 @@
         <v>20</v>
       </c>
       <c r="H574" s="3" t="n">
-        <v>-326</v>
+        <v>-327</v>
       </c>
       <c r="I574" s="0" t="s">
         <v>21</v>
@@ -25458,7 +25458,7 @@
         <v>20</v>
       </c>
       <c r="H576" s="3" t="n">
-        <v>-761</v>
+        <v>-765</v>
       </c>
       <c r="I576" s="0" t="s">
         <v>21</v>
@@ -25487,7 +25487,7 @@
         <v>20</v>
       </c>
       <c r="H577" s="3" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I577" s="0" t="s">
         <v>21</v>
@@ -25545,7 +25545,7 @@
         <v>20</v>
       </c>
       <c r="H579" s="3" t="n">
-        <v>-20</v>
+        <v>-17</v>
       </c>
       <c r="I579" s="0" t="s">
         <v>21</v>
@@ -26444,7 +26444,7 @@
         <v>391</v>
       </c>
       <c r="H610" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I610" s="0" t="s">
         <v>21</v>
@@ -26937,7 +26937,7 @@
         <v>20</v>
       </c>
       <c r="H627" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I627" s="0" t="s">
         <v>21</v>
@@ -26966,7 +26966,7 @@
         <v>20</v>
       </c>
       <c r="H628" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I628" s="0" t="s">
         <v>21</v>
@@ -27024,7 +27024,7 @@
         <v>835</v>
       </c>
       <c r="H630" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I630" s="0" t="s">
         <v>836</v>
@@ -30214,7 +30214,7 @@
         <v>391</v>
       </c>
       <c r="H740" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I740" s="0" t="s">
         <v>21</v>
@@ -30707,7 +30707,7 @@
         <v>391</v>
       </c>
       <c r="H757" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I757" s="0" t="s">
         <v>21</v>
@@ -32795,7 +32795,7 @@
         <v>391</v>
       </c>
       <c r="H829" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I829" s="0" t="s">
         <v>21</v>
@@ -33346,7 +33346,7 @@
         <v>20</v>
       </c>
       <c r="H848" s="3" t="n">
-        <v>-885</v>
+        <v>-888</v>
       </c>
       <c r="I848" s="0" t="s">
         <v>21</v>
@@ -34796,7 +34796,7 @@
         <v>391</v>
       </c>
       <c r="H898" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I898" s="0" t="s">
         <v>21</v>
@@ -35173,7 +35173,7 @@
         <v>20</v>
       </c>
       <c r="H911" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I911" s="0" t="s">
         <v>21</v>
@@ -36101,7 +36101,7 @@
         <v>391</v>
       </c>
       <c r="H943" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I943" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>7339</v>
+        <v>7262</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -13278,7 +13278,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -14409,7 +14409,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14438,7 +14438,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -18469,7 +18469,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18556,7 +18556,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18643,7 +18643,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -19426,7 +19426,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19600,7 +19600,7 @@
         <v>391</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -19629,7 +19629,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19658,7 +19658,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -19687,7 +19687,7 @@
         <v>391</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I377" s="0" t="s">
         <v>21</v>
@@ -20905,7 +20905,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21282,7 +21282,7 @@
         <v>391</v>
       </c>
       <c r="H432" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I432" s="0" t="s">
         <v>21</v>
@@ -21340,7 +21340,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21978,7 +21978,7 @@
         <v>391</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-6603</v>
+        <v>-6616</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22326,7 +22326,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22384,7 +22384,7 @@
         <v>391</v>
       </c>
       <c r="H470" s="3" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I470" s="0" t="s">
         <v>21</v>
@@ -22442,7 +22442,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -23573,7 +23573,7 @@
         <v>391</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I511" s="0" t="s">
         <v>21</v>
@@ -23602,7 +23602,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -23834,7 +23834,7 @@
         <v>391</v>
       </c>
       <c r="H520" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I520" s="0" t="s">
         <v>21</v>
@@ -25545,7 +25545,7 @@
         <v>20</v>
       </c>
       <c r="H579" s="3" t="n">
-        <v>-17</v>
+        <v>-19</v>
       </c>
       <c r="I579" s="0" t="s">
         <v>21</v>
@@ -27343,7 +27343,7 @@
         <v>391</v>
       </c>
       <c r="H641" s="3" t="n">
-        <v>-92</v>
+        <v>-95</v>
       </c>
       <c r="I641" s="0" t="s">
         <v>21</v>
@@ -27372,7 +27372,7 @@
         <v>391</v>
       </c>
       <c r="H642" s="3" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I642" s="0" t="s">
         <v>21</v>
@@ -28532,7 +28532,7 @@
         <v>391</v>
       </c>
       <c r="H682" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I682" s="0" t="s">
         <v>21</v>
@@ -28590,7 +28590,7 @@
         <v>391</v>
       </c>
       <c r="H684" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I684" s="0" t="s">
         <v>21</v>
@@ -28677,7 +28677,7 @@
         <v>391</v>
       </c>
       <c r="H687" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I687" s="0" t="s">
         <v>21</v>
@@ -28706,7 +28706,7 @@
         <v>391</v>
       </c>
       <c r="H688" s="3" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I688" s="0" t="s">
         <v>21</v>
@@ -28735,7 +28735,7 @@
         <v>391</v>
       </c>
       <c r="H689" s="3" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I689" s="0" t="s">
         <v>21</v>
@@ -28764,7 +28764,7 @@
         <v>391</v>
       </c>
       <c r="H690" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I690" s="0" t="s">
         <v>21</v>
@@ -28967,7 +28967,7 @@
         <v>391</v>
       </c>
       <c r="H697" s="3" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="I697" s="0" t="s">
         <v>21</v>
@@ -29373,7 +29373,7 @@
         <v>391</v>
       </c>
       <c r="H711" s="3" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="I711" s="0" t="s">
         <v>21</v>
@@ -30185,7 +30185,7 @@
         <v>391</v>
       </c>
       <c r="H739" s="3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I739" s="0" t="s">
         <v>21</v>
@@ -30968,7 +30968,7 @@
         <v>391</v>
       </c>
       <c r="H766" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I766" s="0" t="s">
         <v>21</v>
@@ -31751,7 +31751,7 @@
         <v>391</v>
       </c>
       <c r="H793" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I793" s="0" t="s">
         <v>21</v>
@@ -31838,7 +31838,7 @@
         <v>391</v>
       </c>
       <c r="H796" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I796" s="0" t="s">
         <v>21</v>
@@ -31867,7 +31867,7 @@
         <v>391</v>
       </c>
       <c r="H797" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I797" s="0" t="s">
         <v>21</v>
@@ -32650,7 +32650,7 @@
         <v>391</v>
       </c>
       <c r="H824" s="3" t="n">
-        <v>1</v>
+        <v>-19</v>
       </c>
       <c r="I824" s="0" t="s">
         <v>21</v>
@@ -32708,7 +32708,7 @@
         <v>391</v>
       </c>
       <c r="H826" s="3" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="I826" s="0" t="s">
         <v>21</v>
@@ -32737,7 +32737,7 @@
         <v>391</v>
       </c>
       <c r="H827" s="3" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="I827" s="0" t="s">
         <v>21</v>
@@ -33172,7 +33172,7 @@
         <v>391</v>
       </c>
       <c r="H842" s="3" t="n">
-        <v>-66</v>
+        <v>-67</v>
       </c>
       <c r="I842" s="0" t="s">
         <v>21</v>
@@ -34332,7 +34332,7 @@
         <v>391</v>
       </c>
       <c r="H882" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I882" s="0" t="s">
         <v>21</v>
@@ -35898,7 +35898,7 @@
         <v>391</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>7262</v>
+        <v>7079</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>20 October 2026</t>
+    <t>21 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12872,7 +12872,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>7079</v>
+        <v>7078</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9421,7 +9421,7 @@
         <v>20</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="I23" s="0" t="s">
         <v>21</v>
@@ -9450,7 +9450,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -11248,7 +11248,7 @@
         <v>20</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I86" s="0" t="s">
         <v>21</v>
@@ -11741,7 +11741,7 @@
         <v>20</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>21</v>
@@ -12408,7 +12408,7 @@
         <v>20</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="I126" s="0" t="s">
         <v>21</v>
@@ -12698,7 +12698,7 @@
         <v>20</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I136" s="0" t="s">
         <v>21</v>
@@ -12930,7 +12930,7 @@
         <v>20</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I144" s="0" t="s">
         <v>21</v>
@@ -13133,7 +13133,7 @@
         <v>20</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I151" s="0" t="s">
         <v>21</v>
@@ -13365,7 +13365,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -17251,7 +17251,7 @@
         <v>20</v>
       </c>
       <c r="H293" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I293" s="0" t="s">
         <v>21</v>
@@ -18933,7 +18933,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -20122,7 +20122,7 @@
         <v>20</v>
       </c>
       <c r="H392" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I392" s="0" t="s">
         <v>21</v>
@@ -22964,7 +22964,7 @@
         <v>391</v>
       </c>
       <c r="H490" s="3" t="n">
-        <v>-428</v>
+        <v>-430</v>
       </c>
       <c r="I490" s="0" t="s">
         <v>21</v>
@@ -25545,7 +25545,7 @@
         <v>20</v>
       </c>
       <c r="H579" s="3" t="n">
-        <v>-19</v>
+        <v>-13</v>
       </c>
       <c r="I579" s="0" t="s">
         <v>21</v>
@@ -25980,7 +25980,7 @@
         <v>391</v>
       </c>
       <c r="H594" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I594" s="0" t="s">
         <v>21</v>
@@ -31577,7 +31577,7 @@
         <v>391</v>
       </c>
       <c r="H787" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I787" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>7078</v>
+        <v>7076</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14409,7 +14409,7 @@
         <v>391</v>
       </c>
       <c r="H195" s="3" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="I195" s="0" t="s">
         <v>21</v>
@@ -14438,7 +14438,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14467,7 +14467,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14496,7 +14496,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -18469,7 +18469,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18498,7 +18498,7 @@
         <v>391</v>
       </c>
       <c r="H336" s="3" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I336" s="0" t="s">
         <v>21</v>
@@ -18556,7 +18556,7 @@
         <v>391</v>
       </c>
       <c r="H338" s="3" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I338" s="0" t="s">
         <v>21</v>
@@ -18585,7 +18585,7 @@
         <v>391</v>
       </c>
       <c r="H339" s="3" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="I339" s="0" t="s">
         <v>21</v>
@@ -18614,7 +18614,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18643,7 +18643,7 @@
         <v>391</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -19368,7 +19368,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19426,7 +19426,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19513,7 +19513,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19542,7 +19542,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19629,7 +19629,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -19658,7 +19658,7 @@
         <v>391</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -19687,7 +19687,7 @@
         <v>391</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I377" s="0" t="s">
         <v>21</v>
@@ -20847,7 +20847,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -20905,7 +20905,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21282,7 +21282,7 @@
         <v>391</v>
       </c>
       <c r="H432" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I432" s="0" t="s">
         <v>21</v>
@@ -21340,7 +21340,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21543,7 +21543,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21978,7 +21978,7 @@
         <v>391</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-6616</v>
+        <v>-6628</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22152,7 +22152,7 @@
         <v>391</v>
       </c>
       <c r="H462" s="3" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I462" s="0" t="s">
         <v>21</v>
@@ -22181,7 +22181,7 @@
         <v>391</v>
       </c>
       <c r="H463" s="3" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="I463" s="0" t="s">
         <v>21</v>
@@ -22384,7 +22384,7 @@
         <v>391</v>
       </c>
       <c r="H470" s="3" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="I470" s="0" t="s">
         <v>21</v>
@@ -22442,7 +22442,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22471,7 +22471,7 @@
         <v>391</v>
       </c>
       <c r="H473" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I473" s="0" t="s">
         <v>21</v>
@@ -23138,7 +23138,7 @@
         <v>391</v>
       </c>
       <c r="H496" s="3" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="I496" s="0" t="s">
         <v>21</v>
@@ -23515,7 +23515,7 @@
         <v>391</v>
       </c>
       <c r="H509" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I509" s="0" t="s">
         <v>21</v>
@@ -23602,7 +23602,7 @@
         <v>391</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -23950,7 +23950,7 @@
         <v>391</v>
       </c>
       <c r="H524" s="3" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="I524" s="0" t="s">
         <v>21</v>
@@ -23979,7 +23979,7 @@
         <v>391</v>
       </c>
       <c r="H525" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I525" s="0" t="s">
         <v>21</v>
@@ -25255,7 +25255,7 @@
         <v>20</v>
       </c>
       <c r="H569" s="3" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="I569" s="0" t="s">
         <v>21</v>
@@ -25922,7 +25922,7 @@
         <v>391</v>
       </c>
       <c r="H592" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I592" s="0" t="s">
         <v>21</v>
@@ -26096,7 +26096,7 @@
         <v>391</v>
       </c>
       <c r="H598" s="3" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="I598" s="0" t="s">
         <v>21</v>
@@ -27343,7 +27343,7 @@
         <v>391</v>
       </c>
       <c r="H641" s="3" t="n">
-        <v>-95</v>
+        <v>-97</v>
       </c>
       <c r="I641" s="0" t="s">
         <v>21</v>
@@ -27372,7 +27372,7 @@
         <v>391</v>
       </c>
       <c r="H642" s="3" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="I642" s="0" t="s">
         <v>21</v>
@@ -29054,7 +29054,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29837,7 +29837,7 @@
         <v>391</v>
       </c>
       <c r="H727" s="3" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="I727" s="0" t="s">
         <v>21</v>
@@ -29866,7 +29866,7 @@
         <v>391</v>
       </c>
       <c r="H728" s="3" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="I728" s="0" t="s">
         <v>21</v>
@@ -30011,7 +30011,7 @@
         <v>391</v>
       </c>
       <c r="H733" s="3" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I733" s="0" t="s">
         <v>21</v>
@@ -30185,7 +30185,7 @@
         <v>391</v>
       </c>
       <c r="H739" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I739" s="0" t="s">
         <v>21</v>
@@ -30214,7 +30214,7 @@
         <v>391</v>
       </c>
       <c r="H740" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I740" s="0" t="s">
         <v>21</v>
@@ -30243,7 +30243,7 @@
         <v>391</v>
       </c>
       <c r="H741" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I741" s="0" t="s">
         <v>21</v>
@@ -31432,7 +31432,7 @@
         <v>391</v>
       </c>
       <c r="H782" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I782" s="0" t="s">
         <v>21</v>
@@ -31751,7 +31751,7 @@
         <v>391</v>
       </c>
       <c r="H793" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I793" s="0" t="s">
         <v>21</v>
@@ -32534,7 +32534,7 @@
         <v>391</v>
       </c>
       <c r="H820" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I820" s="0" t="s">
         <v>21</v>
@@ -34361,7 +34361,7 @@
         <v>391</v>
       </c>
       <c r="H883" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I883" s="0" t="s">
         <v>21</v>
@@ -34390,7 +34390,7 @@
         <v>391</v>
       </c>
       <c r="H884" s="3" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="I884" s="0" t="s">
         <v>21</v>
@@ -34796,7 +34796,7 @@
         <v>391</v>
       </c>
       <c r="H898" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I898" s="0" t="s">
         <v>21</v>
@@ -35898,7 +35898,7 @@
         <v>391</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>7076</v>
+        <v>7192</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>21 October 2026</t>
+    <t>22 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12872,7 +12872,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -16410,7 +16410,7 @@
         <v>20</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I264" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>7192</v>
+        <v>7190</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -10088,7 +10088,7 @@
         <v>20</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="I46" s="0" t="s">
         <v>21</v>
@@ -10117,7 +10117,7 @@
         <v>20</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I47" s="0" t="s">
         <v>21</v>
@@ -10436,7 +10436,7 @@
         <v>20</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I58" s="0" t="s">
         <v>21</v>
@@ -11248,7 +11248,7 @@
         <v>20</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I86" s="0" t="s">
         <v>21</v>
@@ -12089,7 +12089,7 @@
         <v>20</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>21</v>
@@ -12408,7 +12408,7 @@
         <v>20</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="I126" s="0" t="s">
         <v>21</v>
@@ -13133,7 +13133,7 @@
         <v>20</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="I151" s="0" t="s">
         <v>21</v>
@@ -13191,7 +13191,7 @@
         <v>20</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I153" s="0" t="s">
         <v>21</v>
@@ -13278,7 +13278,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -13800,7 +13800,7 @@
         <v>20</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I174" s="0" t="s">
         <v>21</v>
@@ -14003,7 +14003,7 @@
         <v>20</v>
       </c>
       <c r="H181" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I181" s="0" t="s">
         <v>21</v>
@@ -14467,7 +14467,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14496,7 +14496,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -19368,7 +19368,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -20093,7 +20093,7 @@
         <v>20</v>
       </c>
       <c r="H391" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I391" s="0" t="s">
         <v>21</v>
@@ -20180,7 +20180,7 @@
         <v>20</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I394" s="0" t="s">
         <v>21</v>
@@ -20586,7 +20586,7 @@
         <v>20</v>
       </c>
       <c r="H408" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I408" s="0" t="s">
         <v>21</v>
@@ -20905,7 +20905,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -22326,7 +22326,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22384,7 +22384,7 @@
         <v>391</v>
       </c>
       <c r="H470" s="3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I470" s="0" t="s">
         <v>21</v>
@@ -22442,7 +22442,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -25400,7 +25400,7 @@
         <v>20</v>
       </c>
       <c r="H574" s="3" t="n">
-        <v>-327</v>
+        <v>-328</v>
       </c>
       <c r="I574" s="0" t="s">
         <v>21</v>
@@ -25458,7 +25458,7 @@
         <v>20</v>
       </c>
       <c r="H576" s="3" t="n">
-        <v>-765</v>
+        <v>-766</v>
       </c>
       <c r="I576" s="0" t="s">
         <v>21</v>
@@ -25545,7 +25545,7 @@
         <v>20</v>
       </c>
       <c r="H579" s="3" t="n">
-        <v>-13</v>
+        <v>-16</v>
       </c>
       <c r="I579" s="0" t="s">
         <v>21</v>
@@ -27372,7 +27372,7 @@
         <v>391</v>
       </c>
       <c r="H642" s="3" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I642" s="0" t="s">
         <v>21</v>
@@ -28532,7 +28532,7 @@
         <v>391</v>
       </c>
       <c r="H682" s="3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I682" s="0" t="s">
         <v>21</v>
@@ -28996,7 +28996,7 @@
         <v>20</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>-165</v>
+        <v>-170</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -30620,7 +30620,7 @@
         <v>850</v>
       </c>
       <c r="H754" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I754" s="0" t="s">
         <v>21</v>
@@ -34564,7 +34564,7 @@
         <v>20</v>
       </c>
       <c r="H890" s="3" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="I890" s="0" t="s">
         <v>836</v>
@@ -35985,7 +35985,7 @@
         <v>20</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>7190</v>
+        <v>7134</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9566,7 +9566,7 @@
         <v>20</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I28" s="0" t="s">
         <v>21</v>
@@ -11277,7 +11277,7 @@
         <v>20</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I87" s="0" t="s">
         <v>21</v>
@@ -11538,7 +11538,7 @@
         <v>20</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I96" s="0" t="s">
         <v>21</v>
@@ -11741,7 +11741,7 @@
         <v>20</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I103" s="0" t="s">
         <v>21</v>
@@ -12089,7 +12089,7 @@
         <v>20</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I115" s="0" t="s">
         <v>21</v>
@@ -12698,7 +12698,7 @@
         <v>20</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I136" s="0" t="s">
         <v>21</v>
@@ -13800,7 +13800,7 @@
         <v>20</v>
       </c>
       <c r="H174" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I174" s="0" t="s">
         <v>21</v>
@@ -18469,7 +18469,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -18614,7 +18614,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -19629,7 +19629,7 @@
         <v>391</v>
       </c>
       <c r="H375" s="3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I375" s="0" t="s">
         <v>21</v>
@@ -20180,7 +20180,7 @@
         <v>20</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I394" s="0" t="s">
         <v>21</v>
@@ -20905,7 +20905,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21340,7 +21340,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21543,7 +21543,7 @@
         <v>391</v>
       </c>
       <c r="H441" s="3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I441" s="0" t="s">
         <v>21</v>
@@ -21978,7 +21978,7 @@
         <v>391</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-6628</v>
+        <v>-6638</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22007,7 +22007,7 @@
         <v>20</v>
       </c>
       <c r="H457" s="3" t="n">
-        <v>-514</v>
+        <v>-516</v>
       </c>
       <c r="I457" s="0" t="s">
         <v>21</v>
@@ -22297,7 +22297,7 @@
         <v>391</v>
       </c>
       <c r="H467" s="3" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="I467" s="0" t="s">
         <v>21</v>
@@ -22326,7 +22326,7 @@
         <v>391</v>
       </c>
       <c r="H468" s="3" t="n">
-        <v>12</v>
+        <v>-3</v>
       </c>
       <c r="I468" s="0" t="s">
         <v>21</v>
@@ -22355,7 +22355,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22442,7 +22442,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22471,7 +22471,7 @@
         <v>391</v>
       </c>
       <c r="H473" s="3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I473" s="0" t="s">
         <v>21</v>
@@ -23573,7 +23573,7 @@
         <v>391</v>
       </c>
       <c r="H511" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I511" s="0" t="s">
         <v>21</v>
@@ -25255,7 +25255,7 @@
         <v>20</v>
       </c>
       <c r="H569" s="3" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="I569" s="0" t="s">
         <v>21</v>
@@ -25545,7 +25545,7 @@
         <v>20</v>
       </c>
       <c r="H579" s="3" t="n">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="I579" s="0" t="s">
         <v>21</v>
@@ -25806,7 +25806,7 @@
         <v>391</v>
       </c>
       <c r="H588" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I588" s="0" t="s">
         <v>21</v>
@@ -26966,7 +26966,7 @@
         <v>20</v>
       </c>
       <c r="H628" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I628" s="0" t="s">
         <v>21</v>
@@ -27372,7 +27372,7 @@
         <v>391</v>
       </c>
       <c r="H642" s="3" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I642" s="0" t="s">
         <v>21</v>
@@ -28068,7 +28068,7 @@
         <v>391</v>
       </c>
       <c r="H666" s="3" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="I666" s="0" t="s">
         <v>21</v>
@@ -29025,7 +29025,7 @@
         <v>850</v>
       </c>
       <c r="H699" s="3" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I699" s="0" t="s">
         <v>21</v>
@@ -29054,7 +29054,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29112,7 +29112,7 @@
         <v>850</v>
       </c>
       <c r="H702" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I702" s="0" t="s">
         <v>21</v>
@@ -31838,7 +31838,7 @@
         <v>391</v>
       </c>
       <c r="H796" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I796" s="0" t="s">
         <v>21</v>
@@ -31954,7 +31954,7 @@
         <v>391</v>
       </c>
       <c r="H800" s="3" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="I800" s="0" t="s">
         <v>21</v>
@@ -33346,7 +33346,7 @@
         <v>20</v>
       </c>
       <c r="H848" s="3" t="n">
-        <v>-888</v>
+        <v>-891</v>
       </c>
       <c r="I848" s="0" t="s">
         <v>21</v>
@@ -34245,7 +34245,7 @@
         <v>391</v>
       </c>
       <c r="H879" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I879" s="0" t="s">
         <v>21</v>
@@ -34274,7 +34274,7 @@
         <v>391</v>
       </c>
       <c r="H880" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I880" s="0" t="s">
         <v>21</v>
@@ -34448,7 +34448,7 @@
         <v>391</v>
       </c>
       <c r="H886" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I886" s="0" t="s">
         <v>21</v>
@@ -34796,7 +34796,7 @@
         <v>391</v>
       </c>
       <c r="H898" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I898" s="0" t="s">
         <v>21</v>
@@ -35550,7 +35550,7 @@
         <v>20</v>
       </c>
       <c r="H924" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I924" s="0" t="s">
         <v>21</v>
@@ -35898,7 +35898,7 @@
         <v>391</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -35985,7 +35985,7 @@
         <v>20</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>-41</v>
+        <v>-46</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -36217,7 +36217,7 @@
         <v>391</v>
       </c>
       <c r="H947" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I947" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>7134</v>
+        <v>7009</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>22 October 2026</t>
+    <t>23 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12872,7 +12872,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -13278,7 +13278,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -13365,7 +13365,7 @@
         <v>20</v>
       </c>
       <c r="H159" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I159" s="0" t="s">
         <v>21</v>
@@ -14438,7 +14438,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14467,7 +14467,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -15743,7 +15743,7 @@
         <v>20</v>
       </c>
       <c r="H241" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I241" s="0" t="s">
         <v>21</v>
@@ -16468,7 +16468,7 @@
         <v>20</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="I266" s="0" t="s">
         <v>21</v>
@@ -17889,7 +17889,7 @@
         <v>20</v>
       </c>
       <c r="H315" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I315" s="0" t="s">
         <v>21</v>
@@ -19542,7 +19542,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -20847,7 +20847,7 @@
         <v>391</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I417" s="0" t="s">
         <v>21</v>
@@ -22384,7 +22384,7 @@
         <v>391</v>
       </c>
       <c r="H470" s="3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I470" s="0" t="s">
         <v>21</v>
@@ -29373,7 +29373,7 @@
         <v>391</v>
       </c>
       <c r="H711" s="3" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I711" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>7009</v>
+        <v>6980</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -12408,7 +12408,7 @@
         <v>20</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="I126" s="0" t="s">
         <v>21</v>
@@ -12437,7 +12437,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -12669,7 +12669,7 @@
         <v>20</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I135" s="0" t="s">
         <v>21</v>
@@ -12785,7 +12785,7 @@
         <v>20</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I139" s="0" t="s">
         <v>21</v>
@@ -13278,7 +13278,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -14322,7 +14322,7 @@
         <v>20</v>
       </c>
       <c r="H192" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I192" s="0" t="s">
         <v>21</v>
@@ -14438,7 +14438,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -14467,7 +14467,7 @@
         <v>391</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14496,7 +14496,7 @@
         <v>391</v>
       </c>
       <c r="H198" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I198" s="0" t="s">
         <v>21</v>
@@ -14757,7 +14757,7 @@
         <v>20</v>
       </c>
       <c r="H207" s="3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I207" s="0" t="s">
         <v>21</v>
@@ -16033,7 +16033,7 @@
         <v>20</v>
       </c>
       <c r="H251" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I251" s="0" t="s">
         <v>21</v>
@@ -16787,7 +16787,7 @@
         <v>20</v>
       </c>
       <c r="H277" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I277" s="0" t="s">
         <v>21</v>
@@ -18614,7 +18614,7 @@
         <v>391</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18933,7 +18933,7 @@
         <v>20</v>
       </c>
       <c r="H351" s="3" t="n">
-        <v>-20</v>
+        <v>-23</v>
       </c>
       <c r="I351" s="0" t="s">
         <v>21</v>
@@ -19136,7 +19136,7 @@
         <v>391</v>
       </c>
       <c r="H358" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I358" s="0" t="s">
         <v>21</v>
@@ -19542,7 +19542,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -20093,7 +20093,7 @@
         <v>20</v>
       </c>
       <c r="H391" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I391" s="0" t="s">
         <v>21</v>
@@ -20325,7 +20325,7 @@
         <v>20</v>
       </c>
       <c r="H399" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I399" s="0" t="s">
         <v>21</v>
@@ -20905,7 +20905,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -22094,7 +22094,7 @@
         <v>391</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22384,7 +22384,7 @@
         <v>391</v>
       </c>
       <c r="H470" s="3" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I470" s="0" t="s">
         <v>21</v>
@@ -22442,7 +22442,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22558,7 +22558,7 @@
         <v>391</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22587,7 +22587,7 @@
         <v>391</v>
       </c>
       <c r="H477" s="3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I477" s="0" t="s">
         <v>21</v>
@@ -22616,7 +22616,7 @@
         <v>391</v>
       </c>
       <c r="H478" s="3" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="I478" s="0" t="s">
         <v>21</v>
@@ -24617,7 +24617,7 @@
         <v>20</v>
       </c>
       <c r="H547" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I547" s="0" t="s">
         <v>21</v>
@@ -25400,7 +25400,7 @@
         <v>20</v>
       </c>
       <c r="H574" s="3" t="n">
-        <v>-328</v>
+        <v>-331</v>
       </c>
       <c r="I574" s="0" t="s">
         <v>21</v>
@@ -25458,7 +25458,7 @@
         <v>20</v>
       </c>
       <c r="H576" s="3" t="n">
-        <v>-766</v>
+        <v>-767</v>
       </c>
       <c r="I576" s="0" t="s">
         <v>21</v>
@@ -25545,7 +25545,7 @@
         <v>20</v>
       </c>
       <c r="H579" s="3" t="n">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="I579" s="0" t="s">
         <v>21</v>
@@ -26937,7 +26937,7 @@
         <v>20</v>
       </c>
       <c r="H627" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I627" s="0" t="s">
         <v>21</v>
@@ -27024,7 +27024,7 @@
         <v>835</v>
       </c>
       <c r="H630" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I630" s="0" t="s">
         <v>836</v>
@@ -27372,7 +27372,7 @@
         <v>391</v>
       </c>
       <c r="H642" s="3" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I642" s="0" t="s">
         <v>21</v>
@@ -29054,7 +29054,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29112,7 +29112,7 @@
         <v>850</v>
       </c>
       <c r="H702" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I702" s="0" t="s">
         <v>21</v>
@@ -31751,7 +31751,7 @@
         <v>391</v>
       </c>
       <c r="H793" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I793" s="0" t="s">
         <v>21</v>
@@ -31780,7 +31780,7 @@
         <v>391</v>
       </c>
       <c r="H794" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I794" s="0" t="s">
         <v>21</v>
@@ -32012,7 +32012,7 @@
         <v>391</v>
       </c>
       <c r="H802" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I802" s="0" t="s">
         <v>21</v>
@@ -32563,7 +32563,7 @@
         <v>391</v>
       </c>
       <c r="H821" s="3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I821" s="0" t="s">
         <v>21</v>
@@ -32650,7 +32650,7 @@
         <v>391</v>
       </c>
       <c r="H824" s="3" t="n">
-        <v>-19</v>
+        <v>-23</v>
       </c>
       <c r="I824" s="0" t="s">
         <v>21</v>
@@ -34564,7 +34564,7 @@
         <v>20</v>
       </c>
       <c r="H890" s="3" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="I890" s="0" t="s">
         <v>836</v>
@@ -35753,7 +35753,7 @@
         <v>391</v>
       </c>
       <c r="H931" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I931" s="0" t="s">
         <v>21</v>
@@ -35985,7 +35985,7 @@
         <v>20</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>-46</v>
+        <v>-49</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>6980</v>
+        <v>6901</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -12988,7 +12988,7 @@
         <v>20</v>
       </c>
       <c r="H146" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I146" s="0" t="s">
         <v>21</v>
@@ -14438,7 +14438,7 @@
         <v>391</v>
       </c>
       <c r="H196" s="3" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="I196" s="0" t="s">
         <v>21</v>
@@ -18469,7 +18469,7 @@
         <v>391</v>
       </c>
       <c r="H335" s="3" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I335" s="0" t="s">
         <v>21</v>
@@ -19368,7 +19368,7 @@
         <v>391</v>
       </c>
       <c r="H366" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I366" s="0" t="s">
         <v>21</v>
@@ -19426,7 +19426,7 @@
         <v>391</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I368" s="0" t="s">
         <v>21</v>
@@ -19513,7 +19513,7 @@
         <v>391</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19542,7 +19542,7 @@
         <v>391</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -20383,7 +20383,7 @@
         <v>20</v>
       </c>
       <c r="H401" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I401" s="0" t="s">
         <v>21</v>
@@ -20905,7 +20905,7 @@
         <v>850</v>
       </c>
       <c r="H419" s="3" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I419" s="0" t="s">
         <v>21</v>
@@ -21340,7 +21340,7 @@
         <v>391</v>
       </c>
       <c r="H434" s="3" t="n">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="I434" s="0" t="s">
         <v>21</v>
@@ -21978,7 +21978,7 @@
         <v>391</v>
       </c>
       <c r="H456" s="3" t="n">
-        <v>-6638</v>
+        <v>-6648</v>
       </c>
       <c r="I456" s="0" t="s">
         <v>21</v>
@@ -22355,7 +22355,7 @@
         <v>391</v>
       </c>
       <c r="H469" s="3" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="I469" s="0" t="s">
         <v>21</v>
@@ -22384,7 +22384,7 @@
         <v>391</v>
       </c>
       <c r="H470" s="3" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I470" s="0" t="s">
         <v>21</v>
@@ -22442,7 +22442,7 @@
         <v>391</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22471,7 +22471,7 @@
         <v>391</v>
       </c>
       <c r="H473" s="3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I473" s="0" t="s">
         <v>21</v>
@@ -22732,7 +22732,7 @@
         <v>391</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="I482" s="0" t="s">
         <v>21</v>
@@ -22761,7 +22761,7 @@
         <v>391</v>
       </c>
       <c r="H483" s="3" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="I483" s="0" t="s">
         <v>21</v>
@@ -23979,7 +23979,7 @@
         <v>391</v>
       </c>
       <c r="H525" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I525" s="0" t="s">
         <v>21</v>
@@ -25545,7 +25545,7 @@
         <v>20</v>
       </c>
       <c r="H579" s="3" t="n">
-        <v>-22</v>
+        <v>-24</v>
       </c>
       <c r="I579" s="0" t="s">
         <v>21</v>
@@ -27021,13 +27021,13 @@
         <v>19</v>
       </c>
       <c r="G630" s="2" t="s">
-        <v>835</v>
+        <v>20</v>
       </c>
       <c r="H630" s="3" t="n">
         <v>-3</v>
       </c>
       <c r="I630" s="0" t="s">
-        <v>836</v>
+        <v>21</v>
       </c>
     </row>
     <row r="631" spans="1:9" customHeight="1">
@@ -27372,7 +27372,7 @@
         <v>391</v>
       </c>
       <c r="H642" s="3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I642" s="0" t="s">
         <v>21</v>
@@ -29025,7 +29025,7 @@
         <v>850</v>
       </c>
       <c r="H699" s="3" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I699" s="0" t="s">
         <v>21</v>
@@ -29054,7 +29054,7 @@
         <v>850</v>
       </c>
       <c r="H700" s="3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I700" s="0" t="s">
         <v>21</v>
@@ -29828,7 +29828,7 @@
         <v>150</v>
       </c>
       <c r="E727" s="3" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F727" s="2" t="s">
         <v>1209</v>
@@ -29857,7 +29857,7 @@
         <v>150</v>
       </c>
       <c r="E728" s="3" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F728" s="2" t="s">
         <v>1209</v>
@@ -30620,7 +30620,7 @@
         <v>850</v>
       </c>
       <c r="H754" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I754" s="0" t="s">
         <v>21</v>
@@ -35898,7 +35898,7 @@
         <v>391</v>
       </c>
       <c r="H936" s="3" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="I936" s="0" t="s">
         <v>21</v>
@@ -35985,7 +35985,7 @@
         <v>20</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>-49</v>
+        <v>-58</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>6901</v>
+        <v>6806</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>23 October 2026</t>
+    <t>24 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12872,7 +12872,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -37124,7 +37124,7 @@
     </row>
     <row r="979" spans="8:8" customHeight="1">
       <c r="H979" s="3" t="n">
-        <v>6806</v>
+        <v>6805</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -12774,7 +12774,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -13441,7 +13441,7 @@
         <v>20</v>
       </c>
       <c r="H161" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I161" s="0" t="s">
         <v>21</v>
@@ -14108,7 +14108,7 @@
         <v>20</v>
       </c>
       <c r="H184" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I184" s="0" t="s">
         <v>21</v>
@@ -14572,7 +14572,7 @@
         <v>399</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I200" s="0" t="s">
         <v>21</v>
@@ -18632,7 +18632,7 @@
         <v>399</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18661,7 +18661,7 @@
         <v>399</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -18719,7 +18719,7 @@
         <v>399</v>
       </c>
       <c r="H343" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I343" s="0" t="s">
         <v>21</v>
@@ -18748,7 +18748,7 @@
         <v>399</v>
       </c>
       <c r="H344" s="3" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I344" s="0" t="s">
         <v>21</v>
@@ -19473,7 +19473,7 @@
         <v>399</v>
       </c>
       <c r="H369" s="3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I369" s="0" t="s">
         <v>21</v>
@@ -19763,7 +19763,7 @@
         <v>399</v>
       </c>
       <c r="H379" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I379" s="0" t="s">
         <v>21</v>
@@ -21010,7 +21010,7 @@
         <v>856</v>
       </c>
       <c r="H422" s="3" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="I422" s="0" t="s">
         <v>21</v>
@@ -21387,7 +21387,7 @@
         <v>399</v>
       </c>
       <c r="H435" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I435" s="0" t="s">
         <v>21</v>
@@ -21648,7 +21648,7 @@
         <v>399</v>
       </c>
       <c r="H444" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I444" s="0" t="s">
         <v>21</v>
@@ -22083,7 +22083,7 @@
         <v>399</v>
       </c>
       <c r="H459" s="3" t="n">
-        <v>-6648</v>
+        <v>-6656</v>
       </c>
       <c r="I459" s="0" t="s">
         <v>21</v>
@@ -22257,7 +22257,7 @@
         <v>399</v>
       </c>
       <c r="H465" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I465" s="0" t="s">
         <v>21</v>
@@ -22431,7 +22431,7 @@
         <v>399</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>-3</v>
+        <v>-33</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22460,7 +22460,7 @@
         <v>399</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22489,7 +22489,7 @@
         <v>399</v>
       </c>
       <c r="H473" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I473" s="0" t="s">
         <v>21</v>
@@ -22547,7 +22547,7 @@
         <v>399</v>
       </c>
       <c r="H475" s="3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I475" s="0" t="s">
         <v>21</v>
@@ -23069,7 +23069,7 @@
         <v>399</v>
       </c>
       <c r="H493" s="3" t="n">
-        <v>-430</v>
+        <v>-435</v>
       </c>
       <c r="I493" s="0" t="s">
         <v>21</v>
@@ -23678,7 +23678,7 @@
         <v>399</v>
       </c>
       <c r="H514" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I514" s="0" t="s">
         <v>21</v>
@@ -23707,7 +23707,7 @@
         <v>399</v>
       </c>
       <c r="H515" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I515" s="0" t="s">
         <v>21</v>
@@ -23939,7 +23939,7 @@
         <v>399</v>
       </c>
       <c r="H523" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I523" s="0" t="s">
         <v>21</v>
@@ -24084,7 +24084,7 @@
         <v>399</v>
       </c>
       <c r="H528" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I528" s="0" t="s">
         <v>21</v>
@@ -25650,7 +25650,7 @@
         <v>20</v>
       </c>
       <c r="H582" s="3" t="n">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="I582" s="0" t="s">
         <v>21</v>
@@ -26027,7 +26027,7 @@
         <v>399</v>
       </c>
       <c r="H595" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I595" s="0" t="s">
         <v>21</v>
@@ -28550,7 +28550,7 @@
         <v>399</v>
       </c>
       <c r="H682" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I682" s="0" t="s">
         <v>21</v>
@@ -28782,7 +28782,7 @@
         <v>399</v>
       </c>
       <c r="H690" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I690" s="0" t="s">
         <v>21</v>
@@ -29014,7 +29014,7 @@
         <v>399</v>
       </c>
       <c r="H698" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I698" s="0" t="s">
         <v>21</v>
@@ -29478,7 +29478,7 @@
         <v>399</v>
       </c>
       <c r="H714" s="3" t="n">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="I714" s="0" t="s">
         <v>21</v>
@@ -30290,7 +30290,7 @@
         <v>399</v>
       </c>
       <c r="H742" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I742" s="0" t="s">
         <v>21</v>
@@ -30348,7 +30348,7 @@
         <v>399</v>
       </c>
       <c r="H744" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I744" s="0" t="s">
         <v>21</v>
@@ -30725,7 +30725,7 @@
         <v>856</v>
       </c>
       <c r="H757" s="3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I757" s="0" t="s">
         <v>21</v>
@@ -31044,7 +31044,7 @@
         <v>399</v>
       </c>
       <c r="H768" s="3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I768" s="0" t="s">
         <v>21</v>
@@ -31711,7 +31711,7 @@
         <v>399</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -31943,7 +31943,7 @@
         <v>399</v>
       </c>
       <c r="H799" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I799" s="0" t="s">
         <v>21</v>
@@ -31972,7 +31972,7 @@
         <v>399</v>
       </c>
       <c r="H800" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I800" s="0" t="s">
         <v>21</v>
@@ -35974,7 +35974,7 @@
         <v>399</v>
       </c>
       <c r="H938" s="3" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="I938" s="0" t="s">
         <v>21</v>
@@ -37200,7 +37200,7 @@
     </row>
     <row r="981" spans="8:8" customHeight="1">
       <c r="H981" s="3" t="n">
-        <v>7304</v>
+        <v>7179</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>24 October 2026</t>
+    <t>25 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12890,7 +12890,7 @@
         <v>20</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="I142" s="0" t="s">
         <v>21</v>
@@ -37200,7 +37200,7 @@
     </row>
     <row r="981" spans="8:8" customHeight="1">
       <c r="H981" s="3" t="n">
-        <v>7179</v>
+        <v>7178</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -10106,7 +10106,7 @@
         <v>20</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="I46" s="0" t="s">
         <v>21</v>
@@ -12426,7 +12426,7 @@
         <v>20</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="I126" s="0" t="s">
         <v>21</v>
@@ -37200,7 +37200,7 @@
     </row>
     <row r="981" spans="8:8" customHeight="1">
       <c r="H981" s="3" t="n">
-        <v>7178</v>
+        <v>7175</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>25 October 2026</t>
+    <t>26 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12928,7 +12928,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7174</v>
+        <v>7173</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9477,7 +9477,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -9506,7 +9506,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>21</v>
@@ -12464,7 +12464,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -12928,7 +12928,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13160,7 +13160,7 @@
         <v>20</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I151" s="0" t="s">
         <v>21</v>
@@ -13537,7 +13537,7 @@
         <v>20</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I164" s="0" t="s">
         <v>21</v>
@@ -13885,7 +13885,7 @@
         <v>20</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I176" s="0" t="s">
         <v>21</v>
@@ -14088,7 +14088,7 @@
         <v>20</v>
       </c>
       <c r="H183" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I183" s="0" t="s">
         <v>21</v>
@@ -14639,7 +14639,7 @@
         <v>401</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I202" s="0" t="s">
         <v>21</v>
@@ -15248,7 +15248,7 @@
         <v>20</v>
       </c>
       <c r="H223" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I223" s="0" t="s">
         <v>21</v>
@@ -17046,7 +17046,7 @@
         <v>20</v>
       </c>
       <c r="H285" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I285" s="0" t="s">
         <v>21</v>
@@ -17858,7 +17858,7 @@
         <v>20</v>
       </c>
       <c r="H313" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I313" s="0" t="s">
         <v>21</v>
@@ -19511,7 +19511,7 @@
         <v>401</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19540,7 +19540,7 @@
         <v>401</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -20294,7 +20294,7 @@
         <v>20</v>
       </c>
       <c r="H397" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I397" s="0" t="s">
         <v>21</v>
@@ -20323,7 +20323,7 @@
         <v>20</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I398" s="0" t="s">
         <v>21</v>
@@ -20468,7 +20468,7 @@
         <v>20</v>
       </c>
       <c r="H403" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I403" s="0" t="s">
         <v>21</v>
@@ -20497,7 +20497,7 @@
         <v>20</v>
       </c>
       <c r="H404" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I404" s="0" t="s">
         <v>21</v>
@@ -20990,7 +20990,7 @@
         <v>401</v>
       </c>
       <c r="H421" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I421" s="0" t="s">
         <v>21</v>
@@ -21048,7 +21048,7 @@
         <v>858</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I423" s="0" t="s">
         <v>21</v>
@@ -22150,7 +22150,7 @@
         <v>20</v>
       </c>
       <c r="H461" s="3" t="n">
-        <v>-516</v>
+        <v>-518</v>
       </c>
       <c r="I461" s="0" t="s">
         <v>21</v>
@@ -22440,7 +22440,7 @@
         <v>401</v>
       </c>
       <c r="H471" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="I471" s="0" t="s">
         <v>21</v>
@@ -22469,7 +22469,7 @@
         <v>401</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>-33</v>
+        <v>167</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22527,7 +22527,7 @@
         <v>401</v>
       </c>
       <c r="H474" s="3" t="n">
-        <v>11</v>
+        <v>211</v>
       </c>
       <c r="I474" s="0" t="s">
         <v>21</v>
@@ -23339,7 +23339,7 @@
         <v>401</v>
       </c>
       <c r="H502" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I502" s="0" t="s">
         <v>21</v>
@@ -25688,7 +25688,7 @@
         <v>20</v>
       </c>
       <c r="H583" s="3" t="n">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="I583" s="0" t="s">
         <v>21</v>
@@ -25949,7 +25949,7 @@
         <v>401</v>
       </c>
       <c r="H592" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I592" s="0" t="s">
         <v>21</v>
@@ -26587,7 +26587,7 @@
         <v>401</v>
       </c>
       <c r="H614" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I614" s="0" t="s">
         <v>21</v>
@@ -29516,7 +29516,7 @@
         <v>401</v>
       </c>
       <c r="H715" s="3" t="n">
-        <v>327</v>
+        <v>627</v>
       </c>
       <c r="I715" s="0" t="s">
         <v>21</v>
@@ -31807,7 +31807,7 @@
         <v>401</v>
       </c>
       <c r="H794" s="3" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="I794" s="0" t="s">
         <v>21</v>
@@ -32126,7 +32126,7 @@
         <v>401</v>
       </c>
       <c r="H805" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I805" s="0" t="s">
         <v>21</v>
@@ -33489,7 +33489,7 @@
         <v>20</v>
       </c>
       <c r="H852" s="3" t="n">
-        <v>-891</v>
+        <v>-895</v>
       </c>
       <c r="I852" s="0" t="s">
         <v>21</v>
@@ -34533,7 +34533,7 @@
         <v>401</v>
       </c>
       <c r="H888" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I888" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7173</v>
+        <v>8050</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14581,7 +14581,7 @@
         <v>401</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I200" s="0" t="s">
         <v>21</v>
@@ -14610,7 +14610,7 @@
         <v>401</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I201" s="0" t="s">
         <v>21</v>
@@ -14639,7 +14639,7 @@
         <v>401</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I202" s="0" t="s">
         <v>21</v>
@@ -14668,7 +14668,7 @@
         <v>401</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I203" s="0" t="s">
         <v>21</v>
@@ -14697,7 +14697,7 @@
         <v>401</v>
       </c>
       <c r="H204" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I204" s="0" t="s">
         <v>21</v>
@@ -18641,7 +18641,7 @@
         <v>401</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18670,7 +18670,7 @@
         <v>401</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -18699,7 +18699,7 @@
         <v>401</v>
       </c>
       <c r="H342" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I342" s="0" t="s">
         <v>21</v>
@@ -18728,7 +18728,7 @@
         <v>401</v>
       </c>
       <c r="H343" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I343" s="0" t="s">
         <v>21</v>
@@ -18757,7 +18757,7 @@
         <v>401</v>
       </c>
       <c r="H344" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I344" s="0" t="s">
         <v>21</v>
@@ -18786,7 +18786,7 @@
         <v>401</v>
       </c>
       <c r="H345" s="3" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I345" s="0" t="s">
         <v>21</v>
@@ -19511,7 +19511,7 @@
         <v>401</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19540,7 +19540,7 @@
         <v>401</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19569,7 +19569,7 @@
         <v>401</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19627,7 +19627,7 @@
         <v>401</v>
       </c>
       <c r="H374" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I374" s="0" t="s">
         <v>21</v>
@@ -19772,7 +19772,7 @@
         <v>401</v>
       </c>
       <c r="H379" s="3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I379" s="0" t="s">
         <v>21</v>
@@ -19801,7 +19801,7 @@
         <v>401</v>
       </c>
       <c r="H380" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I380" s="0" t="s">
         <v>21</v>
@@ -19830,7 +19830,7 @@
         <v>401</v>
       </c>
       <c r="H381" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I381" s="0" t="s">
         <v>21</v>
@@ -21048,7 +21048,7 @@
         <v>858</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="I423" s="0" t="s">
         <v>21</v>
@@ -21425,7 +21425,7 @@
         <v>401</v>
       </c>
       <c r="H436" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I436" s="0" t="s">
         <v>21</v>
@@ -21483,7 +21483,7 @@
         <v>401</v>
       </c>
       <c r="H438" s="3" t="n">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="I438" s="0" t="s">
         <v>21</v>
@@ -21686,7 +21686,7 @@
         <v>401</v>
       </c>
       <c r="H445" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I445" s="0" t="s">
         <v>21</v>
@@ -22121,7 +22121,7 @@
         <v>401</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>-6656</v>
+        <v>-6678</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22469,7 +22469,7 @@
         <v>401</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22498,7 +22498,7 @@
         <v>401</v>
       </c>
       <c r="H473" s="3" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I473" s="0" t="s">
         <v>21</v>
@@ -22527,7 +22527,7 @@
         <v>401</v>
       </c>
       <c r="H474" s="3" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I474" s="0" t="s">
         <v>21</v>
@@ -22585,7 +22585,7 @@
         <v>401</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22875,7 +22875,7 @@
         <v>401</v>
       </c>
       <c r="H486" s="3" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="I486" s="0" t="s">
         <v>21</v>
@@ -23774,7 +23774,7 @@
         <v>401</v>
       </c>
       <c r="H517" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I517" s="0" t="s">
         <v>21</v>
@@ -23977,7 +23977,7 @@
         <v>401</v>
       </c>
       <c r="H524" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I524" s="0" t="s">
         <v>21</v>
@@ -26065,7 +26065,7 @@
         <v>401</v>
       </c>
       <c r="H596" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I596" s="0" t="s">
         <v>21</v>
@@ -27515,7 +27515,7 @@
         <v>401</v>
       </c>
       <c r="H646" s="3" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="I646" s="0" t="s">
         <v>21</v>
@@ -29168,7 +29168,7 @@
         <v>858</v>
       </c>
       <c r="H703" s="3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I703" s="0" t="s">
         <v>21</v>
@@ -29197,7 +29197,7 @@
         <v>858</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -29255,7 +29255,7 @@
         <v>858</v>
       </c>
       <c r="H706" s="3" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="I706" s="0" t="s">
         <v>21</v>
@@ -29516,7 +29516,7 @@
         <v>401</v>
       </c>
       <c r="H715" s="3" t="n">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="I715" s="0" t="s">
         <v>21</v>
@@ -30357,7 +30357,7 @@
         <v>401</v>
       </c>
       <c r="H744" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I744" s="0" t="s">
         <v>21</v>
@@ -30763,7 +30763,7 @@
         <v>858</v>
       </c>
       <c r="H758" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I758" s="0" t="s">
         <v>21</v>
@@ -30850,7 +30850,7 @@
         <v>401</v>
       </c>
       <c r="H761" s="3" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I761" s="0" t="s">
         <v>21</v>
@@ -31981,7 +31981,7 @@
         <v>401</v>
       </c>
       <c r="H800" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I800" s="0" t="s">
         <v>21</v>
@@ -32010,7 +32010,7 @@
         <v>401</v>
       </c>
       <c r="H801" s="3" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="I801" s="0" t="s">
         <v>21</v>
@@ -32097,7 +32097,7 @@
         <v>401</v>
       </c>
       <c r="H804" s="3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I804" s="0" t="s">
         <v>21</v>
@@ -34417,7 +34417,7 @@
         <v>401</v>
       </c>
       <c r="H884" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I884" s="0" t="s">
         <v>21</v>
@@ -36012,7 +36012,7 @@
         <v>401</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -36331,7 +36331,7 @@
         <v>401</v>
       </c>
       <c r="H950" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I950" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>8050</v>
+        <v>7892</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>26 October 2026</t>
+    <t>27 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12928,7 +12928,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -21048,7 +21048,7 @@
         <v>858</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I423" s="0" t="s">
         <v>21</v>
@@ -29197,7 +29197,7 @@
         <v>858</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7892</v>
+        <v>7889</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -10637,7 +10637,7 @@
         <v>20</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I64" s="0" t="s">
         <v>21</v>
@@ -11797,7 +11797,7 @@
         <v>20</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I104" s="0" t="s">
         <v>21</v>
@@ -12464,7 +12464,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>-20</v>
+        <v>-22</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -12812,7 +12812,7 @@
         <v>20</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I139" s="0" t="s">
         <v>21</v>
@@ -12957,7 +12957,7 @@
         <v>20</v>
       </c>
       <c r="H144" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I144" s="0" t="s">
         <v>21</v>
@@ -13102,7 +13102,7 @@
         <v>20</v>
       </c>
       <c r="H149" s="3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I149" s="0" t="s">
         <v>21</v>
@@ -13189,7 +13189,7 @@
         <v>20</v>
       </c>
       <c r="H152" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I152" s="0" t="s">
         <v>21</v>
@@ -13247,7 +13247,7 @@
         <v>20</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I154" s="0" t="s">
         <v>21</v>
@@ -13305,7 +13305,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -13334,7 +13334,7 @@
         <v>20</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I157" s="0" t="s">
         <v>21</v>
@@ -13856,7 +13856,7 @@
         <v>20</v>
       </c>
       <c r="H175" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I175" s="0" t="s">
         <v>21</v>
@@ -13885,7 +13885,7 @@
         <v>20</v>
       </c>
       <c r="H176" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I176" s="0" t="s">
         <v>21</v>
@@ -14146,7 +14146,7 @@
         <v>20</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I185" s="0" t="s">
         <v>21</v>
@@ -14494,7 +14494,7 @@
         <v>20</v>
       </c>
       <c r="H197" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I197" s="0" t="s">
         <v>21</v>
@@ -14581,7 +14581,7 @@
         <v>401</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I200" s="0" t="s">
         <v>21</v>
@@ -14610,7 +14610,7 @@
         <v>401</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I201" s="0" t="s">
         <v>21</v>
@@ -14639,7 +14639,7 @@
         <v>401</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I202" s="0" t="s">
         <v>21</v>
@@ -14668,7 +14668,7 @@
         <v>401</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I203" s="0" t="s">
         <v>21</v>
@@ -16930,7 +16930,7 @@
         <v>20</v>
       </c>
       <c r="H281" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I281" s="0" t="s">
         <v>21</v>
@@ -17423,7 +17423,7 @@
         <v>20</v>
       </c>
       <c r="H298" s="3" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="I298" s="0" t="s">
         <v>21</v>
@@ -17452,7 +17452,7 @@
         <v>20</v>
       </c>
       <c r="H299" s="3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I299" s="0" t="s">
         <v>21</v>
@@ -18322,7 +18322,7 @@
         <v>20</v>
       </c>
       <c r="H329" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I329" s="0" t="s">
         <v>21</v>
@@ -18641,7 +18641,7 @@
         <v>401</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18670,7 +18670,7 @@
         <v>401</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -18728,7 +18728,7 @@
         <v>401</v>
       </c>
       <c r="H343" s="3" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I343" s="0" t="s">
         <v>21</v>
@@ -18757,7 +18757,7 @@
         <v>401</v>
       </c>
       <c r="H344" s="3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I344" s="0" t="s">
         <v>21</v>
@@ -18786,7 +18786,7 @@
         <v>401</v>
       </c>
       <c r="H345" s="3" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I345" s="0" t="s">
         <v>21</v>
@@ -19511,7 +19511,7 @@
         <v>401</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19540,7 +19540,7 @@
         <v>401</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I371" s="0" t="s">
         <v>21</v>
@@ -19569,7 +19569,7 @@
         <v>401</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19772,7 +19772,7 @@
         <v>401</v>
       </c>
       <c r="H379" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I379" s="0" t="s">
         <v>21</v>
@@ -19801,7 +19801,7 @@
         <v>401</v>
       </c>
       <c r="H380" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I380" s="0" t="s">
         <v>21</v>
@@ -20294,7 +20294,7 @@
         <v>20</v>
       </c>
       <c r="H397" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I397" s="0" t="s">
         <v>21</v>
@@ -20323,7 +20323,7 @@
         <v>20</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I398" s="0" t="s">
         <v>21</v>
@@ -20671,7 +20671,7 @@
         <v>20</v>
       </c>
       <c r="H410" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I410" s="0" t="s">
         <v>21</v>
@@ -20729,7 +20729,7 @@
         <v>20</v>
       </c>
       <c r="H412" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I412" s="0" t="s">
         <v>21</v>
@@ -20903,7 +20903,7 @@
         <v>20</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>-302</v>
+        <v>-304</v>
       </c>
       <c r="I418" s="0" t="s">
         <v>21</v>
@@ -21048,7 +21048,7 @@
         <v>858</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I423" s="0" t="s">
         <v>21</v>
@@ -22121,7 +22121,7 @@
         <v>401</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>-6678</v>
+        <v>-6684.6</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22150,7 +22150,7 @@
         <v>20</v>
       </c>
       <c r="H461" s="3" t="n">
-        <v>-518</v>
+        <v>-520</v>
       </c>
       <c r="I461" s="0" t="s">
         <v>21</v>
@@ -22469,7 +22469,7 @@
         <v>401</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22585,7 +22585,7 @@
         <v>401</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22614,7 +22614,7 @@
         <v>401</v>
       </c>
       <c r="H477" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I477" s="0" t="s">
         <v>21</v>
@@ -23339,7 +23339,7 @@
         <v>401</v>
       </c>
       <c r="H502" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I502" s="0" t="s">
         <v>21</v>
@@ -23716,7 +23716,7 @@
         <v>401</v>
       </c>
       <c r="H515" s="3" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I515" s="0" t="s">
         <v>21</v>
@@ -23745,7 +23745,7 @@
         <v>401</v>
       </c>
       <c r="H516" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I516" s="0" t="s">
         <v>21</v>
@@ -23977,7 +23977,7 @@
         <v>401</v>
       </c>
       <c r="H524" s="3" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="I524" s="0" t="s">
         <v>21</v>
@@ -24064,7 +24064,7 @@
         <v>401</v>
       </c>
       <c r="H527" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I527" s="0" t="s">
         <v>21</v>
@@ -24760,7 +24760,7 @@
         <v>20</v>
       </c>
       <c r="H551" s="3" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="I551" s="0" t="s">
         <v>21</v>
@@ -25543,7 +25543,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-334</v>
+        <v>-335</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -25601,7 +25601,7 @@
         <v>20</v>
       </c>
       <c r="H580" s="3" t="n">
-        <v>-769</v>
+        <v>-770</v>
       </c>
       <c r="I580" s="0" t="s">
         <v>21</v>
@@ -25688,7 +25688,7 @@
         <v>20</v>
       </c>
       <c r="H583" s="3" t="n">
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="I583" s="0" t="s">
         <v>21</v>
@@ -26065,7 +26065,7 @@
         <v>401</v>
       </c>
       <c r="H596" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I596" s="0" t="s">
         <v>21</v>
@@ -26587,7 +26587,7 @@
         <v>401</v>
       </c>
       <c r="H614" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I614" s="0" t="s">
         <v>21</v>
@@ -27167,7 +27167,7 @@
         <v>20</v>
       </c>
       <c r="H634" s="3" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="I634" s="0" t="s">
         <v>21</v>
@@ -27486,7 +27486,7 @@
         <v>401</v>
       </c>
       <c r="H645" s="3" t="n">
-        <v>-97</v>
+        <v>-98</v>
       </c>
       <c r="I645" s="0" t="s">
         <v>21</v>
@@ -27515,7 +27515,7 @@
         <v>401</v>
       </c>
       <c r="H646" s="3" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I646" s="0" t="s">
         <v>21</v>
@@ -29197,7 +29197,7 @@
         <v>858</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -29255,7 +29255,7 @@
         <v>858</v>
       </c>
       <c r="H706" s="3" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="I706" s="0" t="s">
         <v>21</v>
@@ -29516,7 +29516,7 @@
         <v>401</v>
       </c>
       <c r="H715" s="3" t="n">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="I715" s="0" t="s">
         <v>21</v>
@@ -30154,7 +30154,7 @@
         <v>401</v>
       </c>
       <c r="H737" s="3" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="I737" s="0" t="s">
         <v>21</v>
@@ -30328,7 +30328,7 @@
         <v>401</v>
       </c>
       <c r="H743" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I743" s="0" t="s">
         <v>21</v>
@@ -30357,7 +30357,7 @@
         <v>401</v>
       </c>
       <c r="H744" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I744" s="0" t="s">
         <v>21</v>
@@ -30386,7 +30386,7 @@
         <v>401</v>
       </c>
       <c r="H745" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I745" s="0" t="s">
         <v>21</v>
@@ -30763,7 +30763,7 @@
         <v>858</v>
       </c>
       <c r="H758" s="3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I758" s="0" t="s">
         <v>21</v>
@@ -31053,7 +31053,7 @@
         <v>401</v>
       </c>
       <c r="H768" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I768" s="0" t="s">
         <v>21</v>
@@ -31691,7 +31691,7 @@
         <v>401</v>
       </c>
       <c r="H790" s="3" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I790" s="0" t="s">
         <v>21</v>
@@ -31807,7 +31807,7 @@
         <v>401</v>
       </c>
       <c r="H794" s="3" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="I794" s="0" t="s">
         <v>21</v>
@@ -31894,7 +31894,7 @@
         <v>401</v>
       </c>
       <c r="H797" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I797" s="0" t="s">
         <v>21</v>
@@ -33489,7 +33489,7 @@
         <v>20</v>
       </c>
       <c r="H852" s="3" t="n">
-        <v>-895</v>
+        <v>-898</v>
       </c>
       <c r="I852" s="0" t="s">
         <v>21</v>
@@ -34707,7 +34707,7 @@
         <v>20</v>
       </c>
       <c r="H894" s="3" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="I894" s="0" t="s">
         <v>844</v>
@@ -34939,7 +34939,7 @@
         <v>401</v>
       </c>
       <c r="H902" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I902" s="0" t="s">
         <v>21</v>
@@ -36012,7 +36012,7 @@
         <v>401</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -36215,7 +36215,7 @@
         <v>401</v>
       </c>
       <c r="H946" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I946" s="0" t="s">
         <v>21</v>
@@ -36331,7 +36331,7 @@
         <v>401</v>
       </c>
       <c r="H950" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I950" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7889</v>
+        <v>7718.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>27 October 2026</t>
+    <t>28 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -25688,7 +25688,7 @@
         <v>20</v>
       </c>
       <c r="H583" s="3" t="n">
-        <v>-26</v>
+        <v>-28</v>
       </c>
       <c r="I583" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7718.4</v>
+        <v>7716.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9216,7 +9216,7 @@
         <v>20</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="0" t="s">
         <v>21</v>
@@ -9332,7 +9332,7 @@
         <v>20</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I19" s="0" t="s">
         <v>21</v>
@@ -9477,7 +9477,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-14</v>
+        <v>-19</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -9506,7 +9506,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>21</v>
@@ -9535,7 +9535,7 @@
         <v>20</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I26" s="0" t="s">
         <v>21</v>
@@ -9738,7 +9738,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I33" s="0" t="s">
         <v>21</v>
@@ -11217,7 +11217,7 @@
         <v>20</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I84" s="0" t="s">
         <v>21</v>
@@ -11797,7 +11797,7 @@
         <v>20</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="I104" s="0" t="s">
         <v>21</v>
@@ -12203,7 +12203,7 @@
         <v>20</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I118" s="0" t="s">
         <v>21</v>
@@ -12464,7 +12464,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>-22</v>
+        <v>-24</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -13305,7 +13305,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -13479,7 +13479,7 @@
         <v>20</v>
       </c>
       <c r="H162" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I162" s="0" t="s">
         <v>21</v>
@@ -13537,7 +13537,7 @@
         <v>20</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="I164" s="0" t="s">
         <v>21</v>
@@ -14146,7 +14146,7 @@
         <v>20</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I185" s="0" t="s">
         <v>21</v>
@@ -17452,7 +17452,7 @@
         <v>20</v>
       </c>
       <c r="H299" s="3" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I299" s="0" t="s">
         <v>21</v>
@@ -17974,7 +17974,7 @@
         <v>20</v>
       </c>
       <c r="H317" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I317" s="0" t="s">
         <v>21</v>
@@ -20323,7 +20323,7 @@
         <v>20</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I398" s="0" t="s">
         <v>21</v>
@@ -20439,7 +20439,7 @@
         <v>20</v>
       </c>
       <c r="H402" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I402" s="0" t="s">
         <v>21</v>
@@ -20526,7 +20526,7 @@
         <v>20</v>
       </c>
       <c r="H405" s="3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I405" s="0" t="s">
         <v>21</v>
@@ -21048,7 +21048,7 @@
         <v>858</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I423" s="0" t="s">
         <v>21</v>
@@ -21802,7 +21802,7 @@
         <v>20</v>
       </c>
       <c r="H449" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I449" s="0" t="s">
         <v>21</v>
@@ -22150,7 +22150,7 @@
         <v>20</v>
       </c>
       <c r="H461" s="3" t="n">
-        <v>-520</v>
+        <v>-522</v>
       </c>
       <c r="I461" s="0" t="s">
         <v>21</v>
@@ -25601,7 +25601,7 @@
         <v>20</v>
       </c>
       <c r="H580" s="3" t="n">
-        <v>-770</v>
+        <v>-771</v>
       </c>
       <c r="I580" s="0" t="s">
         <v>21</v>
@@ -25688,7 +25688,7 @@
         <v>20</v>
       </c>
       <c r="H583" s="3" t="n">
-        <v>-28</v>
+        <v>-32</v>
       </c>
       <c r="I583" s="0" t="s">
         <v>21</v>
@@ -29197,7 +29197,7 @@
         <v>858</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -29255,7 +29255,7 @@
         <v>858</v>
       </c>
       <c r="H706" s="3" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="I706" s="0" t="s">
         <v>21</v>
@@ -30763,7 +30763,7 @@
         <v>858</v>
       </c>
       <c r="H758" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I758" s="0" t="s">
         <v>21</v>
@@ -33489,7 +33489,7 @@
         <v>20</v>
       </c>
       <c r="H852" s="3" t="n">
-        <v>-898</v>
+        <v>-902</v>
       </c>
       <c r="I852" s="0" t="s">
         <v>21</v>
@@ -34707,7 +34707,7 @@
         <v>20</v>
       </c>
       <c r="H894" s="3" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="I894" s="0" t="s">
         <v>844</v>
@@ -36012,7 +36012,7 @@
         <v>401</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7716.4</v>
+        <v>7663.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14610,7 +14610,7 @@
         <v>401</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I201" s="0" t="s">
         <v>21</v>
@@ -18670,7 +18670,7 @@
         <v>401</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -18786,7 +18786,7 @@
         <v>401</v>
       </c>
       <c r="H345" s="3" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I345" s="0" t="s">
         <v>21</v>
@@ -19511,7 +19511,7 @@
         <v>401</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19569,7 +19569,7 @@
         <v>401</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19801,7 +19801,7 @@
         <v>401</v>
       </c>
       <c r="H380" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I380" s="0" t="s">
         <v>21</v>
@@ -19830,7 +19830,7 @@
         <v>401</v>
       </c>
       <c r="H381" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I381" s="0" t="s">
         <v>21</v>
@@ -20990,7 +20990,7 @@
         <v>401</v>
       </c>
       <c r="H421" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I421" s="0" t="s">
         <v>21</v>
@@ -21048,7 +21048,7 @@
         <v>858</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I423" s="0" t="s">
         <v>21</v>
@@ -21483,7 +21483,7 @@
         <v>401</v>
       </c>
       <c r="H438" s="3" t="n">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="I438" s="0" t="s">
         <v>21</v>
@@ -21686,7 +21686,7 @@
         <v>401</v>
       </c>
       <c r="H445" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I445" s="0" t="s">
         <v>21</v>
@@ -22121,7 +22121,7 @@
         <v>401</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>-6684.6</v>
+        <v>-6697.6</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22237,7 +22237,7 @@
         <v>401</v>
       </c>
       <c r="H464" s="3" t="n">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="I464" s="0" t="s">
         <v>21</v>
@@ -22295,7 +22295,7 @@
         <v>401</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22469,7 +22469,7 @@
         <v>401</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22527,7 +22527,7 @@
         <v>401</v>
       </c>
       <c r="H474" s="3" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="I474" s="0" t="s">
         <v>21</v>
@@ -22585,7 +22585,7 @@
         <v>401</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22730,7 +22730,7 @@
         <v>401</v>
       </c>
       <c r="H481" s="3" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I481" s="0" t="s">
         <v>21</v>
@@ -22759,7 +22759,7 @@
         <v>401</v>
       </c>
       <c r="H482" s="3" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="I482" s="0" t="s">
         <v>21</v>
@@ -22788,7 +22788,7 @@
         <v>401</v>
       </c>
       <c r="H483" s="3" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="I483" s="0" t="s">
         <v>21</v>
@@ -22904,7 +22904,7 @@
         <v>401</v>
       </c>
       <c r="H487" s="3" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I487" s="0" t="s">
         <v>21</v>
@@ -23716,7 +23716,7 @@
         <v>401</v>
       </c>
       <c r="H515" s="3" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I515" s="0" t="s">
         <v>21</v>
@@ -23745,7 +23745,7 @@
         <v>401</v>
       </c>
       <c r="H516" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I516" s="0" t="s">
         <v>21</v>
@@ -27486,7 +27486,7 @@
         <v>401</v>
       </c>
       <c r="H645" s="3" t="n">
-        <v>-98</v>
+        <v>-101</v>
       </c>
       <c r="I645" s="0" t="s">
         <v>21</v>
@@ -27515,7 +27515,7 @@
         <v>401</v>
       </c>
       <c r="H646" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I646" s="0" t="s">
         <v>21</v>
@@ -28095,7 +28095,7 @@
         <v>401</v>
       </c>
       <c r="H666" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I666" s="0" t="s">
         <v>21</v>
@@ -28211,7 +28211,7 @@
         <v>401</v>
       </c>
       <c r="H670" s="3" t="n">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="I670" s="0" t="s">
         <v>21</v>
@@ -28820,7 +28820,7 @@
         <v>401</v>
       </c>
       <c r="H691" s="3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I691" s="0" t="s">
         <v>21</v>
@@ -29110,7 +29110,7 @@
         <v>401</v>
       </c>
       <c r="H701" s="3" t="n">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="I701" s="0" t="s">
         <v>21</v>
@@ -29168,7 +29168,7 @@
         <v>858</v>
       </c>
       <c r="H703" s="3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I703" s="0" t="s">
         <v>21</v>
@@ -29516,7 +29516,7 @@
         <v>401</v>
       </c>
       <c r="H715" s="3" t="n">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="I715" s="0" t="s">
         <v>21</v>
@@ -30328,7 +30328,7 @@
         <v>401</v>
       </c>
       <c r="H743" s="3" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="I743" s="0" t="s">
         <v>21</v>
@@ -30763,7 +30763,7 @@
         <v>858</v>
       </c>
       <c r="H758" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I758" s="0" t="s">
         <v>21</v>
@@ -31981,7 +31981,7 @@
         <v>401</v>
       </c>
       <c r="H800" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I800" s="0" t="s">
         <v>21</v>
@@ -32010,7 +32010,7 @@
         <v>401</v>
       </c>
       <c r="H801" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I801" s="0" t="s">
         <v>21</v>
@@ -35867,7 +35867,7 @@
         <v>401</v>
       </c>
       <c r="H934" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I934" s="0" t="s">
         <v>21</v>
@@ -36012,7 +36012,7 @@
         <v>401</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7663.4</v>
+        <v>7551.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>28 October 2026</t>
+    <t>29 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -9941,7 +9941,7 @@
         <v>20</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I40" s="0" t="s">
         <v>21</v>
@@ -12928,7 +12928,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13305,7 +13305,7 @@
         <v>20</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I156" s="0" t="s">
         <v>21</v>
@@ -13566,7 +13566,7 @@
         <v>20</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I165" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7551.4</v>
+        <v>7546.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -10144,7 +10144,7 @@
         <v>20</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="I47" s="0" t="s">
         <v>21</v>
@@ -12464,7 +12464,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -12812,7 +12812,7 @@
         <v>20</v>
       </c>
       <c r="H139" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I139" s="0" t="s">
         <v>21</v>
@@ -12928,7 +12928,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -13218,7 +13218,7 @@
         <v>20</v>
       </c>
       <c r="H153" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I153" s="0" t="s">
         <v>21</v>
@@ -13247,7 +13247,7 @@
         <v>20</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I154" s="0" t="s">
         <v>21</v>
@@ -13537,7 +13537,7 @@
         <v>20</v>
       </c>
       <c r="H164" s="3" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="I164" s="0" t="s">
         <v>21</v>
@@ -13566,7 +13566,7 @@
         <v>20</v>
       </c>
       <c r="H165" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I165" s="0" t="s">
         <v>21</v>
@@ -14146,7 +14146,7 @@
         <v>20</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I185" s="0" t="s">
         <v>21</v>
@@ -14668,7 +14668,7 @@
         <v>401</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I203" s="0" t="s">
         <v>21</v>
@@ -15886,7 +15886,7 @@
         <v>20</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I245" s="0" t="s">
         <v>21</v>
@@ -17452,7 +17452,7 @@
         <v>20</v>
       </c>
       <c r="H299" s="3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I299" s="0" t="s">
         <v>21</v>
@@ -17974,7 +17974,7 @@
         <v>20</v>
       </c>
       <c r="H317" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I317" s="0" t="s">
         <v>21</v>
@@ -19569,7 +19569,7 @@
         <v>401</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19801,7 +19801,7 @@
         <v>401</v>
       </c>
       <c r="H380" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I380" s="0" t="s">
         <v>21</v>
@@ -20294,7 +20294,7 @@
         <v>20</v>
       </c>
       <c r="H397" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I397" s="0" t="s">
         <v>21</v>
@@ -20323,7 +20323,7 @@
         <v>20</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I398" s="0" t="s">
         <v>21</v>
@@ -20526,7 +20526,7 @@
         <v>20</v>
       </c>
       <c r="H405" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I405" s="0" t="s">
         <v>21</v>
@@ -20613,7 +20613,7 @@
         <v>20</v>
       </c>
       <c r="H408" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I408" s="0" t="s">
         <v>21</v>
@@ -20903,7 +20903,7 @@
         <v>20</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>-304</v>
+        <v>-306</v>
       </c>
       <c r="I418" s="0" t="s">
         <v>21</v>
@@ -21048,7 +21048,7 @@
         <v>858</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I423" s="0" t="s">
         <v>21</v>
@@ -22150,7 +22150,7 @@
         <v>20</v>
       </c>
       <c r="H461" s="3" t="n">
-        <v>-522</v>
+        <v>-524</v>
       </c>
       <c r="I461" s="0" t="s">
         <v>21</v>
@@ -22266,7 +22266,7 @@
         <v>401</v>
       </c>
       <c r="H465" s="3" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I465" s="0" t="s">
         <v>21</v>
@@ -23977,7 +23977,7 @@
         <v>401</v>
       </c>
       <c r="H524" s="3" t="n">
-        <v>-3</v>
+        <v>27</v>
       </c>
       <c r="I524" s="0" t="s">
         <v>21</v>
@@ -25543,7 +25543,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-335</v>
+        <v>-336</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -25688,7 +25688,7 @@
         <v>20</v>
       </c>
       <c r="H583" s="3" t="n">
-        <v>-32</v>
+        <v>-23</v>
       </c>
       <c r="I583" s="0" t="s">
         <v>21</v>
@@ -30328,7 +30328,7 @@
         <v>401</v>
       </c>
       <c r="H743" s="3" t="n">
-        <v>-3</v>
+        <v>17</v>
       </c>
       <c r="I743" s="0" t="s">
         <v>21</v>
@@ -30357,7 +30357,7 @@
         <v>401</v>
       </c>
       <c r="H744" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I744" s="0" t="s">
         <v>21</v>
@@ -30386,7 +30386,7 @@
         <v>401</v>
       </c>
       <c r="H745" s="3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I745" s="0" t="s">
         <v>21</v>
@@ -31894,7 +31894,7 @@
         <v>401</v>
       </c>
       <c r="H797" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I797" s="0" t="s">
         <v>21</v>
@@ -33489,7 +33489,7 @@
         <v>20</v>
       </c>
       <c r="H852" s="3" t="n">
-        <v>-902</v>
+        <v>-906</v>
       </c>
       <c r="I852" s="0" t="s">
         <v>21</v>
@@ -34852,7 +34852,7 @@
         <v>401</v>
       </c>
       <c r="H899" s="3" t="n">
-        <v>-199</v>
+        <v>-204</v>
       </c>
       <c r="I899" s="0" t="s">
         <v>21</v>
@@ -36099,7 +36099,7 @@
         <v>20</v>
       </c>
       <c r="H942" s="3" t="n">
-        <v>-58</v>
+        <v>-28</v>
       </c>
       <c r="I942" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7546.4</v>
+        <v>7617.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14581,7 +14581,7 @@
         <v>401</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I200" s="0" t="s">
         <v>21</v>
@@ -14639,7 +14639,7 @@
         <v>401</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I202" s="0" t="s">
         <v>21</v>
@@ -18641,7 +18641,7 @@
         <v>401</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18670,7 +18670,7 @@
         <v>401</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -18728,7 +18728,7 @@
         <v>401</v>
       </c>
       <c r="H343" s="3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I343" s="0" t="s">
         <v>21</v>
@@ -18757,7 +18757,7 @@
         <v>401</v>
       </c>
       <c r="H344" s="3" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I344" s="0" t="s">
         <v>21</v>
@@ -18786,7 +18786,7 @@
         <v>401</v>
       </c>
       <c r="H345" s="3" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I345" s="0" t="s">
         <v>21</v>
@@ -19511,7 +19511,7 @@
         <v>401</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19569,7 +19569,7 @@
         <v>401</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19685,7 +19685,7 @@
         <v>401</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I376" s="0" t="s">
         <v>21</v>
@@ -19743,7 +19743,7 @@
         <v>401</v>
       </c>
       <c r="H378" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I378" s="0" t="s">
         <v>21</v>
@@ -19772,7 +19772,7 @@
         <v>401</v>
       </c>
       <c r="H379" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I379" s="0" t="s">
         <v>21</v>
@@ -19830,7 +19830,7 @@
         <v>401</v>
       </c>
       <c r="H381" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I381" s="0" t="s">
         <v>21</v>
@@ -21048,7 +21048,7 @@
         <v>858</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I423" s="0" t="s">
         <v>21</v>
@@ -21686,7 +21686,7 @@
         <v>401</v>
       </c>
       <c r="H445" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I445" s="0" t="s">
         <v>21</v>
@@ -22295,7 +22295,7 @@
         <v>401</v>
       </c>
       <c r="H466" s="3" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="I466" s="0" t="s">
         <v>21</v>
@@ -22527,7 +22527,7 @@
         <v>401</v>
       </c>
       <c r="H474" s="3" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="I474" s="0" t="s">
         <v>21</v>
@@ -22585,7 +22585,7 @@
         <v>401</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22614,7 +22614,7 @@
         <v>401</v>
       </c>
       <c r="H477" s="3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I477" s="0" t="s">
         <v>21</v>
@@ -23716,7 +23716,7 @@
         <v>401</v>
       </c>
       <c r="H515" s="3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I515" s="0" t="s">
         <v>21</v>
@@ -23977,7 +23977,7 @@
         <v>401</v>
       </c>
       <c r="H524" s="3" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I524" s="0" t="s">
         <v>21</v>
@@ -24963,7 +24963,7 @@
         <v>401</v>
       </c>
       <c r="H558" s="3" t="n">
-        <v>613</v>
+        <v>589</v>
       </c>
       <c r="I558" s="0" t="s">
         <v>21</v>
@@ -25079,7 +25079,7 @@
         <v>401</v>
       </c>
       <c r="H562" s="3" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I562" s="0" t="s">
         <v>21</v>
@@ -27515,7 +27515,7 @@
         <v>401</v>
       </c>
       <c r="H646" s="3" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I646" s="0" t="s">
         <v>21</v>
@@ -28588,7 +28588,7 @@
         <v>401</v>
       </c>
       <c r="H683" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I683" s="0" t="s">
         <v>21</v>
@@ -28646,7 +28646,7 @@
         <v>401</v>
       </c>
       <c r="H685" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I685" s="0" t="s">
         <v>21</v>
@@ -28675,7 +28675,7 @@
         <v>401</v>
       </c>
       <c r="H686" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I686" s="0" t="s">
         <v>21</v>
@@ -28704,7 +28704,7 @@
         <v>401</v>
       </c>
       <c r="H687" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I687" s="0" t="s">
         <v>21</v>
@@ -28733,7 +28733,7 @@
         <v>401</v>
       </c>
       <c r="H688" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I688" s="0" t="s">
         <v>21</v>
@@ -28762,7 +28762,7 @@
         <v>401</v>
       </c>
       <c r="H689" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I689" s="0" t="s">
         <v>21</v>
@@ -28791,7 +28791,7 @@
         <v>401</v>
       </c>
       <c r="H690" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I690" s="0" t="s">
         <v>21</v>
@@ -28820,7 +28820,7 @@
         <v>401</v>
       </c>
       <c r="H691" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I691" s="0" t="s">
         <v>21</v>
@@ -28849,7 +28849,7 @@
         <v>401</v>
       </c>
       <c r="H692" s="3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I692" s="0" t="s">
         <v>21</v>
@@ -28878,7 +28878,7 @@
         <v>401</v>
       </c>
       <c r="H693" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I693" s="0" t="s">
         <v>21</v>
@@ -28907,7 +28907,7 @@
         <v>401</v>
       </c>
       <c r="H694" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I694" s="0" t="s">
         <v>21</v>
@@ -29255,7 +29255,7 @@
         <v>858</v>
       </c>
       <c r="H706" s="3" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="I706" s="0" t="s">
         <v>21</v>
@@ -30328,7 +30328,7 @@
         <v>401</v>
       </c>
       <c r="H743" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I743" s="0" t="s">
         <v>21</v>
@@ -30357,7 +30357,7 @@
         <v>401</v>
       </c>
       <c r="H744" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I744" s="0" t="s">
         <v>21</v>
@@ -30763,7 +30763,7 @@
         <v>858</v>
       </c>
       <c r="H758" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I758" s="0" t="s">
         <v>21</v>
@@ -31720,7 +31720,7 @@
         <v>401</v>
       </c>
       <c r="H791" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I791" s="0" t="s">
         <v>21</v>
@@ -31981,7 +31981,7 @@
         <v>401</v>
       </c>
       <c r="H800" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I800" s="0" t="s">
         <v>21</v>
@@ -32938,7 +32938,7 @@
         <v>401</v>
       </c>
       <c r="H833" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I833" s="0" t="s">
         <v>21</v>
@@ -33257,7 +33257,7 @@
         <v>401</v>
       </c>
       <c r="H844" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I844" s="0" t="s">
         <v>21</v>
@@ -33315,7 +33315,7 @@
         <v>401</v>
       </c>
       <c r="H846" s="3" t="n">
-        <v>-67</v>
+        <v>-68</v>
       </c>
       <c r="I846" s="0" t="s">
         <v>21</v>
@@ -34446,7 +34446,7 @@
         <v>401</v>
       </c>
       <c r="H885" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I885" s="0" t="s">
         <v>21</v>
@@ -34475,7 +34475,7 @@
         <v>401</v>
       </c>
       <c r="H886" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I886" s="0" t="s">
         <v>21</v>
@@ -34591,7 +34591,7 @@
         <v>401</v>
       </c>
       <c r="H890" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I890" s="0" t="s">
         <v>21</v>
@@ -36012,7 +36012,7 @@
         <v>401</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -36331,7 +36331,7 @@
         <v>401</v>
       </c>
       <c r="H950" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I950" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7617.4</v>
+        <v>7476.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>29 October 2026</t>
+    <t>30 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -12928,7 +12928,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -14668,7 +14668,7 @@
         <v>401</v>
       </c>
       <c r="H203" s="3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I203" s="0" t="s">
         <v>21</v>
@@ -18757,7 +18757,7 @@
         <v>401</v>
       </c>
       <c r="H344" s="3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I344" s="0" t="s">
         <v>21</v>
@@ -18786,7 +18786,7 @@
         <v>401</v>
       </c>
       <c r="H345" s="3" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I345" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7476.4</v>
+        <v>7472.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9477,7 +9477,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-19</v>
+        <v>-23</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -9506,7 +9506,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>21</v>
@@ -10173,7 +10173,7 @@
         <v>20</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I48" s="0" t="s">
         <v>21</v>
@@ -11594,7 +11594,7 @@
         <v>20</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I97" s="0" t="s">
         <v>21</v>
@@ -12145,7 +12145,7 @@
         <v>20</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I116" s="0" t="s">
         <v>21</v>
@@ -12203,7 +12203,7 @@
         <v>20</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I118" s="0" t="s">
         <v>21</v>
@@ -12464,7 +12464,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -12783,7 +12783,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -12928,7 +12928,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -12986,7 +12986,7 @@
         <v>20</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I145" s="0" t="s">
         <v>21</v>
@@ -13160,7 +13160,7 @@
         <v>20</v>
       </c>
       <c r="H151" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I151" s="0" t="s">
         <v>21</v>
@@ -13334,7 +13334,7 @@
         <v>20</v>
       </c>
       <c r="H157" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I157" s="0" t="s">
         <v>21</v>
@@ -14146,7 +14146,7 @@
         <v>20</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I185" s="0" t="s">
         <v>21</v>
@@ -17423,7 +17423,7 @@
         <v>20</v>
       </c>
       <c r="H298" s="3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I298" s="0" t="s">
         <v>21</v>
@@ -18670,7 +18670,7 @@
         <v>401</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -18815,7 +18815,7 @@
         <v>401</v>
       </c>
       <c r="H346" s="3" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I346" s="0" t="s">
         <v>21</v>
@@ -20323,7 +20323,7 @@
         <v>20</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I398" s="0" t="s">
         <v>21</v>
@@ -20468,7 +20468,7 @@
         <v>20</v>
       </c>
       <c r="H403" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I403" s="0" t="s">
         <v>21</v>
@@ -20497,7 +20497,7 @@
         <v>20</v>
       </c>
       <c r="H404" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I404" s="0" t="s">
         <v>21</v>
@@ -21918,7 +21918,7 @@
         <v>401</v>
       </c>
       <c r="H453" s="3" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I453" s="0" t="s">
         <v>21</v>
@@ -22150,7 +22150,7 @@
         <v>20</v>
       </c>
       <c r="H461" s="3" t="n">
-        <v>-524</v>
+        <v>-526</v>
       </c>
       <c r="I461" s="0" t="s">
         <v>21</v>
@@ -23049,7 +23049,7 @@
         <v>401</v>
       </c>
       <c r="H492" s="3" t="n">
-        <v>-58</v>
+        <v>-62</v>
       </c>
       <c r="I492" s="0" t="s">
         <v>21</v>
@@ -23977,7 +23977,7 @@
         <v>401</v>
       </c>
       <c r="H524" s="3" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="I524" s="0" t="s">
         <v>21</v>
@@ -24122,7 +24122,7 @@
         <v>401</v>
       </c>
       <c r="H529" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I529" s="0" t="s">
         <v>21</v>
@@ -25195,7 +25195,7 @@
         <v>20</v>
       </c>
       <c r="H566" s="3" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="I566" s="0" t="s">
         <v>21</v>
@@ -25601,7 +25601,7 @@
         <v>20</v>
       </c>
       <c r="H580" s="3" t="n">
-        <v>-771</v>
+        <v>-772</v>
       </c>
       <c r="I580" s="0" t="s">
         <v>21</v>
@@ -25688,7 +25688,7 @@
         <v>20</v>
       </c>
       <c r="H583" s="3" t="n">
-        <v>-23</v>
+        <v>-27</v>
       </c>
       <c r="I583" s="0" t="s">
         <v>21</v>
@@ -27515,7 +27515,7 @@
         <v>401</v>
       </c>
       <c r="H646" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I646" s="0" t="s">
         <v>21</v>
@@ -29197,7 +29197,7 @@
         <v>858</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -33489,7 +33489,7 @@
         <v>20</v>
       </c>
       <c r="H852" s="3" t="n">
-        <v>-906</v>
+        <v>-910</v>
       </c>
       <c r="I852" s="0" t="s">
         <v>21</v>
@@ -34707,7 +34707,7 @@
         <v>20</v>
       </c>
       <c r="H894" s="3" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="I894" s="0" t="s">
         <v>844</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7472.4</v>
+        <v>7435.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14581,7 +14581,7 @@
         <v>401</v>
       </c>
       <c r="H200" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I200" s="0" t="s">
         <v>21</v>
@@ -14639,7 +14639,7 @@
         <v>401</v>
       </c>
       <c r="H202" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I202" s="0" t="s">
         <v>21</v>
@@ -18641,7 +18641,7 @@
         <v>401</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18670,7 +18670,7 @@
         <v>401</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -19511,7 +19511,7 @@
         <v>401</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I370" s="0" t="s">
         <v>21</v>
@@ -19743,7 +19743,7 @@
         <v>401</v>
       </c>
       <c r="H378" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I378" s="0" t="s">
         <v>21</v>
@@ -19772,7 +19772,7 @@
         <v>401</v>
       </c>
       <c r="H379" s="3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I379" s="0" t="s">
         <v>21</v>
@@ -19801,7 +19801,7 @@
         <v>401</v>
       </c>
       <c r="H380" s="3" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="I380" s="0" t="s">
         <v>21</v>
@@ -21048,7 +21048,7 @@
         <v>858</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I423" s="0" t="s">
         <v>21</v>
@@ -21686,7 +21686,7 @@
         <v>401</v>
       </c>
       <c r="H445" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I445" s="0" t="s">
         <v>21</v>
@@ -22121,7 +22121,7 @@
         <v>401</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>-6697.6</v>
+        <v>-6705.6</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22469,7 +22469,7 @@
         <v>401</v>
       </c>
       <c r="H472" s="3" t="n">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="I472" s="0" t="s">
         <v>21</v>
@@ -22585,7 +22585,7 @@
         <v>401</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22614,7 +22614,7 @@
         <v>401</v>
       </c>
       <c r="H477" s="3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I477" s="0" t="s">
         <v>21</v>
@@ -29168,7 +29168,7 @@
         <v>858</v>
       </c>
       <c r="H703" s="3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I703" s="0" t="s">
         <v>21</v>
@@ -29197,7 +29197,7 @@
         <v>858</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -29255,7 +29255,7 @@
         <v>858</v>
       </c>
       <c r="H706" s="3" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="I706" s="0" t="s">
         <v>21</v>
@@ -30763,7 +30763,7 @@
         <v>858</v>
       </c>
       <c r="H758" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I758" s="0" t="s">
         <v>21</v>
@@ -31952,7 +31952,7 @@
         <v>401</v>
       </c>
       <c r="H799" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I799" s="0" t="s">
         <v>21</v>
@@ -36012,7 +36012,7 @@
         <v>401</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7435.4</v>
+        <v>7363.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -31,7 +31,7 @@
     <t>From</t>
   </si>
   <si>
-    <t>30 October 2026</t>
+    <t>31 October 2026</t>
   </si>
   <si>
     <t>To</t>
@@ -11246,7 +11246,7 @@
         <v>20</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="I85" s="0" t="s">
         <v>21</v>
@@ -12928,7 +12928,7 @@
         <v>20</v>
       </c>
       <c r="H143" s="3" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="I143" s="0" t="s">
         <v>21</v>
@@ -14146,7 +14146,7 @@
         <v>20</v>
       </c>
       <c r="H185" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I185" s="0" t="s">
         <v>21</v>
@@ -20323,7 +20323,7 @@
         <v>20</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I398" s="0" t="s">
         <v>21</v>
@@ -35287,7 +35287,7 @@
         <v>20</v>
       </c>
       <c r="H914" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I914" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7363.4</v>
+        <v>7357.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -9477,7 +9477,7 @@
         <v>20</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>-23</v>
+        <v>-25</v>
       </c>
       <c r="I24" s="0" t="s">
         <v>21</v>
@@ -9506,7 +9506,7 @@
         <v>20</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="I25" s="0" t="s">
         <v>21</v>
@@ -9535,7 +9535,7 @@
         <v>20</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="I26" s="0" t="s">
         <v>21</v>
@@ -10492,7 +10492,7 @@
         <v>20</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I59" s="0" t="s">
         <v>21</v>
@@ -11304,7 +11304,7 @@
         <v>20</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I87" s="0" t="s">
         <v>21</v>
@@ -11797,7 +11797,7 @@
         <v>20</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="I104" s="0" t="s">
         <v>21</v>
@@ -12464,7 +12464,7 @@
         <v>20</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>-28</v>
+        <v>-30</v>
       </c>
       <c r="I127" s="0" t="s">
         <v>21</v>
@@ -12783,7 +12783,7 @@
         <v>20</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="I138" s="0" t="s">
         <v>21</v>
@@ -13247,7 +13247,7 @@
         <v>20</v>
       </c>
       <c r="H154" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I154" s="0" t="s">
         <v>21</v>
@@ -13421,7 +13421,7 @@
         <v>20</v>
       </c>
       <c r="H160" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I160" s="0" t="s">
         <v>21</v>
@@ -14175,7 +14175,7 @@
         <v>20</v>
       </c>
       <c r="H186" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I186" s="0" t="s">
         <v>21</v>
@@ -17423,7 +17423,7 @@
         <v>20</v>
       </c>
       <c r="H298" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I298" s="0" t="s">
         <v>21</v>
@@ -17452,7 +17452,7 @@
         <v>20</v>
       </c>
       <c r="H299" s="3" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I299" s="0" t="s">
         <v>21</v>
@@ -20294,7 +20294,7 @@
         <v>20</v>
       </c>
       <c r="H397" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I397" s="0" t="s">
         <v>21</v>
@@ -20613,7 +20613,7 @@
         <v>20</v>
       </c>
       <c r="H408" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I408" s="0" t="s">
         <v>21</v>
@@ -22150,7 +22150,7 @@
         <v>20</v>
       </c>
       <c r="H461" s="3" t="n">
-        <v>-526</v>
+        <v>-528</v>
       </c>
       <c r="I461" s="0" t="s">
         <v>21</v>
@@ -23368,7 +23368,7 @@
         <v>20</v>
       </c>
       <c r="H503" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I503" s="0" t="s">
         <v>21</v>
@@ -25398,7 +25398,7 @@
         <v>20</v>
       </c>
       <c r="H573" s="3" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="I573" s="0" t="s">
         <v>21</v>
@@ -25543,7 +25543,7 @@
         <v>20</v>
       </c>
       <c r="H578" s="3" t="n">
-        <v>-336</v>
+        <v>-337</v>
       </c>
       <c r="I578" s="0" t="s">
         <v>21</v>
@@ -25601,7 +25601,7 @@
         <v>20</v>
       </c>
       <c r="H580" s="3" t="n">
-        <v>-772</v>
+        <v>-773</v>
       </c>
       <c r="I580" s="0" t="s">
         <v>21</v>
@@ -25688,7 +25688,7 @@
         <v>20</v>
       </c>
       <c r="H583" s="3" t="n">
-        <v>-27</v>
+        <v>-33</v>
       </c>
       <c r="I583" s="0" t="s">
         <v>21</v>
@@ -27080,7 +27080,7 @@
         <v>20</v>
       </c>
       <c r="H631" s="3" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="I631" s="0" t="s">
         <v>21</v>
@@ -29168,7 +29168,7 @@
         <v>858</v>
       </c>
       <c r="H703" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I703" s="0" t="s">
         <v>21</v>
@@ -29197,7 +29197,7 @@
         <v>858</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -33489,7 +33489,7 @@
         <v>20</v>
       </c>
       <c r="H852" s="3" t="n">
-        <v>-910</v>
+        <v>-913</v>
       </c>
       <c r="I852" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7357.4</v>
+        <v>7311.4</v>
       </c>
     </row>
   </sheetData>

--- a/stock_data/SKU.xlsx
+++ b/stock_data/SKU.xlsx
@@ -14610,7 +14610,7 @@
         <v>401</v>
       </c>
       <c r="H201" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I201" s="0" t="s">
         <v>21</v>
@@ -18641,7 +18641,7 @@
         <v>401</v>
       </c>
       <c r="H340" s="3" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I340" s="0" t="s">
         <v>21</v>
@@ -18670,7 +18670,7 @@
         <v>401</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I341" s="0" t="s">
         <v>21</v>
@@ -18728,7 +18728,7 @@
         <v>401</v>
       </c>
       <c r="H343" s="3" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I343" s="0" t="s">
         <v>21</v>
@@ -18757,7 +18757,7 @@
         <v>401</v>
       </c>
       <c r="H344" s="3" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I344" s="0" t="s">
         <v>21</v>
@@ -18786,7 +18786,7 @@
         <v>401</v>
       </c>
       <c r="H345" s="3" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I345" s="0" t="s">
         <v>21</v>
@@ -18815,7 +18815,7 @@
         <v>401</v>
       </c>
       <c r="H346" s="3" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I346" s="0" t="s">
         <v>21</v>
@@ -19569,7 +19569,7 @@
         <v>401</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I372" s="0" t="s">
         <v>21</v>
@@ -19772,7 +19772,7 @@
         <v>401</v>
       </c>
       <c r="H379" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I379" s="0" t="s">
         <v>21</v>
@@ -19801,7 +19801,7 @@
         <v>401</v>
       </c>
       <c r="H380" s="3" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I380" s="0" t="s">
         <v>21</v>
@@ -19830,7 +19830,7 @@
         <v>401</v>
       </c>
       <c r="H381" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I381" s="0" t="s">
         <v>21</v>
@@ -21048,7 +21048,7 @@
         <v>858</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I423" s="0" t="s">
         <v>21</v>
@@ -21425,7 +21425,7 @@
         <v>401</v>
       </c>
       <c r="H436" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I436" s="0" t="s">
         <v>21</v>
@@ -21686,7 +21686,7 @@
         <v>401</v>
       </c>
       <c r="H445" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I445" s="0" t="s">
         <v>21</v>
@@ -22121,7 +22121,7 @@
         <v>401</v>
       </c>
       <c r="H460" s="3" t="n">
-        <v>-6705.6</v>
+        <v>-6721.6</v>
       </c>
       <c r="I460" s="0" t="s">
         <v>21</v>
@@ -22585,7 +22585,7 @@
         <v>401</v>
       </c>
       <c r="H476" s="3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I476" s="0" t="s">
         <v>21</v>
@@ -22817,7 +22817,7 @@
         <v>401</v>
       </c>
       <c r="H484" s="3" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I484" s="0" t="s">
         <v>21</v>
@@ -22904,7 +22904,7 @@
         <v>401</v>
       </c>
       <c r="H487" s="3" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="I487" s="0" t="s">
         <v>21</v>
@@ -23107,7 +23107,7 @@
         <v>401</v>
       </c>
       <c r="H494" s="3" t="n">
-        <v>-435</v>
+        <v>-437</v>
       </c>
       <c r="I494" s="0" t="s">
         <v>21</v>
@@ -23223,7 +23223,7 @@
         <v>401</v>
       </c>
       <c r="H498" s="3" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="I498" s="0" t="s">
         <v>21</v>
@@ -23339,7 +23339,7 @@
         <v>401</v>
       </c>
       <c r="H502" s="3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I502" s="0" t="s">
         <v>21</v>
@@ -23629,7 +23629,7 @@
         <v>401</v>
       </c>
       <c r="H512" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I512" s="0" t="s">
         <v>21</v>
@@ -23658,7 +23658,7 @@
         <v>401</v>
       </c>
       <c r="H513" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I513" s="0" t="s">
         <v>21</v>
@@ -23716,7 +23716,7 @@
         <v>401</v>
       </c>
       <c r="H515" s="3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I515" s="0" t="s">
         <v>21</v>
@@ -23774,7 +23774,7 @@
         <v>401</v>
       </c>
       <c r="H517" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I517" s="0" t="s">
         <v>21</v>
@@ -23977,7 +23977,7 @@
         <v>401</v>
       </c>
       <c r="H524" s="3" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="I524" s="0" t="s">
         <v>21</v>
@@ -25949,7 +25949,7 @@
         <v>401</v>
       </c>
       <c r="H592" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I592" s="0" t="s">
         <v>21</v>
@@ -27486,7 +27486,7 @@
         <v>401</v>
       </c>
       <c r="H645" s="3" t="n">
-        <v>-101</v>
+        <v>-102</v>
       </c>
       <c r="I645" s="0" t="s">
         <v>21</v>
@@ -29168,7 +29168,7 @@
         <v>858</v>
       </c>
       <c r="H703" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I703" s="0" t="s">
         <v>21</v>
@@ -29197,7 +29197,7 @@
         <v>858</v>
       </c>
       <c r="H704" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I704" s="0" t="s">
         <v>21</v>
@@ -29255,7 +29255,7 @@
         <v>858</v>
       </c>
       <c r="H706" s="3" t="n">
-        <v>-11</v>
+        <v>-13</v>
       </c>
       <c r="I706" s="0" t="s">
         <v>21</v>
@@ -29516,7 +29516,7 @@
         <v>401</v>
       </c>
       <c r="H715" s="3" t="n">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="I715" s="0" t="s">
         <v>21</v>
@@ -30763,7 +30763,7 @@
         <v>858</v>
       </c>
       <c r="H758" s="3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I758" s="0" t="s">
         <v>21</v>
@@ -32010,7 +32010,7 @@
         <v>401</v>
       </c>
       <c r="H801" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I801" s="0" t="s">
         <v>21</v>
@@ -32793,7 +32793,7 @@
         <v>401</v>
       </c>
       <c r="H828" s="3" t="n">
-        <v>-23</v>
+        <v>-33</v>
       </c>
       <c r="I828" s="0" t="s">
         <v>21</v>
@@ -32822,7 +32822,7 @@
         <v>401</v>
       </c>
       <c r="H829" s="3" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="I829" s="0" t="s">
         <v>21</v>
@@ -32938,7 +32938,7 @@
         <v>401</v>
       </c>
       <c r="H833" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I833" s="0" t="s">
         <v>21</v>
@@ -34939,7 +34939,7 @@
         <v>401</v>
       </c>
       <c r="H902" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I902" s="0" t="s">
         <v>21</v>
@@ -35142,7 +35142,7 @@
         <v>401</v>
       </c>
       <c r="H909" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I909" s="0" t="s">
         <v>21</v>
@@ -36012,7 +36012,7 @@
         <v>401</v>
       </c>
       <c r="H939" s="3" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I939" s="0" t="s">
         <v>21</v>
@@ -36331,7 +36331,7 @@
         <v>401</v>
       </c>
       <c r="H950" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I950" s="0" t="s">
         <v>21</v>
@@ -37238,7 +37238,7 @@
     </row>
     <row r="982" spans="8:8" customHeight="1">
       <c r="H982" s="3" t="n">
-        <v>7311.4</v>
+        <v>7175.4</v>
       </c>
     </row>
   </sheetData>
